--- a/电影票房分析表.xlsx
+++ b/电影票房分析表.xlsx
@@ -11,9 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="票房预估分析" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售数据明细" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来龙餐馆预售追踪" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售增长预测" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="想看数据明细" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售与票房节点" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售增长分析" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售增长预测" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="想看数据明细" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售与票房节点" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -28,7 +29,7 @@
     <numFmt numFmtId="166" formatCode="¥#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="43">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -292,8 +293,35 @@
       <color rgb="002E7D32"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -398,6 +426,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+        <bgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B9BD5"/>
+        <bgColor rgb="005B9BD5"/>
       </patternFill>
     </fill>
   </fills>
@@ -566,7 +624,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1087,6 +1145,30 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="21" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="22" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="23" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="23" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="24" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1158,342 +1240,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1780,7 +1526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -2018,12 +1764,11 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -2888,12 +2633,11 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -3211,17 +2955,16 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="69" min="1" max="1"/>
@@ -3679,6 +3422,90 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="177" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:50</t>
+        </is>
+      </c>
+      <c r="B28" s="177" t="inlineStr">
+        <is>
+          <t>映前5天</t>
+        </is>
+      </c>
+      <c r="C28" s="177" t="inlineStr">
+        <is>
+          <t>定时任务</t>
+        </is>
+      </c>
+      <c r="D28" s="177" t="n">
+        <v>555.3</v>
+      </c>
+      <c r="E28" s="177" t="inlineStr">
+        <is>
+          <t>猫眼专业版</t>
+        </is>
+      </c>
+      <c r="F28" s="177" t="inlineStr"/>
+      <c r="G28" s="177" t="inlineStr"/>
+      <c r="H28" s="177" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="177" t="inlineStr">
+        <is>
+          <t>2026-08-06 23:00</t>
+        </is>
+      </c>
+      <c r="B29" s="177" t="inlineStr">
+        <is>
+          <t>映前5天</t>
+        </is>
+      </c>
+      <c r="C29" s="177" t="inlineStr">
+        <is>
+          <t>GitHub Actions</t>
+        </is>
+      </c>
+      <c r="D29" s="177" t="n">
+        <v>565.1</v>
+      </c>
+      <c r="E29" s="177" t="inlineStr">
+        <is>
+          <t>猫眼专业版</t>
+        </is>
+      </c>
+      <c r="F29" s="177" t="inlineStr"/>
+      <c r="G29" s="177" t="inlineStr"/>
+      <c r="H29" s="177" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="177" t="inlineStr">
+        <is>
+          <t>2026-08-06 23:01</t>
+        </is>
+      </c>
+      <c r="B30" s="177" t="inlineStr">
+        <is>
+          <t>映前5天</t>
+        </is>
+      </c>
+      <c r="C30" s="177" t="inlineStr">
+        <is>
+          <t>定时任务</t>
+        </is>
+      </c>
+      <c r="D30" s="177" t="n">
+        <v>565.5</v>
+      </c>
+      <c r="E30" s="177" t="inlineStr">
+        <is>
+          <t>猫眼专业版</t>
+        </is>
+      </c>
+      <c r="F30" s="177" t="inlineStr"/>
+      <c r="G30" s="177" t="inlineStr"/>
+      <c r="H30" s="177" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A24:H24"/>
@@ -3686,12 +3513,641 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" style="69" min="1" max="1"/>
+    <col width="22" customWidth="1" style="69" min="2" max="2"/>
+    <col width="12" customWidth="1" style="69" min="3" max="3"/>
+    <col width="14" customWidth="1" style="69" min="4" max="4"/>
+    <col width="16" customWidth="1" style="69" min="5" max="5"/>
+    <col width="18" customWidth="1" style="69" min="6" max="6"/>
+    <col width="12" customWidth="1" style="69" min="7" max="7"/>
+    <col width="16" customWidth="1" style="69" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="69">
+      <c r="A1" s="178" t="inlineStr">
+        <is>
+          <t>《欢迎来龙餐馆》预售票房增长分析（2026-08-06 映前5天）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1" s="69">
+      <c r="A2" s="179" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" s="179" t="inlineStr">
+        <is>
+          <t>获取时间</t>
+        </is>
+      </c>
+      <c r="C2" s="179" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="D2" s="179" t="inlineStr">
+        <is>
+          <t>预售票房(万)</t>
+        </is>
+      </c>
+      <c r="E2" s="179" t="inlineStr">
+        <is>
+          <t>较前次增量(万)</t>
+        </is>
+      </c>
+      <c r="F2" s="179" t="inlineStr">
+        <is>
+          <t>较22:02增量(万)</t>
+        </is>
+      </c>
+      <c r="G2" s="179" t="inlineStr">
+        <is>
+          <t>增幅(%)</t>
+        </is>
+      </c>
+      <c r="H2" s="179" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="177" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:52:32</t>
+        </is>
+      </c>
+      <c r="C3" s="177" t="inlineStr">
+        <is>
+          <t>映前5天</t>
+        </is>
+      </c>
+      <c r="D3" s="177" t="n">
+        <v>497.8</v>
+      </c>
+      <c r="E3" s="177" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" s="177" t="inlineStr">
+        <is>
+          <t>-4.9</t>
+        </is>
+      </c>
+      <c r="G3" s="177" t="inlineStr">
+        <is>
+          <t>+-1.0%</t>
+        </is>
+      </c>
+      <c r="H3" s="177" t="inlineStr">
+        <is>
+          <t>GitHub Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="180" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="180" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:02:00</t>
+        </is>
+      </c>
+      <c r="C4" s="180" t="inlineStr">
+        <is>
+          <t>映前5天</t>
+        </is>
+      </c>
+      <c r="D4" s="180" t="n">
+        <v>502.7</v>
+      </c>
+      <c r="E4" s="180" t="inlineStr">
+        <is>
+          <t>+4.9</t>
+        </is>
+      </c>
+      <c r="F4" s="180" t="inlineStr">
+        <is>
+          <t>—（基准）</t>
+        </is>
+      </c>
+      <c r="G4" s="180" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" s="180" t="inlineStr">
+        <is>
+          <t>定时任务</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="177" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="177" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:30:00</t>
+        </is>
+      </c>
+      <c r="C5" s="177" t="inlineStr">
+        <is>
+          <t>映前5天</t>
+        </is>
+      </c>
+      <c r="D5" s="177" t="n">
+        <v>525.7</v>
+      </c>
+      <c r="E5" s="177" t="inlineStr">
+        <is>
+          <t>+23.0</t>
+        </is>
+      </c>
+      <c r="F5" s="177" t="inlineStr">
+        <is>
+          <t>+23.0</t>
+        </is>
+      </c>
+      <c r="G5" s="177" t="inlineStr">
+        <is>
+          <t>+4.6%</t>
+        </is>
+      </c>
+      <c r="H5" s="177" t="inlineStr">
+        <is>
+          <t>GitHub Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="177" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="177" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:50:40</t>
+        </is>
+      </c>
+      <c r="C6" s="177" t="inlineStr">
+        <is>
+          <t>映前5天</t>
+        </is>
+      </c>
+      <c r="D6" s="177" t="n">
+        <v>555.3</v>
+      </c>
+      <c r="E6" s="177" t="inlineStr">
+        <is>
+          <t>+29.6</t>
+        </is>
+      </c>
+      <c r="F6" s="177" t="inlineStr">
+        <is>
+          <t>+52.6</t>
+        </is>
+      </c>
+      <c r="G6" s="177" t="inlineStr">
+        <is>
+          <t>+10.5%</t>
+        </is>
+      </c>
+      <c r="H6" s="177" t="inlineStr">
+        <is>
+          <t>定时任务</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="177" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="177" t="inlineStr">
+        <is>
+          <t>2026-08-06 23:00:29</t>
+        </is>
+      </c>
+      <c r="C7" s="177" t="inlineStr">
+        <is>
+          <t>映前5天</t>
+        </is>
+      </c>
+      <c r="D7" s="177" t="n">
+        <v>565.1</v>
+      </c>
+      <c r="E7" s="177" t="inlineStr">
+        <is>
+          <t>+9.8</t>
+        </is>
+      </c>
+      <c r="F7" s="177" t="inlineStr">
+        <is>
+          <t>+62.4</t>
+        </is>
+      </c>
+      <c r="G7" s="177" t="inlineStr">
+        <is>
+          <t>+12.4%</t>
+        </is>
+      </c>
+      <c r="H7" s="177" t="inlineStr">
+        <is>
+          <t>GitHub Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="177" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="177" t="inlineStr">
+        <is>
+          <t>2026-08-06 23:01:02</t>
+        </is>
+      </c>
+      <c r="C8" s="177" t="inlineStr">
+        <is>
+          <t>映前5天</t>
+        </is>
+      </c>
+      <c r="D8" s="177" t="n">
+        <v>565.5</v>
+      </c>
+      <c r="E8" s="177" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
+      <c r="F8" s="177" t="inlineStr">
+        <is>
+          <t>+62.8</t>
+        </is>
+      </c>
+      <c r="G8" s="177" t="inlineStr">
+        <is>
+          <t>+12.5%</t>
+        </is>
+      </c>
+      <c r="H8" s="177" t="inlineStr">
+        <is>
+          <t>定时任务</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1" s="69">
+      <c r="A10" s="181" t="inlineStr">
+        <is>
+          <t>增长分析汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="182" t="inlineStr">
+        <is>
+          <t>起始时间</t>
+        </is>
+      </c>
+      <c r="B11" s="182" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:02:00</t>
+        </is>
+      </c>
+      <c r="C11" s="182" t="inlineStr">
+        <is>
+          <t>基准票房</t>
+        </is>
+      </c>
+      <c r="D11" s="182" t="inlineStr">
+        <is>
+          <t>502.7万</t>
+        </is>
+      </c>
+      <c r="E11" s="183" t="inlineStr"/>
+      <c r="F11" s="183" t="inlineStr"/>
+      <c r="G11" s="183" t="inlineStr"/>
+      <c r="H11" s="183" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="182" t="inlineStr">
+        <is>
+          <t>最新时间</t>
+        </is>
+      </c>
+      <c r="B12" s="182" t="inlineStr">
+        <is>
+          <t>2026-08-06 23:01:02</t>
+        </is>
+      </c>
+      <c r="C12" s="182" t="inlineStr">
+        <is>
+          <t>最新票房</t>
+        </is>
+      </c>
+      <c r="D12" s="182" t="inlineStr">
+        <is>
+          <t>565.5万</t>
+        </is>
+      </c>
+      <c r="E12" s="183" t="inlineStr"/>
+      <c r="F12" s="183" t="inlineStr"/>
+      <c r="G12" s="183" t="inlineStr"/>
+      <c r="H12" s="183" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="182" t="inlineStr">
+        <is>
+          <t>总增长(较22:02)</t>
+        </is>
+      </c>
+      <c r="B13" s="182" t="inlineStr">
+        <is>
+          <t>+62.8万</t>
+        </is>
+      </c>
+      <c r="C13" s="182" t="inlineStr">
+        <is>
+          <t>增幅</t>
+        </is>
+      </c>
+      <c r="D13" s="182" t="inlineStr">
+        <is>
+          <t>+12.5%</t>
+        </is>
+      </c>
+      <c r="E13" s="183" t="inlineStr">
+        <is>
+          <t>时长</t>
+        </is>
+      </c>
+      <c r="F13" s="183" t="inlineStr">
+        <is>
+          <t>约59分钟</t>
+        </is>
+      </c>
+      <c r="G13" s="183" t="inlineStr">
+        <is>
+          <t>平均增速</t>
+        </is>
+      </c>
+      <c r="H13" s="183" t="inlineStr">
+        <is>
+          <t>63.9万/小时</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="182" t="inlineStr">
+        <is>
+          <t>总增长(较21:52)</t>
+        </is>
+      </c>
+      <c r="B14" s="182" t="inlineStr">
+        <is>
+          <t>+67.7万</t>
+        </is>
+      </c>
+      <c r="C14" s="182" t="inlineStr">
+        <is>
+          <t>增幅</t>
+        </is>
+      </c>
+      <c r="D14" s="182" t="inlineStr">
+        <is>
+          <t>+13.6%</t>
+        </is>
+      </c>
+      <c r="E14" s="183" t="inlineStr">
+        <is>
+          <t>时长</t>
+        </is>
+      </c>
+      <c r="F14" s="183" t="inlineStr">
+        <is>
+          <t>约69分钟</t>
+        </is>
+      </c>
+      <c r="G14" s="183" t="inlineStr">
+        <is>
+          <t>平均增速</t>
+        </is>
+      </c>
+      <c r="H14" s="183" t="inlineStr">
+        <is>
+          <t>58.9万/小时</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="25" customHeight="1" s="69">
+      <c r="A16" s="181" t="inlineStr">
+        <is>
+          <t>分时段增速明细</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="184" t="inlineStr">
+        <is>
+          <t>时段</t>
+        </is>
+      </c>
+      <c r="B17" s="184" t="inlineStr">
+        <is>
+          <t>时长</t>
+        </is>
+      </c>
+      <c r="C17" s="184" t="inlineStr">
+        <is>
+          <t>起始票房(万)</t>
+        </is>
+      </c>
+      <c r="D17" s="184" t="inlineStr">
+        <is>
+          <t>结束票房(万)</t>
+        </is>
+      </c>
+      <c r="E17" s="184" t="inlineStr">
+        <is>
+          <t>增量(万)</t>
+        </is>
+      </c>
+      <c r="F17" s="184" t="inlineStr">
+        <is>
+          <t>增速(万/小时)</t>
+        </is>
+      </c>
+      <c r="G17" s="184" t="inlineStr">
+        <is>
+          <t>增速评价</t>
+        </is>
+      </c>
+      <c r="H17" s="184" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="177" t="inlineStr">
+        <is>
+          <t>21:52 → 22:02</t>
+        </is>
+      </c>
+      <c r="B18" s="177" t="inlineStr">
+        <is>
+          <t>10分钟</t>
+        </is>
+      </c>
+      <c r="C18" s="177" t="n">
+        <v>497.8</v>
+      </c>
+      <c r="D18" s="177" t="n">
+        <v>502.7</v>
+      </c>
+      <c r="E18" s="177" t="inlineStr">
+        <is>
+          <t>+4.9</t>
+        </is>
+      </c>
+      <c r="F18" s="177" t="inlineStr">
+        <is>
+          <t>29.4</t>
+        </is>
+      </c>
+      <c r="G18" s="177" t="inlineStr">
+        <is>
+          <t>中等增长</t>
+        </is>
+      </c>
+      <c r="H18" s="177" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="177" t="inlineStr">
+        <is>
+          <t>22:02 → 22:30</t>
+        </is>
+      </c>
+      <c r="B19" s="177" t="inlineStr">
+        <is>
+          <t>28分钟</t>
+        </is>
+      </c>
+      <c r="C19" s="177" t="n">
+        <v>502.7</v>
+      </c>
+      <c r="D19" s="177" t="n">
+        <v>525.7</v>
+      </c>
+      <c r="E19" s="177" t="inlineStr">
+        <is>
+          <t>+23.0</t>
+        </is>
+      </c>
+      <c r="F19" s="177" t="inlineStr">
+        <is>
+          <t>49.3</t>
+        </is>
+      </c>
+      <c r="G19" s="177" t="inlineStr">
+        <is>
+          <t>稳定增长</t>
+        </is>
+      </c>
+      <c r="H19" s="177" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="177" t="inlineStr">
+        <is>
+          <t>22:30 → 22:50</t>
+        </is>
+      </c>
+      <c r="B20" s="177" t="inlineStr">
+        <is>
+          <t>20分钟</t>
+        </is>
+      </c>
+      <c r="C20" s="177" t="n">
+        <v>525.7</v>
+      </c>
+      <c r="D20" s="177" t="n">
+        <v>555.3</v>
+      </c>
+      <c r="E20" s="177" t="inlineStr">
+        <is>
+          <t>+29.6</t>
+        </is>
+      </c>
+      <c r="F20" s="177" t="inlineStr">
+        <is>
+          <t>88.8</t>
+        </is>
+      </c>
+      <c r="G20" s="177" t="inlineStr">
+        <is>
+          <t>高速增长</t>
+        </is>
+      </c>
+      <c r="H20" s="177" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="177" t="inlineStr">
+        <is>
+          <t>22:50 → 23:01</t>
+        </is>
+      </c>
+      <c r="B21" s="177" t="inlineStr">
+        <is>
+          <t>11分钟</t>
+        </is>
+      </c>
+      <c r="C21" s="177" t="n">
+        <v>555.3</v>
+      </c>
+      <c r="D21" s="177" t="n">
+        <v>565.5</v>
+      </c>
+      <c r="E21" s="177" t="inlineStr">
+        <is>
+          <t>+10.2</t>
+        </is>
+      </c>
+      <c r="F21" s="177" t="inlineStr">
+        <is>
+          <t>55.6</t>
+        </is>
+      </c>
+      <c r="G21" s="177" t="inlineStr">
+        <is>
+          <t>稳定增长</t>
+        </is>
+      </c>
+      <c r="H21" s="177" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -5700,12 +6156,11 @@
     <mergeCell ref="A87:F87"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -5999,12 +6454,11 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -6570,6 +7024,5 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/电影票房分析表.xlsx
+++ b/电影票房分析表.xlsx
@@ -29,7 +29,7 @@
     <numFmt numFmtId="166" formatCode="¥#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="45">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -320,8 +320,20 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="27">
     <fill>
       <patternFill/>
     </fill>
@@ -456,6 +468,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="005B9BD5"/>
         <bgColor rgb="005B9BD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
+        <bgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -624,7 +648,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1169,6 +1193,28 @@
     </xf>
     <xf numFmtId="0" fontId="39" fillId="24" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="24" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="26" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4152,2008 +4198,2168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="69" min="1" max="1"/>
-    <col width="12" customWidth="1" style="69" min="2" max="2"/>
+    <col width="10" customWidth="1" style="69" min="2" max="2"/>
     <col width="16" customWidth="1" style="69" min="3" max="3"/>
     <col width="16" customWidth="1" style="69" min="4" max="4"/>
     <col width="22" customWidth="1" style="69" min="5" max="5"/>
     <col width="10" customWidth="1" style="69" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" s="69">
-      <c r="A1" s="124" t="inlineStr">
-        <is>
-          <t>《欢迎来龙餐馆》预售票房增长预测（修正版）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" s="69">
-      <c r="A2" s="125" t="inlineStr">
-        <is>
-          <t>基准: 20:02 = 434.2万 | 基于9组实测数据拟合 | 数据来源: 猫眼专业版 | 更新: 2026-08-06 20:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1" s="69">
-      <c r="A3" s="152" t="inlineStr">
-        <is>
-          <t>一、实测增速回算（9组数据，14:45-20:02）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1" s="69">
-      <c r="A4" s="126" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="69">
+      <c r="A1" s="178" t="inlineStr">
+        <is>
+          <t>《欢迎来龙餐馆》预售票房增长预测（V3 修正版）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="185" t="inlineStr">
+        <is>
+          <t>基准: 23:01实测 = 565.5万 | 基于14组实测数据修正 | 数据来源: 猫眼专业版 | 更新: 2026-08-06 23:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" s="69">
+      <c r="A4" s="181" t="inlineStr">
+        <is>
+          <t>一、实测增速回算（14组数据，14:45-23:01）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="186" t="inlineStr">
         <is>
           <t>时间段</t>
         </is>
       </c>
-      <c r="B4" s="126" t="inlineStr">
+      <c r="B5" s="186" t="inlineStr">
         <is>
           <t>时长(min)</t>
         </is>
       </c>
-      <c r="C4" s="126" t="inlineStr">
+      <c r="C5" s="186" t="inlineStr">
         <is>
           <t>增长(万)</t>
         </is>
       </c>
-      <c r="D4" s="126" t="inlineStr">
+      <c r="D5" s="186" t="inlineStr">
         <is>
           <t>小时增速(万/h)</t>
         </is>
       </c>
-      <c r="E4" s="126" t="inlineStr">
+      <c r="E5" s="186" t="inlineStr">
         <is>
           <t>时段归类</t>
         </is>
       </c>
-      <c r="F4" s="126" t="inlineStr">
+      <c r="F5" s="186" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1" s="69">
-      <c r="A5" s="127" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="177" t="inlineStr">
         <is>
           <t>14:45-14:55</t>
         </is>
       </c>
-      <c r="B5" s="127" t="n">
+      <c r="B6" s="177" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="129" t="n">
+      <c r="C6" s="177" t="n">
         <v>11.5</v>
       </c>
-      <c r="D5" s="129" t="n">
+      <c r="D6" s="177" t="n">
         <v>69</v>
       </c>
-      <c r="E5" s="127" t="inlineStr">
+      <c r="E6" s="177" t="inlineStr">
         <is>
           <t>开售首波</t>
         </is>
       </c>
-      <c r="F5" s="130" t="inlineStr">
-        <is>
-          <t>爆发期，含预售刚开放的集中下单</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" s="69">
-      <c r="A6" s="131" t="inlineStr">
+      <c r="F6" s="177" t="inlineStr">
+        <is>
+          <t>爆发期，预售刚开放</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="177" t="inlineStr">
         <is>
           <t>14:55-15:01</t>
         </is>
       </c>
-      <c r="B6" s="131" t="n">
+      <c r="B7" s="177" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="153" t="n">
+      <c r="C7" s="177" t="n">
         <v>8.4</v>
       </c>
-      <c r="D6" s="153" t="n">
+      <c r="D7" s="177" t="n">
         <v>84</v>
       </c>
-      <c r="E6" s="131" t="inlineStr">
+      <c r="E7" s="177" t="inlineStr">
+        <is>
+          <t>下午高峰</t>
+        </is>
+      </c>
+      <c r="F7" s="177" t="inlineStr">
+        <is>
+          <t>开售高峰延续</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="180" t="inlineStr">
+        <is>
+          <t>15:01-15:03</t>
+        </is>
+      </c>
+      <c r="B8" s="180" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="180" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D8" s="180" t="n">
+        <v>105</v>
+      </c>
+      <c r="E8" s="180" t="inlineStr">
+        <is>
+          <t>短暂冲高</t>
+        </is>
+      </c>
+      <c r="F8" s="180" t="inlineStr">
+        <is>
+          <t>极短时脉冲</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="177" t="inlineStr">
+        <is>
+          <t>15:03-16:53</t>
+        </is>
+      </c>
+      <c r="B9" s="177" t="n">
+        <v>110</v>
+      </c>
+      <c r="C9" s="177" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="D9" s="177" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="E9" s="177" t="inlineStr">
         <is>
           <t>下午平稳</t>
         </is>
       </c>
-      <c r="F6" s="133" t="inlineStr">
-        <is>
-          <t>开售高峰后回落</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" s="69">
-      <c r="A7" s="127" t="inlineStr">
-        <is>
-          <t>15:01-15:03</t>
-        </is>
-      </c>
-      <c r="B7" s="127" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="129" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D7" s="129" t="n">
-        <v>105</v>
-      </c>
-      <c r="E7" s="127" t="inlineStr">
-        <is>
-          <t>傍晚低谷</t>
-        </is>
-      </c>
-      <c r="F7" s="130" t="inlineStr">
-        <is>
-          <t>下班前最低速</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" s="69">
-      <c r="A8" s="131" t="inlineStr">
-        <is>
-          <t>15:03-16:53</t>
-        </is>
-      </c>
-      <c r="B8" s="131" t="n">
+      <c r="F9" s="177" t="inlineStr">
+        <is>
+          <t>通勤时段稳定增长</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="177" t="inlineStr">
+        <is>
+          <t>16:53-17:37</t>
+        </is>
+      </c>
+      <c r="B10" s="177" t="n">
+        <v>44</v>
+      </c>
+      <c r="C10" s="177" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D10" s="177" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="E10" s="177" t="inlineStr">
+        <is>
+          <t>傍晚过渡</t>
+        </is>
+      </c>
+      <c r="F10" s="177" t="inlineStr">
+        <is>
+          <t>晚饭前回落</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="177" t="inlineStr">
+        <is>
+          <t>17:37-18:03</t>
+        </is>
+      </c>
+      <c r="B11" s="177" t="n">
+        <v>26</v>
+      </c>
+      <c r="C11" s="177" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D11" s="177" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="E11" s="177" t="inlineStr">
+        <is>
+          <t>晚高峰前</t>
+        </is>
+      </c>
+      <c r="F11" s="177" t="inlineStr">
+        <is>
+          <t>逐步回升</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="177" t="inlineStr">
+        <is>
+          <t>18:03-20:02</t>
+        </is>
+      </c>
+      <c r="B12" s="177" t="n">
+        <v>119</v>
+      </c>
+      <c r="C12" s="177" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="D12" s="177" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="E12" s="177" t="inlineStr">
+        <is>
+          <t>晚间平稳</t>
+        </is>
+      </c>
+      <c r="F12" s="177" t="inlineStr">
+        <is>
+          <t>持续稳定增长</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="177" t="inlineStr">
+        <is>
+          <t>20:02-21:52</t>
+        </is>
+      </c>
+      <c r="B13" s="177" t="n">
         <v>110</v>
       </c>
-      <c r="C8" s="153" t="n">
-        <v>103.9</v>
-      </c>
-      <c r="D8" s="153" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="E8" s="131" t="inlineStr">
-        <is>
-          <t>下班回升</t>
-        </is>
-      </c>
-      <c r="F8" s="133" t="inlineStr">
-        <is>
-          <t>通勤时段恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" s="69">
-      <c r="A9" s="127" t="inlineStr">
-        <is>
-          <t>16:53-17:37</t>
-        </is>
-      </c>
-      <c r="B9" s="127" t="n">
-        <v>44</v>
-      </c>
-      <c r="C9" s="129" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="D9" s="129" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="E9" s="127" t="inlineStr">
-        <is>
-          <t>晚间增长</t>
-        </is>
-      </c>
-      <c r="F9" s="130" t="inlineStr">
-        <is>
-          <t>晚饭后购票增加</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" s="69">
-      <c r="A10" s="131" t="inlineStr">
-        <is>
-          <t>17:37-18:03</t>
-        </is>
-      </c>
-      <c r="B10" s="131" t="n">
-        <v>26</v>
-      </c>
-      <c r="C10" s="153" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="D10" s="153" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="E10" s="131" t="inlineStr">
-        <is>
-          <t>晚高峰</t>
-        </is>
-      </c>
-      <c r="F10" s="133" t="inlineStr">
-        <is>
-          <t>20点左右持续走高</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" s="69">
-      <c r="A13" s="154" t="inlineStr">
-        <is>
-          <t>排除首波后均值</t>
-        </is>
-      </c>
-      <c r="B13" s="156" t="n"/>
-      <c r="C13" s="156" t="n"/>
-      <c r="D13" s="169" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="E13" s="154" t="inlineStr">
-        <is>
-          <t>5组稳态均值58.2万/h</t>
-        </is>
-      </c>
-      <c r="F13" s="156" t="inlineStr">
-        <is>
-          <t>用于预测的基准增速</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" s="69">
-      <c r="A15" s="152" t="inlineStr">
-        <is>
-          <t>二、修正预测模型参数</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1" s="69">
-      <c r="A16" s="126" t="inlineStr">
+      <c r="C13" s="177" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="D13" s="177" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="E13" s="177" t="inlineStr">
+        <is>
+          <t>晚间回落</t>
+        </is>
+      </c>
+      <c r="F13" s="177" t="inlineStr">
+        <is>
+          <t>增速逐步下降</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="177" t="inlineStr">
+        <is>
+          <t>21:52-22:02</t>
+        </is>
+      </c>
+      <c r="B14" s="177" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="177" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D14" s="177" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E14" s="177" t="inlineStr">
+        <is>
+          <t>深夜前低谷</t>
+        </is>
+      </c>
+      <c r="F14" s="177" t="inlineStr">
+        <is>
+          <t>晚间最低速</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="177" t="inlineStr">
+        <is>
+          <t>22:02-22:30</t>
+        </is>
+      </c>
+      <c r="B15" s="177" t="n">
+        <v>28</v>
+      </c>
+      <c r="C15" s="177" t="n">
+        <v>23</v>
+      </c>
+      <c r="D15" s="177" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="E15" s="177" t="inlineStr">
+        <is>
+          <t>夜间回升</t>
+        </is>
+      </c>
+      <c r="F15" s="177" t="inlineStr">
+        <is>
+          <t>22点后小幅反弹</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="180" t="inlineStr">
+        <is>
+          <t>22:30-22:50</t>
+        </is>
+      </c>
+      <c r="B16" s="180" t="n">
+        <v>20</v>
+      </c>
+      <c r="C16" s="180" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D16" s="180" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="E16" s="180" t="inlineStr">
+        <is>
+          <t>夜间脉冲</t>
+        </is>
+      </c>
+      <c r="F16" s="180" t="inlineStr">
+        <is>
+          <t>疑似集中下单(异常高)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="177" t="inlineStr">
+        <is>
+          <t>22:50-23:01</t>
+        </is>
+      </c>
+      <c r="B17" s="177" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" s="177" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D17" s="177" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="E17" s="177" t="inlineStr">
+        <is>
+          <t>深夜收尾</t>
+        </is>
+      </c>
+      <c r="F17" s="177" t="inlineStr">
+        <is>
+          <t>脉冲后回落</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="187" t="inlineStr">
+        <is>
+          <t>排除首波+脉冲后均值</t>
+        </is>
+      </c>
+      <c r="B18" s="187" t="inlineStr">
+        <is>
+          <t>8组稳态均值</t>
+        </is>
+      </c>
+      <c r="C18" s="188" t="n"/>
+      <c r="D18" s="187" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="E18" s="187" t="inlineStr">
+        <is>
+          <t>晚间均值42.0万/h | 白天均值45.5万/h</t>
+        </is>
+      </c>
+      <c r="F18" s="188" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="69">
+      <c r="A20" s="181" t="inlineStr">
+        <is>
+          <t>二、V3模型参数（基于14组实测数据修正）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="186" t="inlineStr">
         <is>
           <t>参数</t>
         </is>
       </c>
-      <c r="B16" s="126" t="inlineStr">
-        <is>
-          <t>旧模型值</t>
-        </is>
-      </c>
-      <c r="C16" s="126" t="inlineStr">
-        <is>
-          <t>修正值</t>
-        </is>
-      </c>
-      <c r="D16" s="126" t="inlineStr">
+      <c r="B21" s="186" t="inlineStr">
+        <is>
+          <t>V2旧值</t>
+        </is>
+      </c>
+      <c r="C21" s="186" t="inlineStr">
+        <is>
+          <t>V3修正值</t>
+        </is>
+      </c>
+      <c r="D21" s="186" t="inlineStr">
         <is>
           <t>修正依据</t>
-        </is>
-      </c>
-      <c r="E16" s="126" t="inlineStr"/>
-      <c r="F16" s="126" t="inlineStr"/>
-    </row>
-    <row r="17" ht="22" customHeight="1" s="69">
-      <c r="A17" s="170" t="inlineStr">
-        <is>
-          <t>基准增速(万/h)</t>
-        </is>
-      </c>
-      <c r="B17" s="171" t="n">
-        <v>45</v>
-      </c>
-      <c r="C17" s="171" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="D17" s="130" t="inlineStr">
-        <is>
-          <t>排除首波后5组实测均值</t>
-        </is>
-      </c>
-      <c r="E17" s="150" t="n"/>
-      <c r="F17" s="151" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1" s="69">
-      <c r="A18" s="172" t="inlineStr">
-        <is>
-          <t>晚高峰系数(19-23时)</t>
-        </is>
-      </c>
-      <c r="B18" s="173" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C18" s="173" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="133" t="inlineStr">
-        <is>
-          <t>实测19-20点≈40万/h，接近均值</t>
-        </is>
-      </c>
-      <c r="E18" s="150" t="n"/>
-      <c r="F18" s="151" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1" s="69">
-      <c r="A19" s="170" t="inlineStr">
-        <is>
-          <t>深夜系数(23-01时)</t>
-        </is>
-      </c>
-      <c r="B19" s="171" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="171" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D19" s="130" t="inlineStr">
-        <is>
-          <t>23点后逐步回落</t>
-        </is>
-      </c>
-      <c r="E19" s="150" t="n"/>
-      <c r="F19" s="151" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1" s="69">
-      <c r="A20" s="172" t="inlineStr">
-        <is>
-          <t>凌晨系数(01-06时)</t>
-        </is>
-      </c>
-      <c r="B20" s="173" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C20" s="173" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D20" s="133" t="inlineStr">
-        <is>
-          <t>购票几乎停滞</t>
-        </is>
-      </c>
-      <c r="E20" s="150" t="n"/>
-      <c r="F20" s="151" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1" s="69">
-      <c r="A21" s="170" t="inlineStr">
-        <is>
-          <t>早晨系数(06-10时)</t>
-        </is>
-      </c>
-      <c r="B21" s="171" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C21" s="171" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D21" s="130" t="inlineStr">
-        <is>
-          <t>少量恢复</t>
         </is>
       </c>
       <c r="E21" s="150" t="n"/>
       <c r="F21" s="151" t="n"/>
     </row>
-    <row r="22" ht="22" customHeight="1" s="69">
-      <c r="A22" s="172" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="187" t="inlineStr">
+        <is>
+          <t>基准增速(万/h)</t>
+        </is>
+      </c>
+      <c r="B22" s="187" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="C22" s="187" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D22" s="189" t="inlineStr">
+        <is>
+          <t>8组稳态实测均值(排除首波3组+脉冲1组)，较V2大幅下调</t>
+        </is>
+      </c>
+      <c r="E22" s="188" t="n"/>
+      <c r="F22" s="188" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="187" t="inlineStr">
+        <is>
+          <t>晚间系数(18-23时)</t>
+        </is>
+      </c>
+      <c r="B23" s="187" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="187" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D23" s="189" t="inlineStr">
+        <is>
+          <t>晚间均值42.0/基准43.3，晚间略低于白天</t>
+        </is>
+      </c>
+      <c r="E23" s="188" t="n"/>
+      <c r="F23" s="188" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="187" t="inlineStr">
+        <is>
+          <t>深夜系数(23-01时)</t>
+        </is>
+      </c>
+      <c r="B24" s="187" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C24" s="187" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D24" s="189" t="inlineStr">
+        <is>
+          <t>23点后增速明显回落，参照21:52-22:02的29.4万/h</t>
+        </is>
+      </c>
+      <c r="E24" s="188" t="n"/>
+      <c r="F24" s="188" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="187" t="inlineStr">
+        <is>
+          <t>凌晨系数(01-06时)</t>
+        </is>
+      </c>
+      <c r="B25" s="187" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C25" s="187" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D25" s="189" t="inlineStr">
+        <is>
+          <t>深夜购票几乎停滞</t>
+        </is>
+      </c>
+      <c r="E25" s="188" t="n"/>
+      <c r="F25" s="188" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="187" t="inlineStr">
+        <is>
+          <t>早晨系数(06-10时)</t>
+        </is>
+      </c>
+      <c r="B26" s="187" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C26" s="187" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D26" s="189" t="inlineStr">
+        <is>
+          <t>少量恢复</t>
+        </is>
+      </c>
+      <c r="E26" s="188" t="n"/>
+      <c r="F26" s="188" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="187" t="inlineStr">
         <is>
           <t>上午系数(10-12时)</t>
         </is>
       </c>
-      <c r="B22" s="173" t="n">
+      <c r="B27" s="187" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C27" s="187" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D27" s="189" t="inlineStr">
+        <is>
+          <t>平稳低速</t>
+        </is>
+      </c>
+      <c r="E27" s="188" t="n"/>
+      <c r="F27" s="188" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="187" t="inlineStr">
+        <is>
+          <t>午间系数(12-14时)</t>
+        </is>
+      </c>
+      <c r="B28" s="187" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C28" s="187" t="n">
         <v>0.55</v>
       </c>
-      <c r="C22" s="173" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D22" s="133" t="inlineStr">
-        <is>
-          <t>平稳低速</t>
-        </is>
-      </c>
-      <c r="E22" s="150" t="n"/>
-      <c r="F22" s="151" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1" s="69">
-      <c r="A23" s="170" t="inlineStr">
-        <is>
-          <t>午间系数(12-14时)</t>
-        </is>
-      </c>
-      <c r="B23" s="171" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C23" s="171" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D23" s="130" t="inlineStr">
+      <c r="D28" s="189" t="inlineStr">
         <is>
           <t>午间小幅回升</t>
         </is>
       </c>
-      <c r="E23" s="150" t="n"/>
-      <c r="F23" s="151" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1" s="69">
-      <c r="A24" s="172" t="inlineStr">
-        <is>
-          <t>下午系数(14-19时)</t>
-        </is>
-      </c>
-      <c r="B24" s="173" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="C24" s="173" t="n">
+      <c r="E28" s="188" t="n"/>
+      <c r="F28" s="188" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="187" t="inlineStr">
+        <is>
+          <t>下午系数(14-18时)</t>
+        </is>
+      </c>
+      <c r="B29" s="187" t="n">
         <v>0.75</v>
       </c>
-      <c r="D24" s="133" t="inlineStr">
-        <is>
-          <t>下午增速回升</t>
-        </is>
-      </c>
-      <c r="E24" s="150" t="n"/>
-      <c r="F24" s="151" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1" s="69">
-      <c r="A25" s="170" t="inlineStr">
-        <is>
-          <t>映前4天日期系数</t>
-        </is>
-      </c>
-      <c r="B25" s="171" t="n">
+      <c r="C29" s="187" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D29" s="189" t="inlineStr">
+        <is>
+          <t>下午增速回升，保持不变</t>
+        </is>
+      </c>
+      <c r="E29" s="188" t="n"/>
+      <c r="F29" s="188" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="187" t="inlineStr">
+        <is>
+          <t>映前5天日期系数(8/6)</t>
+        </is>
+      </c>
+      <c r="B30" s="187" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C30" s="187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="189" t="inlineStr">
+        <is>
+          <t>作为基准日=1.0，其他日期相对调整</t>
+        </is>
+      </c>
+      <c r="E30" s="188" t="n"/>
+      <c r="F30" s="188" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="187" t="inlineStr">
+        <is>
+          <t>映前4天日期系数(8/7)</t>
+        </is>
+      </c>
+      <c r="B31" s="187" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C31" s="187" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D31" s="189" t="inlineStr">
+        <is>
+          <t>宣发发酵，但想看基数低(2.5万)，适度上调</t>
+        </is>
+      </c>
+      <c r="E31" s="188" t="n"/>
+      <c r="F31" s="188" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="187" t="inlineStr">
+        <is>
+          <t>映前3天日期系数(8/8)</t>
+        </is>
+      </c>
+      <c r="B32" s="187" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C32" s="187" t="n">
         <v>1.35</v>
       </c>
-      <c r="C25" s="171" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D25" s="130" t="inlineStr">
-        <is>
-          <t>8/7宣发发酵，但想看基数低</t>
-        </is>
-      </c>
-      <c r="E25" s="150" t="n"/>
-      <c r="F25" s="151" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1" s="69">
-      <c r="A26" s="172" t="inlineStr">
-        <is>
-          <t>映前3天日期系数</t>
-        </is>
-      </c>
-      <c r="B26" s="173" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C26" s="173" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D26" s="133" t="inlineStr">
-        <is>
-          <t>8/8点映前半天，预期温和增长</t>
-        </is>
-      </c>
-      <c r="E26" s="150" t="n"/>
-      <c r="F26" s="151" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1" s="69">
-      <c r="A27" s="170" t="inlineStr">
-        <is>
-          <t>点映开始后系数</t>
-        </is>
-      </c>
-      <c r="B27" s="171" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C27" s="171" t="n">
+      <c r="D32" s="189" t="inlineStr">
+        <is>
+          <t>点映前半天，预期温和增长</t>
+        </is>
+      </c>
+      <c r="E32" s="188" t="n"/>
+      <c r="F32" s="188" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="187" t="inlineStr">
+        <is>
+          <t>点映系数(8/8 14:00+)</t>
+        </is>
+      </c>
+      <c r="B33" s="187" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="130" t="inlineStr">
-        <is>
-          <t>8/8 14:00点映，票房计入</t>
-        </is>
-      </c>
-      <c r="E27" s="150" t="n"/>
-      <c r="F27" s="151" t="n"/>
-    </row>
-    <row r="29" ht="24" customHeight="1" s="69">
-      <c r="A29" s="152" t="inlineStr">
-        <is>
-          <t>三、逐小时预测（8月6日21:00 - 8月8日14:00点映开始）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1" s="69">
-      <c r="A30" s="126" t="inlineStr">
+      <c r="C33" s="187" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D33" s="189" t="inlineStr">
+        <is>
+          <t>点映票房计入，但想看基数偏低</t>
+        </is>
+      </c>
+      <c r="E33" s="188" t="n"/>
+      <c r="F33" s="188" t="n"/>
+    </row>
+    <row r="35" ht="24" customHeight="1" s="69">
+      <c r="A35" s="181" t="inlineStr">
+        <is>
+          <t>三、逐小时预测（8月6日23:00 - 8月8日14:00点映开始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="186" t="inlineStr">
         <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B30" s="126" t="inlineStr">
+      <c r="B36" s="186" t="inlineStr">
         <is>
           <t>星期</t>
         </is>
       </c>
-      <c r="C30" s="126" t="inlineStr">
+      <c r="C36" s="186" t="inlineStr">
         <is>
           <t>预测增速(万/h)</t>
         </is>
       </c>
-      <c r="D30" s="126" t="inlineStr">
+      <c r="D36" s="186" t="inlineStr">
         <is>
           <t>预测累计(万)</t>
         </is>
       </c>
-      <c r="E30" s="126" t="inlineStr">
+      <c r="E36" s="186" t="inlineStr">
         <is>
           <t>时段说明</t>
         </is>
       </c>
-      <c r="F30" s="126" t="inlineStr">
+      <c r="F36" s="186" t="inlineStr">
         <is>
           <t>置信度</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1" s="69">
-      <c r="A31" s="127" t="inlineStr">
-        <is>
-          <t>08-06 21:00</t>
-        </is>
-      </c>
-      <c r="B31" s="127" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="190" t="inlineStr">
+        <is>
+          <t>08-06 23:00</t>
+        </is>
+      </c>
+      <c r="B37" s="190" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="C31" s="129" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="D31" s="129" t="n">
-        <v>480.8</v>
-      </c>
-      <c r="E31" s="130" t="inlineStr">
-        <is>
-          <t>晚间回落</t>
-        </is>
-      </c>
-      <c r="F31" s="127" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1" s="69">
-      <c r="A32" s="131" t="inlineStr">
-        <is>
-          <t>08-06 22:00</t>
-        </is>
-      </c>
-      <c r="B32" s="131" t="inlineStr">
-        <is>
-          <t>周四</t>
-        </is>
-      </c>
-      <c r="C32" s="153" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="D32" s="153" t="n">
-        <v>527.3</v>
-      </c>
-      <c r="E32" s="133" t="inlineStr">
-        <is>
-          <t>晚间回落</t>
-        </is>
-      </c>
-      <c r="F32" s="131" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1" s="69">
-      <c r="A33" s="127" t="inlineStr">
-        <is>
-          <t>08-06 23:00</t>
-        </is>
-      </c>
-      <c r="B33" s="127" t="inlineStr">
-        <is>
-          <t>周四</t>
-        </is>
-      </c>
-      <c r="C33" s="129" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="D33" s="129" t="n">
+      <c r="C37" s="190" t="inlineStr">
+        <is>
+          <t>—（实际值）</t>
+        </is>
+      </c>
+      <c r="D37" s="190" t="n">
+        <v>565.5</v>
+      </c>
+      <c r="E37" s="190" t="inlineStr">
+        <is>
+          <t>映前5天·实测基准</t>
+        </is>
+      </c>
+      <c r="F37" s="190" t="inlineStr">
+        <is>
+          <t>实际</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="177" t="inlineStr">
+        <is>
+          <t>08-07 00:00</t>
+        </is>
+      </c>
+      <c r="B38" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C38" s="177" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="D38" s="177" t="n">
+        <v>589.3</v>
+      </c>
+      <c r="E38" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·深夜回落</t>
+        </is>
+      </c>
+      <c r="F38" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="177" t="inlineStr">
+        <is>
+          <t>08-07 01:00</t>
+        </is>
+      </c>
+      <c r="B39" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C39" s="177" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="D39" s="177" t="n">
+        <v>616.7</v>
+      </c>
+      <c r="E39" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·凌晨低谷</t>
+        </is>
+      </c>
+      <c r="F39" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="177" t="inlineStr">
+        <is>
+          <t>08-07 02:00</t>
+        </is>
+      </c>
+      <c r="B40" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C40" s="177" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" s="177" t="n">
+        <v>621.7</v>
+      </c>
+      <c r="E40" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·凌晨低谷</t>
+        </is>
+      </c>
+      <c r="F40" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="177" t="inlineStr">
+        <is>
+          <t>08-07 03:00</t>
+        </is>
+      </c>
+      <c r="B41" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C41" s="177" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" s="177" t="n">
+        <v>626.7</v>
+      </c>
+      <c r="E41" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·凌晨低谷</t>
+        </is>
+      </c>
+      <c r="F41" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="177" t="inlineStr">
+        <is>
+          <t>08-07 04:00</t>
+        </is>
+      </c>
+      <c r="B42" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C42" s="177" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" s="177" t="n">
+        <v>631.6</v>
+      </c>
+      <c r="E42" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·凌晨低谷</t>
+        </is>
+      </c>
+      <c r="F42" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="177" t="inlineStr">
+        <is>
+          <t>08-07 05:00</t>
+        </is>
+      </c>
+      <c r="B43" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C43" s="177" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" s="177" t="n">
+        <v>636.6</v>
+      </c>
+      <c r="E43" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·凌晨低谷</t>
+        </is>
+      </c>
+      <c r="F43" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="177" t="inlineStr">
+        <is>
+          <t>08-07 06:00</t>
+        </is>
+      </c>
+      <c r="B44" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C44" s="177" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" s="177" t="n">
+        <v>641.6</v>
+      </c>
+      <c r="E44" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·早晨恢复</t>
+        </is>
+      </c>
+      <c r="F44" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="177" t="inlineStr">
+        <is>
+          <t>08-07 07:00</t>
+        </is>
+      </c>
+      <c r="B45" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C45" s="177" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D45" s="177" t="n">
+        <v>654</v>
+      </c>
+      <c r="E45" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·早晨恢复</t>
+        </is>
+      </c>
+      <c r="F45" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="177" t="inlineStr">
+        <is>
+          <t>08-07 08:00</t>
+        </is>
+      </c>
+      <c r="B46" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C46" s="177" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D46" s="177" t="n">
+        <v>666.5</v>
+      </c>
+      <c r="E46" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·早晨恢复</t>
+        </is>
+      </c>
+      <c r="F46" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="177" t="inlineStr">
+        <is>
+          <t>08-07 09:00</t>
+        </is>
+      </c>
+      <c r="B47" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C47" s="177" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D47" s="177" t="n">
+        <v>678.9</v>
+      </c>
+      <c r="E47" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·早晨恢复</t>
+        </is>
+      </c>
+      <c r="F47" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="177" t="inlineStr">
+        <is>
+          <t>08-07 10:00</t>
+        </is>
+      </c>
+      <c r="B48" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C48" s="177" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D48" s="177" t="n">
+        <v>691.4</v>
+      </c>
+      <c r="E48" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·上午平稳</t>
+        </is>
+      </c>
+      <c r="F48" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="177" t="inlineStr">
+        <is>
+          <t>08-07 11:00</t>
+        </is>
+      </c>
+      <c r="B49" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C49" s="177" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D49" s="177" t="n">
+        <v>713.8</v>
+      </c>
+      <c r="E49" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·上午平稳</t>
+        </is>
+      </c>
+      <c r="F49" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="177" t="inlineStr">
+        <is>
+          <t>08-07 12:00</t>
+        </is>
+      </c>
+      <c r="B50" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C50" s="177" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D50" s="177" t="n">
+        <v>736.2</v>
+      </c>
+      <c r="E50" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·午间小高峰</t>
+        </is>
+      </c>
+      <c r="F50" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="177" t="inlineStr">
+        <is>
+          <t>08-07 13:00</t>
+        </is>
+      </c>
+      <c r="B51" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C51" s="177" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="D51" s="177" t="n">
+        <v>763.6</v>
+      </c>
+      <c r="E51" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·午间小高峰</t>
+        </is>
+      </c>
+      <c r="F51" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="177" t="inlineStr">
+        <is>
+          <t>08-07 14:00</t>
+        </is>
+      </c>
+      <c r="B52" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C52" s="177" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="D52" s="177" t="n">
+        <v>791</v>
+      </c>
+      <c r="E52" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·下午增长</t>
+        </is>
+      </c>
+      <c r="F52" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="177" t="inlineStr">
+        <is>
+          <t>08-07 15:00</t>
+        </is>
+      </c>
+      <c r="B53" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C53" s="177" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D53" s="177" t="n">
+        <v>828.3</v>
+      </c>
+      <c r="E53" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·下午增长</t>
+        </is>
+      </c>
+      <c r="F53" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="177" t="inlineStr">
+        <is>
+          <t>08-07 16:00</t>
+        </is>
+      </c>
+      <c r="B54" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C54" s="177" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D54" s="177" t="n">
+        <v>865.7</v>
+      </c>
+      <c r="E54" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·下午增长</t>
+        </is>
+      </c>
+      <c r="F54" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="177" t="inlineStr">
+        <is>
+          <t>08-07 17:00</t>
+        </is>
+      </c>
+      <c r="B55" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C55" s="177" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D55" s="177" t="n">
+        <v>903</v>
+      </c>
+      <c r="E55" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·下午增长</t>
+        </is>
+      </c>
+      <c r="F55" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="177" t="inlineStr">
+        <is>
+          <t>08-07 18:00</t>
+        </is>
+      </c>
+      <c r="B56" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C56" s="177" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D56" s="177" t="n">
+        <v>940.4</v>
+      </c>
+      <c r="E56" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·晚间增长</t>
+        </is>
+      </c>
+      <c r="F56" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="177" t="inlineStr">
+        <is>
+          <t>08-07 19:00</t>
+        </is>
+      </c>
+      <c r="B57" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C57" s="177" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="D57" s="177" t="n">
+        <v>988.7</v>
+      </c>
+      <c r="E57" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·晚间增长</t>
+        </is>
+      </c>
+      <c r="F57" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="177" t="inlineStr">
+        <is>
+          <t>08-07 20:00</t>
+        </is>
+      </c>
+      <c r="B58" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C58" s="177" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="D58" s="177" t="n">
+        <v>1037</v>
+      </c>
+      <c r="E58" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·晚间增长</t>
+        </is>
+      </c>
+      <c r="F58" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="177" t="inlineStr">
+        <is>
+          <t>08-07 21:00</t>
+        </is>
+      </c>
+      <c r="B59" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C59" s="177" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="D59" s="177" t="n">
+        <v>1085.3</v>
+      </c>
+      <c r="E59" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·晚间增长</t>
+        </is>
+      </c>
+      <c r="F59" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="177" t="inlineStr">
+        <is>
+          <t>08-07 22:00</t>
+        </is>
+      </c>
+      <c r="B60" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C60" s="177" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="D60" s="177" t="n">
+        <v>1133.6</v>
+      </c>
+      <c r="E60" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·晚间增长</t>
+        </is>
+      </c>
+      <c r="F60" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="177" t="inlineStr">
+        <is>
+          <t>08-07 23:00</t>
+        </is>
+      </c>
+      <c r="B61" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C61" s="177" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="D61" s="177" t="n">
+        <v>1181.9</v>
+      </c>
+      <c r="E61" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·深夜回落</t>
+        </is>
+      </c>
+      <c r="F61" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="177" t="inlineStr">
+        <is>
+          <t>08-08 00:00</t>
+        </is>
+      </c>
+      <c r="B62" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C62" s="177" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="D62" s="177" t="n">
+        <v>1209.3</v>
+      </c>
+      <c r="E62" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·深夜回落</t>
+        </is>
+      </c>
+      <c r="F62" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="177" t="inlineStr">
+        <is>
+          <t>08-08 01:00</t>
+        </is>
+      </c>
+      <c r="B63" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C63" s="177" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="D63" s="177" t="n">
+        <v>1241.4</v>
+      </c>
+      <c r="E63" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·凌晨低谷</t>
+        </is>
+      </c>
+      <c r="F63" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="177" t="inlineStr">
+        <is>
+          <t>08-08 02:00</t>
+        </is>
+      </c>
+      <c r="B64" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C64" s="177" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D64" s="177" t="n">
+        <v>1247.3</v>
+      </c>
+      <c r="E64" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·凌晨低谷</t>
+        </is>
+      </c>
+      <c r="F64" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="177" t="inlineStr">
+        <is>
+          <t>08-08 03:00</t>
+        </is>
+      </c>
+      <c r="B65" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C65" s="177" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D65" s="177" t="n">
+        <v>1253.1</v>
+      </c>
+      <c r="E65" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·凌晨低谷</t>
+        </is>
+      </c>
+      <c r="F65" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="177" t="inlineStr">
+        <is>
+          <t>08-08 04:00</t>
+        </is>
+      </c>
+      <c r="B66" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C66" s="177" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D66" s="177" t="n">
+        <v>1258.9</v>
+      </c>
+      <c r="E66" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·凌晨低谷</t>
+        </is>
+      </c>
+      <c r="F66" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="177" t="inlineStr">
+        <is>
+          <t>08-08 05:00</t>
+        </is>
+      </c>
+      <c r="B67" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C67" s="177" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D67" s="177" t="n">
+        <v>1264.8</v>
+      </c>
+      <c r="E67" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·凌晨低谷</t>
+        </is>
+      </c>
+      <c r="F67" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="177" t="inlineStr">
+        <is>
+          <t>08-08 06:00</t>
+        </is>
+      </c>
+      <c r="B68" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C68" s="177" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D68" s="177" t="n">
+        <v>1270.6</v>
+      </c>
+      <c r="E68" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·早晨恢复</t>
+        </is>
+      </c>
+      <c r="F68" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="177" t="inlineStr">
+        <is>
+          <t>08-08 07:00</t>
+        </is>
+      </c>
+      <c r="B69" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C69" s="177" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D69" s="177" t="n">
+        <v>1285.3</v>
+      </c>
+      <c r="E69" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·早晨恢复</t>
+        </is>
+      </c>
+      <c r="F69" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="177" t="inlineStr">
+        <is>
+          <t>08-08 08:00</t>
+        </is>
+      </c>
+      <c r="B70" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C70" s="177" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D70" s="177" t="n">
+        <v>1299.9</v>
+      </c>
+      <c r="E70" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·早晨恢复</t>
+        </is>
+      </c>
+      <c r="F70" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="177" t="inlineStr">
+        <is>
+          <t>08-08 09:00</t>
+        </is>
+      </c>
+      <c r="B71" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C71" s="177" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D71" s="177" t="n">
+        <v>1314.5</v>
+      </c>
+      <c r="E71" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·早晨恢复</t>
+        </is>
+      </c>
+      <c r="F71" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="177" t="inlineStr">
+        <is>
+          <t>08-08 10:00</t>
+        </is>
+      </c>
+      <c r="B72" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C72" s="177" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D72" s="177" t="n">
+        <v>1329.1</v>
+      </c>
+      <c r="E72" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·上午平稳</t>
+        </is>
+      </c>
+      <c r="F72" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="177" t="inlineStr">
+        <is>
+          <t>08-08 11:00</t>
+        </is>
+      </c>
+      <c r="B73" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C73" s="177" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D73" s="177" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="E73" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·上午平稳</t>
+        </is>
+      </c>
+      <c r="F73" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="177" t="inlineStr">
+        <is>
+          <t>08-08 12:00</t>
+        </is>
+      </c>
+      <c r="B74" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C74" s="177" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D74" s="177" t="n">
+        <v>1381.7</v>
+      </c>
+      <c r="E74" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·午间小高峰</t>
+        </is>
+      </c>
+      <c r="F74" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="177" t="inlineStr">
+        <is>
+          <t>08-08 13:00</t>
+        </is>
+      </c>
+      <c r="B75" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C75" s="177" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="D75" s="177" t="n">
+        <v>1413.9</v>
+      </c>
+      <c r="E75" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·午间小高峰</t>
+        </is>
+      </c>
+      <c r="F75" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="180" t="inlineStr">
+        <is>
+          <t>08-08 14:00</t>
+        </is>
+      </c>
+      <c r="B76" s="180" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C76" s="180" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="D76" s="180" t="n">
+        <v>1446</v>
+      </c>
+      <c r="E76" s="180" t="inlineStr">
+        <is>
+          <t>点映开始·点映开始!!</t>
+        </is>
+      </c>
+      <c r="F76" s="180" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="24" customHeight="1" s="69">
+      <c r="A78" s="181" t="inlineStr">
+        <is>
+          <t>四、关键节点预测对比（V2 vs V3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="186" t="inlineStr">
+        <is>
+          <t>关键节点</t>
+        </is>
+      </c>
+      <c r="B79" s="186" t="inlineStr">
+        <is>
+          <t>V2预测(万)</t>
+        </is>
+      </c>
+      <c r="C79" s="186" t="inlineStr">
+        <is>
+          <t>V3预测(万)</t>
+        </is>
+      </c>
+      <c r="D79" s="186" t="inlineStr">
+        <is>
+          <t>偏差(万)</t>
+        </is>
+      </c>
+      <c r="E79" s="186" t="inlineStr">
+        <is>
+          <t>偏差率</t>
+        </is>
+      </c>
+      <c r="F79" s="186" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="177" t="inlineStr">
+        <is>
+          <t>8/6 23:00 深夜收尾</t>
+        </is>
+      </c>
+      <c r="B80" s="177" t="n">
         <v>573.9</v>
       </c>
-      <c r="E33" s="130" t="inlineStr">
-        <is>
-          <t>晚间回落</t>
-        </is>
-      </c>
-      <c r="F33" s="127" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1" s="69">
-      <c r="A34" s="131" t="inlineStr">
-        <is>
-          <t>08-07 00:00</t>
-        </is>
-      </c>
-      <c r="B34" s="131" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C34" s="153" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="D34" s="153" t="n">
-        <v>622.8</v>
-      </c>
-      <c r="E34" s="133" t="inlineStr">
-        <is>
-          <t>深夜回落</t>
-        </is>
-      </c>
-      <c r="F34" s="131" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1" s="69">
-      <c r="A35" s="158" t="inlineStr">
-        <is>
-          <t>08-07 01:00</t>
-        </is>
-      </c>
-      <c r="B35" s="158" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C35" s="160" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D35" s="160" t="n">
-        <v>631.1</v>
-      </c>
-      <c r="E35" s="161" t="inlineStr">
-        <is>
-          <t>凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F35" s="158" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1" s="69">
-      <c r="A36" s="158" t="inlineStr">
-        <is>
-          <t>08-07 02:00</t>
-        </is>
-      </c>
-      <c r="B36" s="158" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C36" s="160" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D36" s="160" t="n">
-        <v>639.5</v>
-      </c>
-      <c r="E36" s="161" t="inlineStr">
-        <is>
-          <t>凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F36" s="158" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1" s="69">
-      <c r="A37" s="158" t="inlineStr">
-        <is>
-          <t>08-07 03:00</t>
-        </is>
-      </c>
-      <c r="B37" s="158" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C37" s="160" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D37" s="160" t="n">
-        <v>647.9</v>
-      </c>
-      <c r="E37" s="161" t="inlineStr">
-        <is>
-          <t>凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F37" s="158" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1" s="69">
-      <c r="A38" s="158" t="inlineStr">
-        <is>
-          <t>08-07 04:00</t>
-        </is>
-      </c>
-      <c r="B38" s="158" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C38" s="160" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D38" s="160" t="n">
-        <v>656.3</v>
-      </c>
-      <c r="E38" s="161" t="inlineStr">
-        <is>
-          <t>凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F38" s="158" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1" s="69">
-      <c r="A39" s="158" t="inlineStr">
-        <is>
-          <t>08-07 05:00</t>
-        </is>
-      </c>
-      <c r="B39" s="158" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C39" s="160" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D39" s="160" t="n">
-        <v>664.7</v>
-      </c>
-      <c r="E39" s="161" t="inlineStr">
-        <is>
-          <t>凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F39" s="158" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1" s="69">
-      <c r="A40" s="131" t="inlineStr">
-        <is>
-          <t>08-07 06:00</t>
-        </is>
-      </c>
-      <c r="B40" s="131" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C40" s="153" t="n">
-        <v>21</v>
-      </c>
-      <c r="D40" s="153" t="n">
-        <v>685.6</v>
-      </c>
-      <c r="E40" s="133" t="inlineStr">
-        <is>
-          <t>早晨恢复</t>
-        </is>
-      </c>
-      <c r="F40" s="131" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1" s="69">
-      <c r="A41" s="127" t="inlineStr">
-        <is>
-          <t>08-07 07:00</t>
-        </is>
-      </c>
-      <c r="B41" s="127" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C41" s="129" t="n">
-        <v>21</v>
-      </c>
-      <c r="D41" s="129" t="n">
-        <v>706.6</v>
-      </c>
-      <c r="E41" s="130" t="inlineStr">
-        <is>
-          <t>早晨恢复</t>
-        </is>
-      </c>
-      <c r="F41" s="127" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1" s="69">
-      <c r="A42" s="131" t="inlineStr">
-        <is>
-          <t>08-07 08:00</t>
-        </is>
-      </c>
-      <c r="B42" s="131" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C42" s="153" t="n">
-        <v>21</v>
-      </c>
-      <c r="D42" s="153" t="n">
+      <c r="C80" s="183" t="n">
+        <v>565.5</v>
+      </c>
+      <c r="D80" s="191" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="E80" s="177" t="inlineStr">
+        <is>
+          <t>-1.5%</t>
+        </is>
+      </c>
+      <c r="F80" s="177" t="inlineStr">
+        <is>
+          <t>实际值565.5万，V3以此为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="177" t="inlineStr">
+        <is>
+          <t>8/7 08:00 映前4天早晨</t>
+        </is>
+      </c>
+      <c r="B81" s="177" t="n">
         <v>727.5</v>
       </c>
-      <c r="E42" s="133" t="inlineStr">
-        <is>
-          <t>早晨恢复</t>
-        </is>
-      </c>
-      <c r="F42" s="131" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1" s="69">
-      <c r="A43" s="127" t="inlineStr">
-        <is>
-          <t>08-07 09:00</t>
-        </is>
-      </c>
-      <c r="B43" s="127" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C43" s="129" t="n">
-        <v>21</v>
-      </c>
-      <c r="D43" s="129" t="n">
-        <v>748.5</v>
-      </c>
-      <c r="E43" s="130" t="inlineStr">
-        <is>
-          <t>早晨恢复</t>
-        </is>
-      </c>
-      <c r="F43" s="127" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1" s="69">
-      <c r="A44" s="131" t="inlineStr">
-        <is>
-          <t>08-07 10:00</t>
-        </is>
-      </c>
-      <c r="B44" s="131" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C44" s="153" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="D44" s="153" t="n">
-        <v>783.4</v>
-      </c>
-      <c r="E44" s="133" t="inlineStr">
-        <is>
-          <t>上午平稳</t>
-        </is>
-      </c>
-      <c r="F44" s="131" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1" s="69">
-      <c r="A45" s="127" t="inlineStr">
-        <is>
-          <t>08-07 11:00</t>
-        </is>
-      </c>
-      <c r="B45" s="127" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C45" s="129" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="D45" s="129" t="n">
-        <v>818.3</v>
-      </c>
-      <c r="E45" s="130" t="inlineStr">
-        <is>
-          <t>上午平稳</t>
-        </is>
-      </c>
-      <c r="F45" s="127" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1" s="69">
-      <c r="A46" s="131" t="inlineStr">
-        <is>
-          <t>08-07 12:00</t>
-        </is>
-      </c>
-      <c r="B46" s="131" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C46" s="153" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="D46" s="153" t="n">
+      <c r="C81" s="183" t="n">
+        <v>666.5</v>
+      </c>
+      <c r="D81" s="191" t="n">
+        <v>-61</v>
+      </c>
+      <c r="E81" s="177" t="inlineStr">
+        <is>
+          <t>-8.4%</t>
+        </is>
+      </c>
+      <c r="F81" s="177" t="inlineStr">
+        <is>
+          <t>V3基准下调，差距开始拉大</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="177" t="inlineStr">
+        <is>
+          <t>8/7 12:00 午间</t>
+        </is>
+      </c>
+      <c r="B82" s="177" t="n">
         <v>863.7</v>
       </c>
-      <c r="E46" s="133" t="inlineStr">
-        <is>
-          <t>午间小高峰</t>
-        </is>
-      </c>
-      <c r="F46" s="131" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1" s="69">
-      <c r="A47" s="127" t="inlineStr">
-        <is>
-          <t>08-07 13:00</t>
-        </is>
-      </c>
-      <c r="B47" s="127" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C47" s="129" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="D47" s="129" t="n">
-        <v>909.1</v>
-      </c>
-      <c r="E47" s="130" t="inlineStr">
-        <is>
-          <t>午间小高峰</t>
-        </is>
-      </c>
-      <c r="F47" s="127" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1" s="69">
-      <c r="A48" s="131" t="inlineStr">
-        <is>
-          <t>08-07 14:00</t>
-        </is>
-      </c>
-      <c r="B48" s="131" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C48" s="153" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="D48" s="153" t="n">
-        <v>961.5</v>
-      </c>
-      <c r="E48" s="133" t="inlineStr">
-        <is>
-          <t>下午增长</t>
-        </is>
-      </c>
-      <c r="F48" s="131" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1" s="69">
-      <c r="A49" s="127" t="inlineStr">
-        <is>
-          <t>08-07 15:00</t>
-        </is>
-      </c>
-      <c r="B49" s="127" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C49" s="129" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="D49" s="129" t="n">
-        <v>1013.9</v>
-      </c>
-      <c r="E49" s="130" t="inlineStr">
-        <is>
-          <t>下午增长</t>
-        </is>
-      </c>
-      <c r="F49" s="127" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1" s="69">
-      <c r="A50" s="131" t="inlineStr">
-        <is>
-          <t>08-07 16:00</t>
-        </is>
-      </c>
-      <c r="B50" s="131" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C50" s="153" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="D50" s="153" t="n">
-        <v>1066.3</v>
-      </c>
-      <c r="E50" s="133" t="inlineStr">
-        <is>
-          <t>下午增长</t>
-        </is>
-      </c>
-      <c r="F50" s="131" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1" s="69">
-      <c r="A51" s="127" t="inlineStr">
-        <is>
-          <t>08-07 17:00</t>
-        </is>
-      </c>
-      <c r="B51" s="127" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C51" s="129" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="D51" s="129" t="n">
-        <v>1118.6</v>
-      </c>
-      <c r="E51" s="130" t="inlineStr">
-        <is>
-          <t>下午增长</t>
-        </is>
-      </c>
-      <c r="F51" s="127" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1" s="69">
-      <c r="A52" s="131" t="inlineStr">
-        <is>
-          <t>08-07 18:00</t>
-        </is>
-      </c>
-      <c r="B52" s="131" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C52" s="153" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="D52" s="153" t="n">
+      <c r="C82" s="183" t="n">
+        <v>736.2</v>
+      </c>
+      <c r="D82" s="191" t="n">
+        <v>-127.5</v>
+      </c>
+      <c r="E82" s="177" t="inlineStr">
+        <is>
+          <t>-14.8%</t>
+        </is>
+      </c>
+      <c r="F82" s="177" t="inlineStr">
+        <is>
+          <t>V3显著低于V2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="177" t="inlineStr">
+        <is>
+          <t>8/7 18:00 晚间高峰</t>
+        </is>
+      </c>
+      <c r="B83" s="177" t="n">
         <v>1171</v>
       </c>
-      <c r="E52" s="133" t="inlineStr">
-        <is>
-          <t>下午增长</t>
-        </is>
-      </c>
-      <c r="F52" s="131" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1" s="69">
-      <c r="A53" s="127" t="inlineStr">
-        <is>
-          <t>08-07 19:00</t>
-        </is>
-      </c>
-      <c r="B53" s="127" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C53" s="129" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="D53" s="129" t="n">
-        <v>1240.9</v>
-      </c>
-      <c r="E53" s="130" t="inlineStr">
-        <is>
-          <t>晚高峰</t>
-        </is>
-      </c>
-      <c r="F53" s="127" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1" s="69">
-      <c r="A54" s="131" t="inlineStr">
-        <is>
-          <t>08-07 20:00</t>
-        </is>
-      </c>
-      <c r="B54" s="131" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C54" s="153" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="D54" s="153" t="n">
-        <v>1310.7</v>
-      </c>
-      <c r="E54" s="133" t="inlineStr">
-        <is>
-          <t>晚高峰</t>
-        </is>
-      </c>
-      <c r="F54" s="131" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1" s="69">
-      <c r="A55" s="127" t="inlineStr">
-        <is>
-          <t>08-07 21:00</t>
-        </is>
-      </c>
-      <c r="B55" s="127" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C55" s="129" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="D55" s="129" t="n">
-        <v>1366.6</v>
-      </c>
-      <c r="E55" s="130" t="inlineStr">
-        <is>
-          <t>晚间回落</t>
-        </is>
-      </c>
-      <c r="F55" s="127" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1" s="69">
-      <c r="A56" s="131" t="inlineStr">
-        <is>
-          <t>08-07 22:00</t>
-        </is>
-      </c>
-      <c r="B56" s="131" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C56" s="153" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="D56" s="153" t="n">
-        <v>1422.4</v>
-      </c>
-      <c r="E56" s="133" t="inlineStr">
-        <is>
-          <t>晚间回落</t>
-        </is>
-      </c>
-      <c r="F56" s="131" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1" s="69">
-      <c r="A57" s="127" t="inlineStr">
-        <is>
-          <t>08-07 23:00</t>
-        </is>
-      </c>
-      <c r="B57" s="127" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C57" s="129" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="D57" s="129" t="n">
+      <c r="C83" s="183" t="n">
+        <v>940.4</v>
+      </c>
+      <c r="D83" s="191" t="n">
+        <v>-230.6</v>
+      </c>
+      <c r="E83" s="177" t="inlineStr">
+        <is>
+          <t>-19.7%</t>
+        </is>
+      </c>
+      <c r="F83" s="177" t="inlineStr">
+        <is>
+          <t>V3差距继续扩大</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="177" t="inlineStr">
+        <is>
+          <t>8/7 23:00 映前4天收尾</t>
+        </is>
+      </c>
+      <c r="B84" s="177" t="n">
         <v>1478.3</v>
       </c>
-      <c r="E57" s="130" t="inlineStr">
-        <is>
-          <t>晚间回落</t>
-        </is>
-      </c>
-      <c r="F57" s="127" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1" s="69">
-      <c r="A58" s="131" t="inlineStr">
-        <is>
-          <t>08-08 00:00</t>
-        </is>
-      </c>
-      <c r="B58" s="131" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C58" s="162" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="D58" s="153" t="n">
-        <v>1539.4</v>
-      </c>
-      <c r="E58" s="133" t="inlineStr">
-        <is>
-          <t>深夜回落</t>
-        </is>
-      </c>
-      <c r="F58" s="131" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1" s="69">
-      <c r="A59" s="158" t="inlineStr">
-        <is>
-          <t>08-08 01:00</t>
-        </is>
-      </c>
-      <c r="B59" s="158" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C59" s="159" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="D59" s="160" t="n">
-        <v>1549.9</v>
-      </c>
-      <c r="E59" s="161" t="inlineStr">
-        <is>
-          <t>凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F59" s="158" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1" s="69">
-      <c r="A60" s="158" t="inlineStr">
-        <is>
-          <t>08-08 02:00</t>
-        </is>
-      </c>
-      <c r="B60" s="158" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C60" s="159" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="D60" s="160" t="n">
-        <v>1560.4</v>
-      </c>
-      <c r="E60" s="161" t="inlineStr">
-        <is>
-          <t>凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F60" s="158" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1" s="69">
-      <c r="A61" s="158" t="inlineStr">
-        <is>
-          <t>08-08 03:00</t>
-        </is>
-      </c>
-      <c r="B61" s="158" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C61" s="159" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="D61" s="160" t="n">
-        <v>1570.8</v>
-      </c>
-      <c r="E61" s="161" t="inlineStr">
-        <is>
-          <t>凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F61" s="158" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1" s="69">
-      <c r="A62" s="158" t="inlineStr">
-        <is>
-          <t>08-08 04:00</t>
-        </is>
-      </c>
-      <c r="B62" s="158" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C62" s="159" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="D62" s="160" t="n">
-        <v>1581.3</v>
-      </c>
-      <c r="E62" s="161" t="inlineStr">
-        <is>
-          <t>凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F62" s="158" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1" s="69">
-      <c r="A63" s="158" t="inlineStr">
-        <is>
-          <t>08-08 05:00</t>
-        </is>
-      </c>
-      <c r="B63" s="158" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C63" s="159" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="D63" s="160" t="n">
-        <v>1591.8</v>
-      </c>
-      <c r="E63" s="161" t="inlineStr">
-        <is>
-          <t>凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F63" s="158" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1" s="69">
-      <c r="A64" s="131" t="inlineStr">
-        <is>
-          <t>08-08 06:00</t>
-        </is>
-      </c>
-      <c r="B64" s="131" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C64" s="162" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="D64" s="153" t="n">
-        <v>1618</v>
-      </c>
-      <c r="E64" s="133" t="inlineStr">
-        <is>
-          <t>早晨恢复</t>
-        </is>
-      </c>
-      <c r="F64" s="131" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1" s="69">
-      <c r="A65" s="127" t="inlineStr">
-        <is>
-          <t>08-08 07:00</t>
-        </is>
-      </c>
-      <c r="B65" s="127" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C65" s="157" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="D65" s="129" t="n">
-        <v>1644.2</v>
-      </c>
-      <c r="E65" s="130" t="inlineStr">
-        <is>
-          <t>早晨恢复</t>
-        </is>
-      </c>
-      <c r="F65" s="127" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1" s="69">
-      <c r="A66" s="131" t="inlineStr">
-        <is>
-          <t>08-08 08:00</t>
-        </is>
-      </c>
-      <c r="B66" s="131" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C66" s="162" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="D66" s="153" t="n">
+      <c r="C84" s="183" t="n">
+        <v>1181.9</v>
+      </c>
+      <c r="D84" s="191" t="n">
+        <v>-296.4</v>
+      </c>
+      <c r="E84" s="177" t="inlineStr">
+        <is>
+          <t>-20.1%</t>
+        </is>
+      </c>
+      <c r="F84" s="177" t="inlineStr">
+        <is>
+          <t>V3约低230万</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="177" t="inlineStr">
+        <is>
+          <t>8/8 08:00 点映日早晨</t>
+        </is>
+      </c>
+      <c r="B85" s="177" t="n">
         <v>1670.4</v>
       </c>
-      <c r="E66" s="133" t="inlineStr">
-        <is>
-          <t>早晨恢复</t>
-        </is>
-      </c>
-      <c r="F66" s="131" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1" s="69">
-      <c r="A67" s="127" t="inlineStr">
-        <is>
-          <t>08-08 09:00</t>
-        </is>
-      </c>
-      <c r="B67" s="127" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C67" s="157" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="D67" s="129" t="n">
-        <v>1696.6</v>
-      </c>
-      <c r="E67" s="130" t="inlineStr">
-        <is>
-          <t>早晨恢复</t>
-        </is>
-      </c>
-      <c r="F67" s="127" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1" s="69">
-      <c r="A68" s="131" t="inlineStr">
-        <is>
-          <t>08-08 10:00</t>
-        </is>
-      </c>
-      <c r="B68" s="131" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C68" s="162" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="D68" s="153" t="n">
-        <v>1740.2</v>
-      </c>
-      <c r="E68" s="133" t="inlineStr">
-        <is>
-          <t>上午平稳</t>
-        </is>
-      </c>
-      <c r="F68" s="131" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1" s="69">
-      <c r="A69" s="127" t="inlineStr">
-        <is>
-          <t>08-08 11:00</t>
-        </is>
-      </c>
-      <c r="B69" s="127" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C69" s="157" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="D69" s="129" t="n">
-        <v>1783.9</v>
-      </c>
-      <c r="E69" s="130" t="inlineStr">
-        <is>
-          <t>上午平稳</t>
-        </is>
-      </c>
-      <c r="F69" s="127" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1" s="69">
-      <c r="A70" s="131" t="inlineStr">
-        <is>
-          <t>08-08 12:00</t>
-        </is>
-      </c>
-      <c r="B70" s="131" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C70" s="162" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="D70" s="153" t="n">
-        <v>1840.6</v>
-      </c>
-      <c r="E70" s="133" t="inlineStr">
-        <is>
-          <t>午间小高峰</t>
-        </is>
-      </c>
-      <c r="F70" s="131" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1" s="69">
-      <c r="A71" s="127" t="inlineStr">
-        <is>
-          <t>08-08 13:00</t>
-        </is>
-      </c>
-      <c r="B71" s="127" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C71" s="157" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="D71" s="129" t="n">
-        <v>1897.3</v>
-      </c>
-      <c r="E71" s="130" t="inlineStr">
-        <is>
-          <t>午间小高峰</t>
-        </is>
-      </c>
-      <c r="F71" s="127" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1" s="69">
-      <c r="A72" s="163" t="inlineStr">
-        <is>
-          <t>08-08 14:00</t>
-        </is>
-      </c>
-      <c r="B72" s="163" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C72" s="164" t="n">
-        <v>174.6</v>
-      </c>
-      <c r="D72" s="165" t="n">
+      <c r="C85" s="183" t="n">
+        <v>1299.9</v>
+      </c>
+      <c r="D85" s="191" t="n">
+        <v>-370.5</v>
+      </c>
+      <c r="E85" s="177" t="inlineStr">
+        <is>
+          <t>-22.2%</t>
+        </is>
+      </c>
+      <c r="F85" s="177" t="inlineStr">
+        <is>
+          <t>V3约低280万</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="177" t="inlineStr">
+        <is>
+          <t>8/8 14:00 点映开始!!</t>
+        </is>
+      </c>
+      <c r="B86" s="177" t="n">
         <v>2071.9</v>
       </c>
-      <c r="E72" s="166" t="inlineStr">
-        <is>
-          <t>点映开始!!</t>
-        </is>
-      </c>
-      <c r="F72" s="163" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="24" customHeight="1" s="69">
-      <c r="A74" s="152" t="inlineStr">
-        <is>
-          <t>四、关键节点预测对比（旧模型 vs 修正模型）</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="26" customHeight="1" s="69">
-      <c r="A75" s="126" t="inlineStr">
-        <is>
-          <t>关键节点</t>
-        </is>
-      </c>
-      <c r="B75" s="126" t="inlineStr">
-        <is>
-          <t>旧模型预测(万)</t>
-        </is>
-      </c>
-      <c r="C75" s="126" t="inlineStr">
-        <is>
-          <t>修正模型预测(万)</t>
-        </is>
-      </c>
-      <c r="D75" s="126" t="inlineStr">
-        <is>
-          <t>偏差</t>
-        </is>
-      </c>
-      <c r="E75" s="126" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="F75" s="126" t="inlineStr"/>
-    </row>
-    <row r="76" ht="24" customHeight="1" s="69">
-      <c r="A76" s="130" t="inlineStr">
-        <is>
-          <t>8/6 23:00 深夜收尾</t>
-        </is>
-      </c>
-      <c r="B76" s="129" t="n">
-        <v>612.2</v>
-      </c>
-      <c r="C76" s="129" t="n">
-        <v>573.9</v>
-      </c>
-      <c r="D76" s="174" t="inlineStr">
-        <is>
-          <t>-38.3</t>
-        </is>
-      </c>
-      <c r="E76" s="130" t="inlineStr">
-        <is>
-          <t>预售首日收尾</t>
-        </is>
-      </c>
-      <c r="F76" s="130" t="n"/>
-    </row>
-    <row r="77" ht="24" customHeight="1" s="69">
-      <c r="A77" s="133" t="inlineStr">
-        <is>
-          <t>8/7 08:00 映前4天早晨</t>
-        </is>
-      </c>
-      <c r="B77" s="153" t="n">
-        <v>794.4</v>
-      </c>
-      <c r="C77" s="153" t="n">
-        <v>727.5</v>
-      </c>
-      <c r="D77" s="175" t="inlineStr">
-        <is>
-          <t>-66.9</t>
-        </is>
-      </c>
-      <c r="E77" s="133" t="inlineStr">
-        <is>
-          <t>映前4天，宣发发酵期</t>
-        </is>
-      </c>
-      <c r="F77" s="133" t="n"/>
-    </row>
-    <row r="78" ht="24" customHeight="1" s="69">
-      <c r="A78" s="130" t="inlineStr">
-        <is>
-          <t>8/7 12:00 午间</t>
-        </is>
-      </c>
-      <c r="B78" s="129" t="n">
-        <v>925.1</v>
-      </c>
-      <c r="C78" s="129" t="n">
-        <v>863.7</v>
-      </c>
-      <c r="D78" s="174" t="inlineStr">
-        <is>
-          <t>-61.4</t>
-        </is>
-      </c>
-      <c r="E78" s="130" t="inlineStr">
-        <is>
-          <t>映前4天，宣发发酵期</t>
-        </is>
-      </c>
-      <c r="F78" s="130" t="n"/>
-    </row>
-    <row r="79" ht="24" customHeight="1" s="69">
-      <c r="A79" s="133" t="inlineStr">
-        <is>
-          <t>8/7 18:00 晚间高峰</t>
-        </is>
-      </c>
-      <c r="B79" s="153" t="n">
-        <v>1225.8</v>
-      </c>
-      <c r="C79" s="153" t="n">
-        <v>1171</v>
-      </c>
-      <c r="D79" s="175" t="inlineStr">
-        <is>
-          <t>-54.8</t>
-        </is>
-      </c>
-      <c r="E79" s="133" t="inlineStr">
-        <is>
-          <t>映前4天，宣发发酵期</t>
-        </is>
-      </c>
-      <c r="F79" s="133" t="n"/>
-    </row>
-    <row r="80" ht="24" customHeight="1" s="69">
-      <c r="A80" s="130" t="inlineStr">
-        <is>
-          <t>8/7 23:00 映前4天收尾</t>
-        </is>
-      </c>
-      <c r="B80" s="129" t="n">
-        <v>1590.3</v>
-      </c>
-      <c r="C80" s="129" t="n">
-        <v>1478.3</v>
-      </c>
-      <c r="D80" s="174" t="inlineStr">
-        <is>
-          <t>-112.0</t>
-        </is>
-      </c>
-      <c r="E80" s="130" t="inlineStr">
-        <is>
-          <t>映前4天，宣发发酵期</t>
-        </is>
-      </c>
-      <c r="F80" s="130" t="n"/>
-    </row>
-    <row r="81" ht="24" customHeight="1" s="69">
-      <c r="A81" s="133" t="inlineStr">
-        <is>
-          <t>8/8 08:00 点映日早晨</t>
-        </is>
-      </c>
-      <c r="B81" s="153" t="n">
-        <v>1887.3</v>
-      </c>
-      <c r="C81" s="153" t="n">
-        <v>1670.4</v>
-      </c>
-      <c r="D81" s="175" t="inlineStr">
-        <is>
-          <t>-216.9</t>
-        </is>
-      </c>
-      <c r="E81" s="133" t="inlineStr">
-        <is>
-          <t>预售首日收尾</t>
-        </is>
-      </c>
-      <c r="F81" s="133" t="n"/>
-    </row>
-    <row r="82" ht="24" customHeight="1" s="69">
-      <c r="A82" s="166" t="inlineStr">
-        <is>
-          <t>8/8 14:00 点映开始!!</t>
-        </is>
-      </c>
-      <c r="B82" s="165" t="n">
-        <v>2303.3</v>
-      </c>
-      <c r="C82" s="164" t="n">
-        <v>2071.9</v>
-      </c>
-      <c r="D82" s="176" t="inlineStr">
-        <is>
-          <t>-231.4</t>
-        </is>
-      </c>
-      <c r="E82" s="167" t="inlineStr">
-        <is>
-          <t>点映开始，最大变量</t>
-        </is>
-      </c>
-      <c r="F82" s="167" t="n"/>
-    </row>
-    <row r="84" ht="24" customHeight="1" s="69">
-      <c r="A84" s="152" t="inlineStr">
-        <is>
-          <t>五、模型修正说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1" s="69">
-      <c r="A85" s="168" t="inlineStr">
-        <is>
-          <t>• 基准增速修正：旧模型45万/h → 修正后58.2万/h（实测5组稳态均值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1" s="69">
-      <c r="A86" s="168" t="inlineStr">
-        <is>
-          <t>• 实测增速区间：33-57万/h（排除开售首波78万/h），晚间19-20点实测40万/h</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1" s="69">
-      <c r="A87" s="168" t="inlineStr">
-        <is>
-          <t>• 晚高峰系数下调：旧模型1.2 → 1.0，因实测晚高峰增速未显著高于均值</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1" s="69">
-      <c r="A88" s="168" t="inlineStr">
-        <is>
-          <t>• 日期系数下调：映前4天1.35→1.2、点映前2.2→1.5，因想看基数偏低(仅2.5万)，宣发发酵空间有限</t>
+      <c r="C86" s="183" t="n">
+        <v>1446</v>
+      </c>
+      <c r="D86" s="191" t="n">
+        <v>-625.9</v>
+      </c>
+      <c r="E86" s="177" t="inlineStr">
+        <is>
+          <t>-30.2%</t>
+        </is>
+      </c>
+      <c r="F86" s="177" t="inlineStr">
+        <is>
+          <t>V3约低515万，最大变量</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="24" customHeight="1" s="69">
+      <c r="A88" s="181" t="inlineStr">
+        <is>
+          <t>五、V3模型修正说明</t>
         </is>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1" s="69">
-      <c r="A89" s="168" t="inlineStr">
-        <is>
-          <t>• 点映系数下调：3.5→3.0，参照抓娃娃点映首日当日新增34.5万，但来龙餐馆想看基数更低</t>
+      <c r="A89" s="192" t="inlineStr">
+        <is>
+          <t>• 基准增速大幅修正：V2的58.2万/h → V3的43.3万/h（8组稳态实测均值）</t>
         </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1" s="69">
-      <c r="A90" s="168" t="inlineStr">
-        <is>
-          <t>• 整体判断：修正后预测值全面低于旧模型约15-25%，更贴近实际增速趋势</t>
+      <c r="A90" s="192" t="inlineStr">
+        <is>
+          <t>• V2高估原因：V2仅基于白天5组数据(14:45-18:03)，白天增速偏高；晚间18:03-23:01实测均值仅42.0万/h</t>
         </is>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1" s="69">
-      <c r="A91" s="168" t="inlineStr">
-        <is>
-          <t>• 最大变量：8/8 14:00点映口碑，若口碑爆发则增速可能远超预测；若口碑平庸则增速可能更低</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1" s="69">
-      <c r="A93" s="135" t="inlineStr">
-        <is>
-          <t>数据来源：猫眼专业版。预测基于9组实测数据(14:45-20:02)拟合，仅供参考。</t>
+      <c r="A91" s="192" t="inlineStr">
+        <is>
+          <t>• 晚间系数修正：V2的1.0 → V3的0.97（晚间实际略低于白天）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1" s="69">
+      <c r="A92" s="192" t="inlineStr">
+        <is>
+          <t>• 深夜系数修正：V2的0.7 → V3的0.55（21:52-22:02实测仅29.4万/h，远低于预期）</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1" s="69">
+      <c r="A93" s="192" t="inlineStr">
+        <is>
+          <t>• 日期系数修正：映前4天1.2→1.15、映前3天1.5→1.35、点映3.0→2.5（想看基数低，增长空间有限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1" s="69">
+      <c r="A94" s="192" t="inlineStr">
+        <is>
+          <t>• 实测vs预测验证：V2预测23:00=573.9万，实际565.5万，误差仅1.5%（V2单点尚可，但累积偏差放大）</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1" s="69">
+      <c r="A95" s="192" t="inlineStr">
+        <is>
+          <t>• V3与V2关键节点偏差：8/8 14:00点映开始 V3比V2低约515万（-24.9%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1" s="69">
+      <c r="A96" s="192" t="inlineStr">
+        <is>
+          <t>• 异常数据说明：22:30-22:50出现88.8万/h脉冲增速，疑似集中下单，已排除出基准计算</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1" s="69">
+      <c r="A97" s="192" t="inlineStr">
+        <is>
+          <t>• 最大变量：8/8 14:00点映口碑，若口碑爆发增速可能远超预测；若平庸则更低</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1" s="69">
+      <c r="A98" s="192" t="inlineStr">
+        <is>
+          <t>• 数据来源：猫眼专业版 | 预测基于14组实测数据(14:45-23:01)拟合，仅供参考</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="32">
     <mergeCell ref="D27:F27"/>
-    <mergeCell ref="A84:F84"/>
     <mergeCell ref="A90:F90"/>
+    <mergeCell ref="D32:F32"/>
     <mergeCell ref="A89:F89"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A95:F95"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A85:F85"/>
-    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="D30:F30"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="A96:F96"/>
     <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D29:F29"/>
     <mergeCell ref="A93:F93"/>
     <mergeCell ref="D23:F23"/>
     <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="D31:F31"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="A88:F88"/>
     <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="E18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/电影票房分析表.xlsx
+++ b/电影票房分析表.xlsx
@@ -12,9 +12,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售数据明细" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来龙餐馆预售追踪" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售增长分析" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售增长预测" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="想看数据明细" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售与票房节点" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="抓娃娃基准对比" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售增长预测" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="想看数据明细" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售与票房节点" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -29,7 +30,7 @@
     <numFmt numFmtId="166" formatCode="¥#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="45">
+  <fonts count="46">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -330,6 +331,12 @@
       <name val="微软雅黑"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -648,7 +655,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1214,6 +1221,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="22" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="26" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4198,6 +4220,775 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="69" min="1" max="1"/>
+    <col width="14" customWidth="1" style="69" min="2" max="2"/>
+    <col width="12" customWidth="1" style="69" min="3" max="3"/>
+    <col width="16" customWidth="1" style="69" min="4" max="4"/>
+    <col width="14" customWidth="1" style="69" min="5" max="5"/>
+    <col width="14" customWidth="1" style="69" min="6" max="6"/>
+    <col width="14" customWidth="1" style="69" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="69">
+      <c r="A1" s="178" t="inlineStr">
+        <is>
+          <t>抓娃娃 vs 来龙餐馆 预售基准对比分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" s="69">
+      <c r="A3" s="181" t="inlineStr">
+        <is>
+          <t>一、抓娃娃每日新增点映及预售总票房（基准）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="186" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="B4" s="186" t="inlineStr">
+        <is>
+          <t>每日新增(万)</t>
+        </is>
+      </c>
+      <c r="C4" s="186" t="inlineStr">
+        <is>
+          <t>日增长率</t>
+        </is>
+      </c>
+      <c r="D4" s="186" t="inlineStr">
+        <is>
+          <t>累计(万)</t>
+        </is>
+      </c>
+      <c r="E4" s="186" t="inlineStr">
+        <is>
+          <t>增长倍数(vs前日)</t>
+        </is>
+      </c>
+      <c r="F4" s="186" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="G4" s="151" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="177" t="inlineStr">
+        <is>
+          <t>映前5天</t>
+        </is>
+      </c>
+      <c r="B5" s="177" t="n">
+        <v>579.5</v>
+      </c>
+      <c r="C5" s="177" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="177" t="n">
+        <v>579.5</v>
+      </c>
+      <c r="E5" s="177" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="177" t="inlineStr">
+        <is>
+          <t>预售首日</t>
+        </is>
+      </c>
+      <c r="G5" s="188" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="177" t="inlineStr">
+        <is>
+          <t>映前4天</t>
+        </is>
+      </c>
+      <c r="B6" s="177" t="n">
+        <v>1630.24</v>
+      </c>
+      <c r="C6" s="177" t="inlineStr">
+        <is>
+          <t>+181%</t>
+        </is>
+      </c>
+      <c r="D6" s="177" t="n">
+        <v>2209.74</v>
+      </c>
+      <c r="E6" s="177" t="inlineStr">
+        <is>
+          <t>2.81x</t>
+        </is>
+      </c>
+      <c r="F6" s="177" t="inlineStr">
+        <is>
+          <t>稳步增长</t>
+        </is>
+      </c>
+      <c r="G6" s="188" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="180" t="inlineStr">
+        <is>
+          <t>映前3天</t>
+        </is>
+      </c>
+      <c r="B7" s="180" t="n">
+        <v>14876.95</v>
+      </c>
+      <c r="C7" s="180" t="inlineStr">
+        <is>
+          <t>+813%</t>
+        </is>
+      </c>
+      <c r="D7" s="180" t="n">
+        <v>17086.69</v>
+      </c>
+      <c r="E7" s="180" t="inlineStr">
+        <is>
+          <t>9.13x</t>
+        </is>
+      </c>
+      <c r="F7" s="180" t="inlineStr">
+        <is>
+          <t>点映开始!! 爆发</t>
+        </is>
+      </c>
+      <c r="G7" s="188" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="180" t="inlineStr">
+        <is>
+          <t>映前2天</t>
+        </is>
+      </c>
+      <c r="B8" s="180" t="n">
+        <v>19202.61</v>
+      </c>
+      <c r="C8" s="180" t="inlineStr">
+        <is>
+          <t>+29%</t>
+        </is>
+      </c>
+      <c r="D8" s="180" t="n">
+        <v>36289.3</v>
+      </c>
+      <c r="E8" s="180" t="inlineStr">
+        <is>
+          <t>1.29x</t>
+        </is>
+      </c>
+      <c r="F8" s="180" t="inlineStr">
+        <is>
+          <t>点映高峰</t>
+        </is>
+      </c>
+      <c r="G8" s="188" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="177" t="inlineStr">
+        <is>
+          <t>映前1天</t>
+        </is>
+      </c>
+      <c r="B9" s="177" t="n">
+        <v>14188.64</v>
+      </c>
+      <c r="C9" s="177" t="inlineStr">
+        <is>
+          <t>+-26%</t>
+        </is>
+      </c>
+      <c r="D9" s="177" t="n">
+        <v>50477.94</v>
+      </c>
+      <c r="E9" s="177" t="inlineStr">
+        <is>
+          <t>0.74x</t>
+        </is>
+      </c>
+      <c r="F9" s="177" t="inlineStr">
+        <is>
+          <t>首映前夕</t>
+        </is>
+      </c>
+      <c r="G9" s="188" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="193" t="inlineStr">
+        <is>
+          <t>关键比率: 映前5天→4天增长 2.81x | 日均增速(映前4天) 67.9万/h</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" s="69">
+      <c r="A13" s="181" t="inlineStr">
+        <is>
+          <t>二、来龙餐馆当前进度（8/7 映前4天）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="186" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B14" s="186" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="C14" s="186" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="D14" s="150" t="n"/>
+      <c r="E14" s="150" t="n"/>
+      <c r="F14" s="150" t="n"/>
+      <c r="G14" s="151" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="187" t="inlineStr">
+        <is>
+          <t>8/6收尾累计(映前5天)</t>
+        </is>
+      </c>
+      <c r="B15" s="177" t="inlineStr">
+        <is>
+          <t>565.5万</t>
+        </is>
+      </c>
+      <c r="C15" s="189" t="inlineStr">
+        <is>
+          <t>8/6 23:01实测值</t>
+        </is>
+      </c>
+      <c r="D15" s="188" t="n"/>
+      <c r="E15" s="188" t="n"/>
+      <c r="F15" s="188" t="n"/>
+      <c r="G15" s="188" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="187" t="inlineStr">
+        <is>
+          <t>当前累计(8/7 01:29)</t>
+        </is>
+      </c>
+      <c r="B16" s="177" t="inlineStr">
+        <is>
+          <t>618.1万</t>
+        </is>
+      </c>
+      <c r="C16" s="189" t="inlineStr">
+        <is>
+          <t>最新获取数据</t>
+        </is>
+      </c>
+      <c r="D16" s="188" t="n"/>
+      <c r="E16" s="188" t="n"/>
+      <c r="F16" s="188" t="n"/>
+      <c r="G16" s="188" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="187" t="inlineStr">
+        <is>
+          <t>8/7已新增</t>
+        </is>
+      </c>
+      <c r="B17" s="177" t="inlineStr">
+        <is>
+          <t>52.6万</t>
+        </is>
+      </c>
+      <c r="C17" s="189" t="inlineStr">
+        <is>
+          <t>约1.5小时增长，增速35.1万/h</t>
+        </is>
+      </c>
+      <c r="D17" s="188" t="n"/>
+      <c r="E17" s="188" t="n"/>
+      <c r="F17" s="188" t="n"/>
+      <c r="G17" s="188" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="194" t="inlineStr">
+        <is>
+          <t>8/7目标新增</t>
+        </is>
+      </c>
+      <c r="B18" s="180" t="inlineStr">
+        <is>
+          <t>1630.24万</t>
+        </is>
+      </c>
+      <c r="C18" s="189" t="inlineStr">
+        <is>
+          <t>对标抓娃娃映前4天</t>
+        </is>
+      </c>
+      <c r="D18" s="188" t="n"/>
+      <c r="E18" s="188" t="n"/>
+      <c r="F18" s="188" t="n"/>
+      <c r="G18" s="188" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="187" t="inlineStr">
+        <is>
+          <t>8/7目标累计</t>
+        </is>
+      </c>
+      <c r="B19" s="177" t="inlineStr">
+        <is>
+          <t>2195.74万</t>
+        </is>
+      </c>
+      <c r="C19" s="189">
+        <f> 565.5 + 1630.24</f>
+        <v/>
+      </c>
+      <c r="D19" s="188" t="n"/>
+      <c r="E19" s="188" t="n"/>
+      <c r="F19" s="188" t="n"/>
+      <c r="G19" s="188" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="187" t="inlineStr">
+        <is>
+          <t>剩余需增长</t>
+        </is>
+      </c>
+      <c r="B20" s="177" t="inlineStr">
+        <is>
+          <t>1577.64万</t>
+        </is>
+      </c>
+      <c r="C20" s="189" t="inlineStr">
+        <is>
+          <t>目标1630.24 - 已完成52.6</t>
+        </is>
+      </c>
+      <c r="D20" s="188" t="n"/>
+      <c r="E20" s="188" t="n"/>
+      <c r="F20" s="188" t="n"/>
+      <c r="G20" s="188" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="187" t="inlineStr">
+        <is>
+          <t>剩余时间</t>
+        </is>
+      </c>
+      <c r="B21" s="177" t="inlineStr">
+        <is>
+          <t>21.5小时</t>
+        </is>
+      </c>
+      <c r="C21" s="189" t="inlineStr">
+        <is>
+          <t>至8/7 23:00</t>
+        </is>
+      </c>
+      <c r="D21" s="188" t="n"/>
+      <c r="E21" s="188" t="n"/>
+      <c r="F21" s="188" t="n"/>
+      <c r="G21" s="188" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="194" t="inlineStr">
+        <is>
+          <t>所需平均增速</t>
+        </is>
+      </c>
+      <c r="B22" s="180" t="inlineStr">
+        <is>
+          <t>73.4万/h</t>
+        </is>
+      </c>
+      <c r="C22" s="189" t="inlineStr">
+        <is>
+          <t>V3预测仅43.3万/h，需达成的1.7倍</t>
+        </is>
+      </c>
+      <c r="D22" s="188" t="n"/>
+      <c r="E22" s="188" t="n"/>
+      <c r="F22" s="188" t="n"/>
+      <c r="G22" s="188" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="187" t="inlineStr">
+        <is>
+          <t>V3预测8/7累计</t>
+        </is>
+      </c>
+      <c r="B23" s="191" t="inlineStr">
+        <is>
+          <t>1181.9万</t>
+        </is>
+      </c>
+      <c r="C23" s="189" t="inlineStr">
+        <is>
+          <t>比目标低1013.8万</t>
+        </is>
+      </c>
+      <c r="D23" s="188" t="n"/>
+      <c r="E23" s="188" t="n"/>
+      <c r="F23" s="188" t="n"/>
+      <c r="G23" s="188" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="187" t="inlineStr">
+        <is>
+          <t>V3预测8/7新增</t>
+        </is>
+      </c>
+      <c r="B24" s="191" t="inlineStr">
+        <is>
+          <t>616.4万</t>
+        </is>
+      </c>
+      <c r="C24" s="189" t="inlineStr">
+        <is>
+          <t>比目标低1013.8万</t>
+        </is>
+      </c>
+      <c r="D24" s="188" t="n"/>
+      <c r="E24" s="188" t="n"/>
+      <c r="F24" s="188" t="n"/>
+      <c r="G24" s="188" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1" s="69">
+      <c r="A26" s="181" t="inlineStr">
+        <is>
+          <t>三、达成1630.24万目标的逐小时所需增速</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="186" t="inlineStr">
+        <is>
+          <t>时段</t>
+        </is>
+      </c>
+      <c r="B27" s="186" t="inlineStr">
+        <is>
+          <t>时长(h)</t>
+        </is>
+      </c>
+      <c r="C27" s="186" t="inlineStr">
+        <is>
+          <t>时段系数</t>
+        </is>
+      </c>
+      <c r="D27" s="186" t="inlineStr">
+        <is>
+          <t>所需增速(万/h)</t>
+        </is>
+      </c>
+      <c r="E27" s="186" t="inlineStr">
+        <is>
+          <t>时段新增(万)</t>
+        </is>
+      </c>
+      <c r="F27" s="186" t="inlineStr">
+        <is>
+          <t>累计(万)</t>
+        </is>
+      </c>
+      <c r="G27" s="186" t="inlineStr">
+        <is>
+          <t>难度评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="177" t="inlineStr">
+        <is>
+          <t>01:30-06:00 凌晨</t>
+        </is>
+      </c>
+      <c r="B28" s="177" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C28" s="177" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D28" s="177" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="E28" s="177" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="F28" s="177" t="n">
+        <v>691.7</v>
+      </c>
+      <c r="G28" s="182" t="inlineStr">
+        <is>
+          <t>轻松</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="177" t="inlineStr">
+        <is>
+          <t>06:00-10:00 早晨</t>
+        </is>
+      </c>
+      <c r="B29" s="177" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="177" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D29" s="177" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E29" s="177" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="F29" s="177" t="n">
+        <v>822.5</v>
+      </c>
+      <c r="G29" s="182" t="inlineStr">
+        <is>
+          <t>可行</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="177" t="inlineStr">
+        <is>
+          <t>10:00-12:00 上午</t>
+        </is>
+      </c>
+      <c r="B30" s="177" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="177" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D30" s="177" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="E30" s="177" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="F30" s="177" t="n">
+        <v>942.4</v>
+      </c>
+      <c r="G30" s="194" t="inlineStr">
+        <is>
+          <t>有挑战</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="177" t="inlineStr">
+        <is>
+          <t>12:00-14:00 午间</t>
+        </is>
+      </c>
+      <c r="B31" s="177" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="177" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D31" s="177" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="E31" s="177" t="n">
+        <v>152.6</v>
+      </c>
+      <c r="F31" s="177" t="n">
+        <v>1095</v>
+      </c>
+      <c r="G31" s="195" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="177" t="inlineStr">
+        <is>
+          <t>14:00-18:00 下午</t>
+        </is>
+      </c>
+      <c r="B32" s="177" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="177" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D32" s="177" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="E32" s="177" t="n">
+        <v>392.4</v>
+      </c>
+      <c r="F32" s="177" t="n">
+        <v>1487.4</v>
+      </c>
+      <c r="G32" s="195" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="177" t="inlineStr">
+        <is>
+          <t>18:00-23:00 晚间</t>
+        </is>
+      </c>
+      <c r="B33" s="177" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" s="177" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D33" s="177" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="E33" s="177" t="n">
+        <v>708.4</v>
+      </c>
+      <c r="F33" s="177" t="n">
+        <v>2195.8</v>
+      </c>
+      <c r="G33" s="195" t="inlineStr">
+        <is>
+          <t>极难</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1" s="69">
+      <c r="A35" s="181" t="inlineStr">
+        <is>
+          <t>四、对比分析与结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" s="69">
+      <c r="A36" s="192" t="inlineStr">
+        <is>
+          <t>• 抓娃娃映前5天→4天增长比 2.81x（579.5万→1630.24万，日增1050.74万）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1" s="69">
+      <c r="A37" s="192" t="inlineStr">
+        <is>
+          <t>• 龙餐馆映前5天收尾 565.5万，按同比例等效目标 1590.86万，设定目标 1630.24万</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1" s="69">
+      <c r="A38" s="192" t="inlineStr">
+        <is>
+          <t>• 达成目标需8/7全天平均增速 73.4万/h，是V3预测(43.3万/h)的 1.7倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1" s="69">
+      <c r="A39" s="196" t="inlineStr">
+        <is>
+          <t>• 关键时段：18:00-23:00晚间需贡献约708万，占比约45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1" s="69">
+      <c r="A40" s="192" t="inlineStr">
+        <is>
+          <t>• V3预测8/7累计仅1181.9万，比目标低1014万，需大幅修正预期或依赖晚间爆发</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1" s="69">
+      <c r="A41" s="192" t="inlineStr">
+        <is>
+          <t>• 当前深夜增速偏低(01:29仅35.1万/h)，凌晨时段对总量贡献有限</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1" s="69">
+      <c r="A42" s="197" t="inlineStr">
+        <is>
+          <t>• 可行性判断：达成目标难度极大，需8/7白天增速显著高于8/6，且晚间出现爆发式增长</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1" s="69">
+      <c r="A43" s="192" t="inlineStr">
+        <is>
+          <t>• 参考抓娃娃映前3天爆发(14876.95万)，点映开始后增速可能数倍增长，但龙餐馆想看基数远低于抓娃娃</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" s="69">
+      <c r="A44" s="197" t="inlineStr">
+        <is>
+          <t>• 建议持续跟踪8/7白天增速趋势，若12:00前累计未达800万，目标基本无法达成</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="A42:G42"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4585,7 +5376,7 @@
           <t>8组稳态均值</t>
         </is>
       </c>
-      <c r="C18" s="188" t="n"/>
+      <c r="C18" s="151" t="n"/>
       <c r="D18" s="187" t="n">
         <v>43.3</v>
       </c>
@@ -4594,7 +5385,7 @@
           <t>晚间均值42.0万/h | 白天均值45.5万/h</t>
         </is>
       </c>
-      <c r="F18" s="188" t="n"/>
+      <c r="F18" s="151" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1" s="69">
       <c r="A20" s="181" t="inlineStr">
@@ -4644,8 +5435,8 @@
           <t>8组稳态实测均值(排除首波3组+脉冲1组)，较V2大幅下调</t>
         </is>
       </c>
-      <c r="E22" s="188" t="n"/>
-      <c r="F22" s="188" t="n"/>
+      <c r="E22" s="150" t="n"/>
+      <c r="F22" s="151" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="187" t="inlineStr">
@@ -4664,8 +5455,8 @@
           <t>晚间均值42.0/基准43.3，晚间略低于白天</t>
         </is>
       </c>
-      <c r="E23" s="188" t="n"/>
-      <c r="F23" s="188" t="n"/>
+      <c r="E23" s="150" t="n"/>
+      <c r="F23" s="151" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="187" t="inlineStr">
@@ -4684,8 +5475,8 @@
           <t>23点后增速明显回落，参照21:52-22:02的29.4万/h</t>
         </is>
       </c>
-      <c r="E24" s="188" t="n"/>
-      <c r="F24" s="188" t="n"/>
+      <c r="E24" s="150" t="n"/>
+      <c r="F24" s="151" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="187" t="inlineStr">
@@ -4704,8 +5495,8 @@
           <t>深夜购票几乎停滞</t>
         </is>
       </c>
-      <c r="E25" s="188" t="n"/>
-      <c r="F25" s="188" t="n"/>
+      <c r="E25" s="150" t="n"/>
+      <c r="F25" s="151" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="187" t="inlineStr">
@@ -4724,8 +5515,8 @@
           <t>少量恢复</t>
         </is>
       </c>
-      <c r="E26" s="188" t="n"/>
-      <c r="F26" s="188" t="n"/>
+      <c r="E26" s="150" t="n"/>
+      <c r="F26" s="151" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="187" t="inlineStr">
@@ -4744,8 +5535,8 @@
           <t>平稳低速</t>
         </is>
       </c>
-      <c r="E27" s="188" t="n"/>
-      <c r="F27" s="188" t="n"/>
+      <c r="E27" s="150" t="n"/>
+      <c r="F27" s="151" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="187" t="inlineStr">
@@ -4764,8 +5555,8 @@
           <t>午间小幅回升</t>
         </is>
       </c>
-      <c r="E28" s="188" t="n"/>
-      <c r="F28" s="188" t="n"/>
+      <c r="E28" s="150" t="n"/>
+      <c r="F28" s="151" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="187" t="inlineStr">
@@ -4784,8 +5575,8 @@
           <t>下午增速回升，保持不变</t>
         </is>
       </c>
-      <c r="E29" s="188" t="n"/>
-      <c r="F29" s="188" t="n"/>
+      <c r="E29" s="150" t="n"/>
+      <c r="F29" s="151" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="187" t="inlineStr">
@@ -4804,8 +5595,8 @@
           <t>作为基准日=1.0，其他日期相对调整</t>
         </is>
       </c>
-      <c r="E30" s="188" t="n"/>
-      <c r="F30" s="188" t="n"/>
+      <c r="E30" s="150" t="n"/>
+      <c r="F30" s="151" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="187" t="inlineStr">
@@ -4824,8 +5615,8 @@
           <t>宣发发酵，但想看基数低(2.5万)，适度上调</t>
         </is>
       </c>
-      <c r="E31" s="188" t="n"/>
-      <c r="F31" s="188" t="n"/>
+      <c r="E31" s="150" t="n"/>
+      <c r="F31" s="151" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="187" t="inlineStr">
@@ -4844,8 +5635,8 @@
           <t>点映前半天，预期温和增长</t>
         </is>
       </c>
-      <c r="E32" s="188" t="n"/>
-      <c r="F32" s="188" t="n"/>
+      <c r="E32" s="150" t="n"/>
+      <c r="F32" s="151" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="187" t="inlineStr">
@@ -4864,8 +5655,8 @@
           <t>点映票房计入，但想看基数偏低</t>
         </is>
       </c>
-      <c r="E33" s="188" t="n"/>
-      <c r="F33" s="188" t="n"/>
+      <c r="E33" s="150" t="n"/>
+      <c r="F33" s="151" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1" s="69">
       <c r="A35" s="181" t="inlineStr">
@@ -6344,8 +7135,8 @@
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A96:F96"/>
     <mergeCell ref="D33:F33"/>
-    <mergeCell ref="A96:F96"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="A93:F93"/>
@@ -6365,7 +7156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6663,7 +7454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/电影票房分析表.xlsx
+++ b/电影票房分析表.xlsx
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B15" s="177" t="inlineStr">
         <is>
-          <t>565.5万</t>
+          <t>599.1万</t>
         </is>
       </c>
       <c r="C15" s="189" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="B17" s="177" t="inlineStr">
         <is>
-          <t>52.6万</t>
+          <t>19.0万</t>
         </is>
       </c>
       <c r="C17" s="189" t="inlineStr">
         <is>
-          <t>约1.5小时增长，增速35.1万/h</t>
+          <t>约1.5小时增长，增速12.7万/h</t>
         </is>
       </c>
       <c r="D17" s="188" t="n"/>
@@ -4551,11 +4551,11 @@
       </c>
       <c r="B19" s="177" t="inlineStr">
         <is>
-          <t>2195.74万</t>
+          <t>2229.34万</t>
         </is>
       </c>
       <c r="C19" s="189">
-        <f> 565.5 + 1630.24</f>
+        <f> 599.1 + 1630.24</f>
         <v/>
       </c>
       <c r="D19" s="188" t="n"/>
@@ -4571,12 +4571,12 @@
       </c>
       <c r="B20" s="177" t="inlineStr">
         <is>
-          <t>1577.64万</t>
+          <t>1611.24万</t>
         </is>
       </c>
       <c r="C20" s="189" t="inlineStr">
         <is>
-          <t>目标1630.24 - 已完成52.6</t>
+          <t>目标1630.24 - 已完成19.0</t>
         </is>
       </c>
       <c r="D20" s="188" t="n"/>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="B22" s="180" t="inlineStr">
         <is>
-          <t>73.4万/h</t>
+          <t>74.9万/h</t>
         </is>
       </c>
       <c r="C22" s="189" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B23" s="191" t="inlineStr">
         <is>
-          <t>1181.9万</t>
+          <t>1215.5万</t>
         </is>
       </c>
       <c r="C23" s="189" t="inlineStr">
@@ -4725,13 +4725,13 @@
         <v>0.15</v>
       </c>
       <c r="D28" s="177" t="n">
-        <v>16.3</v>
+        <v>16.7</v>
       </c>
       <c r="E28" s="177" t="n">
-        <v>73.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F28" s="177" t="n">
-        <v>691.7</v>
+        <v>693.2</v>
       </c>
       <c r="G28" s="182" t="inlineStr">
         <is>
@@ -4752,13 +4752,13 @@
         <v>0.3</v>
       </c>
       <c r="D29" s="177" t="n">
-        <v>32.7</v>
+        <v>33.4</v>
       </c>
       <c r="E29" s="177" t="n">
-        <v>130.8</v>
+        <v>133.6</v>
       </c>
       <c r="F29" s="177" t="n">
-        <v>822.5</v>
+        <v>826.8</v>
       </c>
       <c r="G29" s="182" t="inlineStr">
         <is>
@@ -4779,13 +4779,13 @@
         <v>0.55</v>
       </c>
       <c r="D30" s="177" t="n">
-        <v>59.9</v>
+        <v>61.2</v>
       </c>
       <c r="E30" s="177" t="n">
-        <v>119.9</v>
+        <v>122.4</v>
       </c>
       <c r="F30" s="177" t="n">
-        <v>942.4</v>
+        <v>949.2</v>
       </c>
       <c r="G30" s="194" t="inlineStr">
         <is>
@@ -4806,13 +4806,13 @@
         <v>0.7</v>
       </c>
       <c r="D31" s="177" t="n">
-        <v>76.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E31" s="177" t="n">
-        <v>152.6</v>
+        <v>155.8</v>
       </c>
       <c r="F31" s="177" t="n">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="G31" s="195" t="inlineStr">
         <is>
@@ -4833,17 +4833,17 @@
         <v>0.9</v>
       </c>
       <c r="D32" s="177" t="n">
-        <v>98.09999999999999</v>
+        <v>100.2</v>
       </c>
       <c r="E32" s="177" t="n">
-        <v>392.4</v>
+        <v>400.7</v>
       </c>
       <c r="F32" s="177" t="n">
-        <v>1487.4</v>
+        <v>1505.7</v>
       </c>
       <c r="G32" s="195" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>极难</t>
         </is>
       </c>
     </row>
@@ -4860,13 +4860,13 @@
         <v>1.3</v>
       </c>
       <c r="D33" s="177" t="n">
-        <v>141.7</v>
+        <v>144.7</v>
       </c>
       <c r="E33" s="177" t="n">
-        <v>708.4</v>
+        <v>723.5</v>
       </c>
       <c r="F33" s="177" t="n">
-        <v>2195.8</v>
+        <v>2229.2</v>
       </c>
       <c r="G33" s="195" t="inlineStr">
         <is>
@@ -4891,35 +4891,35 @@
     <row r="37" ht="20" customHeight="1" s="69">
       <c r="A37" s="192" t="inlineStr">
         <is>
-          <t>• 龙餐馆映前5天收尾 565.5万，按同比例等效目标 1590.86万，设定目标 1630.24万</t>
+          <t>• 龙餐馆映前5天收尾 599.1万，按同比例等效目标 1685.38万，设定目标 1630.24万</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" s="69">
       <c r="A38" s="192" t="inlineStr">
         <is>
-          <t>• 达成目标需8/7全天平均增速 73.4万/h，是V3预测(43.3万/h)的 1.7倍</t>
+          <t>• 达成目标需8/7全天平均增速 74.9万/h，是V3预测(43.3万/h)的 1.7倍</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" s="69">
       <c r="A39" s="196" t="inlineStr">
         <is>
-          <t>• 关键时段：18:00-23:00晚间需贡献约708万，占比约45%</t>
+          <t>• 关键时段：18:00-23:00晚间需贡献约724万，占比约45%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1" s="69">
       <c r="A40" s="192" t="inlineStr">
         <is>
-          <t>• V3预测8/7累计仅1181.9万，比目标低1014万，需大幅修正预期或依赖晚间爆发</t>
+          <t>• V3预测8/7累计仅1215.5万，比目标低1014万，需大幅修正预期或依赖晚间爆发</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1" s="69">
       <c r="A41" s="192" t="inlineStr">
         <is>
-          <t>• 当前深夜增速偏低(01:29仅35.1万/h)，凌晨时段对总量贡献有限</t>
+          <t>• 当前深夜增速偏低(01:29仅12.7万/h)，凌晨时段对总量贡献有限</t>
         </is>
       </c>
     </row>

--- a/电影票房分析表.xlsx
+++ b/电影票房分析表.xlsx
@@ -12,10 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售数据明细" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来龙餐馆预售追踪" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售增长分析" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="抓娃娃基准对比" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售增长预测" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="想看数据明细" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售与票房节点" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售增长预测" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目标达成路径" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="抓娃娃基准对比" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="想看数据明细" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预售与票房节点" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -655,7 +656,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1237,6 +1238,15 @@
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="26" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1835,6 +1845,576 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="16" customWidth="1" style="68" min="1" max="1"/>
+    <col width="12" customWidth="1" style="68" min="2" max="2"/>
+    <col width="24" customWidth="1" style="68" min="3" max="3"/>
+    <col width="16" customWidth="1" style="68" min="4" max="4"/>
+    <col width="40" customWidth="1" style="68" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31.5" customHeight="1" s="69">
+      <c r="A1" s="70" t="inlineStr">
+        <is>
+          <t>预售与票房关键节点数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25.5" customHeight="1" s="69">
+      <c r="A2" s="72" t="inlineStr">
+        <is>
+          <t>电影</t>
+        </is>
+      </c>
+      <c r="B2" s="72" t="inlineStr">
+        <is>
+          <t>数据类型</t>
+        </is>
+      </c>
+      <c r="C2" s="72" t="inlineStr">
+        <is>
+          <t>时间节点</t>
+        </is>
+      </c>
+      <c r="D2" s="72" t="inlineStr">
+        <is>
+          <t>金额(元)</t>
+        </is>
+      </c>
+      <c r="E2" s="72" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21.75" customHeight="1" s="69">
+      <c r="A3" s="142" t="inlineStr">
+        <is>
+          <t>抓娃娃</t>
+        </is>
+      </c>
+      <c r="B3" s="143" t="inlineStr">
+        <is>
+          <t>预售</t>
+        </is>
+      </c>
+      <c r="C3" s="121" t="inlineStr">
+        <is>
+          <t>映前10天(07-06)</t>
+        </is>
+      </c>
+      <c r="D3" s="77" t="n">
+        <v>630000</v>
+      </c>
+      <c r="E3" s="144" t="inlineStr">
+        <is>
+          <t>当日新增63.0万</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21.75" customHeight="1" s="69">
+      <c r="A4" s="145" t="inlineStr">
+        <is>
+          <t>抓娃娃</t>
+        </is>
+      </c>
+      <c r="B4" s="143" t="inlineStr">
+        <is>
+          <t>预售</t>
+        </is>
+      </c>
+      <c r="C4" s="119" t="inlineStr">
+        <is>
+          <t>映前4天(07-12)</t>
+        </is>
+      </c>
+      <c r="D4" s="83" t="n">
+        <v>1720000</v>
+      </c>
+      <c r="E4" s="146" t="inlineStr">
+        <is>
+          <t>当日新增17.2万</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21.75" customHeight="1" s="69">
+      <c r="A5" s="142" t="inlineStr">
+        <is>
+          <t>抓娃娃</t>
+        </is>
+      </c>
+      <c r="B5" s="143" t="inlineStr">
+        <is>
+          <t>预售</t>
+        </is>
+      </c>
+      <c r="C5" s="121" t="inlineStr">
+        <is>
+          <t>映前3天(07-13)</t>
+        </is>
+      </c>
+      <c r="D5" s="77" t="n">
+        <v>3450000</v>
+      </c>
+      <c r="E5" s="144" t="inlineStr">
+        <is>
+          <t>当日新增34.5万，点映首日</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.75" customHeight="1" s="69">
+      <c r="A6" s="145" t="inlineStr">
+        <is>
+          <t>抓娃娃</t>
+        </is>
+      </c>
+      <c r="B6" s="143" t="inlineStr">
+        <is>
+          <t>预售</t>
+        </is>
+      </c>
+      <c r="C6" s="119" t="inlineStr">
+        <is>
+          <t>映前2天(07-14)</t>
+        </is>
+      </c>
+      <c r="D6" s="83" t="n">
+        <v>15640000</v>
+      </c>
+      <c r="E6" s="146" t="inlineStr">
+        <is>
+          <t>当日新增156.4万</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21.75" customHeight="1" s="69">
+      <c r="A7" s="142" t="inlineStr">
+        <is>
+          <t>抓娃娃</t>
+        </is>
+      </c>
+      <c r="B7" s="143" t="inlineStr">
+        <is>
+          <t>预售</t>
+        </is>
+      </c>
+      <c r="C7" s="121" t="inlineStr">
+        <is>
+          <t>映前1天(07-15)</t>
+        </is>
+      </c>
+      <c r="D7" s="78" t="n">
+        <v>138260000</v>
+      </c>
+      <c r="E7" s="144" t="inlineStr">
+        <is>
+          <t>当日新增1382.6万，预售集中爆发</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21.75" customHeight="1" s="69">
+      <c r="A8" s="145" t="inlineStr">
+        <is>
+          <t>抓娃娃</t>
+        </is>
+      </c>
+      <c r="B8" s="147" t="inlineStr">
+        <is>
+          <t>票房</t>
+        </is>
+      </c>
+      <c r="C8" s="80" t="inlineStr">
+        <is>
+          <t>2024-07-13(点映首日)</t>
+        </is>
+      </c>
+      <c r="D8" s="83" t="n">
+        <v>156000000</v>
+      </c>
+      <c r="E8" s="146" t="inlineStr">
+        <is>
+          <t>点映首日单日票房约1.56亿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21.75" customHeight="1" s="69">
+      <c r="A9" s="142" t="inlineStr">
+        <is>
+          <t>抓娃娃</t>
+        </is>
+      </c>
+      <c r="B9" s="147" t="inlineStr">
+        <is>
+          <t>票房</t>
+        </is>
+      </c>
+      <c r="C9" s="74" t="inlineStr">
+        <is>
+          <t>2024-07-16(上映首日)</t>
+        </is>
+      </c>
+      <c r="D9" s="77" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="E9" s="144" t="inlineStr">
+        <is>
+          <t>正式上映首日票房6.5亿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21.75" customHeight="1" s="69">
+      <c r="A10" s="145" t="inlineStr">
+        <is>
+          <t>抓娃娃</t>
+        </is>
+      </c>
+      <c r="B10" s="147" t="inlineStr">
+        <is>
+          <t>票房</t>
+        </is>
+      </c>
+      <c r="C10" s="80" t="inlineStr">
+        <is>
+          <t>2024-07-20(上映第4天)</t>
+        </is>
+      </c>
+      <c r="D10" s="83" t="n">
+        <v>1100000000</v>
+      </c>
+      <c r="E10" s="146" t="inlineStr">
+        <is>
+          <t>票房突破11亿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21.75" customHeight="1" s="69">
+      <c r="A11" s="142" t="inlineStr">
+        <is>
+          <t>抓娃娃</t>
+        </is>
+      </c>
+      <c r="B11" s="147" t="inlineStr">
+        <is>
+          <t>票房</t>
+        </is>
+      </c>
+      <c r="C11" s="121" t="inlineStr">
+        <is>
+          <t>累计总票房</t>
+        </is>
+      </c>
+      <c r="D11" s="78" t="n">
+        <v>3300000000</v>
+      </c>
+      <c r="E11" s="144" t="inlineStr">
+        <is>
+          <t>累计票房超33亿，暑期档冠军</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21.75" customHeight="1" s="69">
+      <c r="A12" s="145" t="inlineStr">
+        <is>
+          <t>独行月球</t>
+        </is>
+      </c>
+      <c r="B12" s="143" t="inlineStr">
+        <is>
+          <t>预售</t>
+        </is>
+      </c>
+      <c r="C12" s="119" t="inlineStr">
+        <is>
+          <t>映前10天(07-19)</t>
+        </is>
+      </c>
+      <c r="D12" s="83" t="n">
+        <v>890000</v>
+      </c>
+      <c r="E12" s="146" t="inlineStr">
+        <is>
+          <t>当日新增8.9万</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21.75" customHeight="1" s="69">
+      <c r="A13" s="142" t="inlineStr">
+        <is>
+          <t>独行月球</t>
+        </is>
+      </c>
+      <c r="B13" s="143" t="inlineStr">
+        <is>
+          <t>预售</t>
+        </is>
+      </c>
+      <c r="C13" s="121" t="inlineStr">
+        <is>
+          <t>映前7天(07-22)</t>
+        </is>
+      </c>
+      <c r="D13" s="77" t="n">
+        <v>2582000</v>
+      </c>
+      <c r="E13" s="144" t="inlineStr">
+        <is>
+          <t>当日新增258.2万</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21.75" customHeight="1" s="69">
+      <c r="A14" s="145" t="inlineStr">
+        <is>
+          <t>独行月球</t>
+        </is>
+      </c>
+      <c r="B14" s="143" t="inlineStr">
+        <is>
+          <t>预售</t>
+        </is>
+      </c>
+      <c r="C14" s="119" t="inlineStr">
+        <is>
+          <t>映前4天(07-25)</t>
+        </is>
+      </c>
+      <c r="D14" s="83" t="n">
+        <v>27200000</v>
+      </c>
+      <c r="E14" s="146" t="inlineStr">
+        <is>
+          <t>当日新增272.0万</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="21.75" customHeight="1" s="69">
+      <c r="A15" s="142" t="inlineStr">
+        <is>
+          <t>独行月球</t>
+        </is>
+      </c>
+      <c r="B15" s="143" t="inlineStr">
+        <is>
+          <t>预售</t>
+        </is>
+      </c>
+      <c r="C15" s="121" t="inlineStr">
+        <is>
+          <t>映前3天(07-26)</t>
+        </is>
+      </c>
+      <c r="D15" s="77" t="n">
+        <v>40040000</v>
+      </c>
+      <c r="E15" s="144" t="inlineStr">
+        <is>
+          <t>当日新增400.4万</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="21.75" customHeight="1" s="69">
+      <c r="A16" s="145" t="inlineStr">
+        <is>
+          <t>独行月球</t>
+        </is>
+      </c>
+      <c r="B16" s="143" t="inlineStr">
+        <is>
+          <t>预售</t>
+        </is>
+      </c>
+      <c r="C16" s="119" t="inlineStr">
+        <is>
+          <t>映前2天(07-27)</t>
+        </is>
+      </c>
+      <c r="D16" s="83" t="n">
+        <v>89600000</v>
+      </c>
+      <c r="E16" s="146" t="inlineStr">
+        <is>
+          <t>当日新增896.0万</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="21.75" customHeight="1" s="69">
+      <c r="A17" s="142" t="inlineStr">
+        <is>
+          <t>独行月球</t>
+        </is>
+      </c>
+      <c r="B17" s="143" t="inlineStr">
+        <is>
+          <t>预售</t>
+        </is>
+      </c>
+      <c r="C17" s="121" t="inlineStr">
+        <is>
+          <t>映前1天(07-28)</t>
+        </is>
+      </c>
+      <c r="D17" s="78" t="n">
+        <v>273500000</v>
+      </c>
+      <c r="E17" s="144" t="inlineStr">
+        <is>
+          <t>当日新增2735.0万，预售集中爆发</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="21.75" customHeight="1" s="69">
+      <c r="A18" s="145" t="inlineStr">
+        <is>
+          <t>独行月球</t>
+        </is>
+      </c>
+      <c r="B18" s="147" t="inlineStr">
+        <is>
+          <t>票房</t>
+        </is>
+      </c>
+      <c r="C18" s="80" t="inlineStr">
+        <is>
+          <t>2022-07-29(上映首日)</t>
+        </is>
+      </c>
+      <c r="D18" s="83" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="E18" s="146" t="inlineStr">
+        <is>
+          <t>首日票房(含预售)破2亿</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21.75" customHeight="1" s="69">
+      <c r="A19" s="142" t="inlineStr">
+        <is>
+          <t>独行月球</t>
+        </is>
+      </c>
+      <c r="B19" s="147" t="inlineStr">
+        <is>
+          <t>票房</t>
+        </is>
+      </c>
+      <c r="C19" s="74" t="inlineStr">
+        <is>
+          <t>2022-07-31(上映第3天)</t>
+        </is>
+      </c>
+      <c r="D19" s="77" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="E19" s="148" t="inlineStr">
+        <is>
+          <t>3天票房破10亿</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="21.75" customHeight="1" s="69">
+      <c r="A20" s="145" t="inlineStr">
+        <is>
+          <t>独行月球</t>
+        </is>
+      </c>
+      <c r="B20" s="147" t="inlineStr">
+        <is>
+          <t>票房</t>
+        </is>
+      </c>
+      <c r="C20" s="119" t="inlineStr">
+        <is>
+          <t>累计总票房</t>
+        </is>
+      </c>
+      <c r="D20" s="78" t="n">
+        <v>3103000000</v>
+      </c>
+      <c r="E20" s="146" t="inlineStr">
+        <is>
+          <t>最终累计票房31.03亿，2022年度亚军</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="21.75" customHeight="1" s="69">
+      <c r="A21" s="142" t="inlineStr">
+        <is>
+          <t>欢迎来龙餐馆</t>
+        </is>
+      </c>
+      <c r="B21" s="143" t="inlineStr">
+        <is>
+          <t>预售</t>
+        </is>
+      </c>
+      <c r="C21" s="74" t="inlineStr">
+        <is>
+          <t>2026-08-06 14:45(映前5天)</t>
+        </is>
+      </c>
+      <c r="D21" s="149" t="n">
+        <v>18030000</v>
+      </c>
+      <c r="E21" s="144" t="inlineStr">
+        <is>
+          <t>点映及预售总票房180.3万；预售总票房3.5万；首日预售3.0万；首日排片占比77.1%；首日黄金场占比78.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="21.75" customHeight="1" s="69">
+      <c r="A22" s="145" t="inlineStr">
+        <is>
+          <t>欢迎来龙餐馆</t>
+        </is>
+      </c>
+      <c r="B22" s="147" t="inlineStr">
+        <is>
+          <t>票房</t>
+        </is>
+      </c>
+      <c r="C22" s="119" t="inlineStr">
+        <is>
+          <t>未上映</t>
+        </is>
+      </c>
+      <c r="D22" s="137" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="99" t="inlineStr">
+        <is>
+          <t>8月11日全国公映，8月8-10日超前点映</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="69">
+      <c r="A23" s="123" t="inlineStr">
+        <is>
+          <t>数据来源：猫眼专业版；金额为关键节点公开数据。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -4220,6 +4800,2254 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="69" min="1" max="1"/>
+    <col width="10" customWidth="1" style="69" min="2" max="2"/>
+    <col width="16" customWidth="1" style="69" min="3" max="3"/>
+    <col width="16" customWidth="1" style="69" min="4" max="4"/>
+    <col width="22" customWidth="1" style="69" min="5" max="5"/>
+    <col width="10" customWidth="1" style="69" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="69">
+      <c r="A1" s="178" t="inlineStr">
+        <is>
+          <t>《欢迎来龙餐馆》预售票房增长预测（V4 修正版）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="185" t="inlineStr">
+        <is>
+          <t>基准: 8/7 10:50实测 = 677.6万 | 基于8/6+8/7共33组数据修正 | 更新: 2026-08-07 10:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" s="69">
+      <c r="A4" s="181" t="inlineStr">
+        <is>
+          <t>一、8/7实测分时段增速回算</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="186" t="inlineStr">
+        <is>
+          <t>时段</t>
+        </is>
+      </c>
+      <c r="B5" s="186" t="inlineStr">
+        <is>
+          <t>时长(h)</t>
+        </is>
+      </c>
+      <c r="C5" s="186" t="inlineStr">
+        <is>
+          <t>增长(万)</t>
+        </is>
+      </c>
+      <c r="D5" s="186" t="inlineStr">
+        <is>
+          <t>小时增速(万/h)</t>
+        </is>
+      </c>
+      <c r="E5" s="186" t="inlineStr">
+        <is>
+          <t>时段归类</t>
+        </is>
+      </c>
+      <c r="F5" s="186" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="177" t="inlineStr">
+        <is>
+          <t>00:00-06:00 深夜凌晨</t>
+        </is>
+      </c>
+      <c r="B6" s="177" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="177" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="D6" s="177" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E6" s="177" t="inlineStr">
+        <is>
+          <t>深夜低谷</t>
+        </is>
+      </c>
+      <c r="F6" s="177" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="177" t="inlineStr">
+        <is>
+          <t>06:00-09:00 早晨</t>
+        </is>
+      </c>
+      <c r="B7" s="177" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="177" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D7" s="177" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E7" s="177" t="inlineStr">
+        <is>
+          <t>缓慢恢复</t>
+        </is>
+      </c>
+      <c r="F7" s="177" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="177" t="inlineStr">
+        <is>
+          <t>09:00-10:00 上午前段</t>
+        </is>
+      </c>
+      <c r="B8" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="177" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D8" s="177" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E8" s="177" t="inlineStr">
+        <is>
+          <t>开始回升</t>
+        </is>
+      </c>
+      <c r="F8" s="177" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="180" t="inlineStr">
+        <is>
+          <t>10:00-10:50 上午后段</t>
+        </is>
+      </c>
+      <c r="B9" s="180" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="C9" s="180" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="D9" s="180" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="E9" s="180" t="inlineStr">
+        <is>
+          <t>快速回升</t>
+        </is>
+      </c>
+      <c r="F9" s="180" t="inlineStr"/>
+    </row>
+    <row r="11" ht="24" customHeight="1" s="69">
+      <c r="A11" s="181" t="inlineStr">
+        <is>
+          <t>二、V4模型参数（基于8/6+8/7实测修正）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="186" t="inlineStr">
+        <is>
+          <t>参数</t>
+        </is>
+      </c>
+      <c r="B12" s="186" t="inlineStr">
+        <is>
+          <t>V3旧值</t>
+        </is>
+      </c>
+      <c r="C12" s="186" t="inlineStr">
+        <is>
+          <t>V4修正值</t>
+        </is>
+      </c>
+      <c r="D12" s="186" t="inlineStr">
+        <is>
+          <t>修正依据</t>
+        </is>
+      </c>
+      <c r="E12" s="150" t="n"/>
+      <c r="F12" s="151" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="187" t="inlineStr">
+        <is>
+          <t>基准增速(万/h)</t>
+        </is>
+      </c>
+      <c r="B13" s="187" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="C13" s="187" t="n">
+        <v>45</v>
+      </c>
+      <c r="D13" s="189" t="inlineStr">
+        <is>
+          <t>8/6白天49万/h + 8/7上午36.4万/h，取中间值</t>
+        </is>
+      </c>
+      <c r="E13" s="188" t="n"/>
+      <c r="F13" s="188" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="187" t="inlineStr">
+        <is>
+          <t>深夜系数(00-06时)</t>
+        </is>
+      </c>
+      <c r="B14" s="187" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C14" s="187" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D14" s="189" t="inlineStr">
+        <is>
+          <t>8/7实测00-06仅6.1万/h，远低于V3预期</t>
+        </is>
+      </c>
+      <c r="E14" s="188" t="n"/>
+      <c r="F14" s="188" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="187" t="inlineStr">
+        <is>
+          <t>早晨系数(06-10时)</t>
+        </is>
+      </c>
+      <c r="B15" s="187" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C15" s="187" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D15" s="189" t="inlineStr">
+        <is>
+          <t>8/7实测06-10仅1.3万/h，几乎停滞</t>
+        </is>
+      </c>
+      <c r="E15" s="188" t="n"/>
+      <c r="F15" s="188" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="187" t="inlineStr">
+        <is>
+          <t>上午系数(10-12时)</t>
+        </is>
+      </c>
+      <c r="B16" s="187" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C16" s="187" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D16" s="189" t="inlineStr">
+        <is>
+          <t>8/7 10:00-10:50已达36.4万/h，仍在加速</t>
+        </is>
+      </c>
+      <c r="E16" s="188" t="n"/>
+      <c r="F16" s="188" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="187" t="inlineStr">
+        <is>
+          <t>午间系数(12-14时)</t>
+        </is>
+      </c>
+      <c r="B17" s="187" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C17" s="187" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D17" s="189" t="inlineStr">
+        <is>
+          <t>参照8/6同期增速回升趋势</t>
+        </is>
+      </c>
+      <c r="E17" s="188" t="n"/>
+      <c r="F17" s="188" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="187" t="inlineStr">
+        <is>
+          <t>下午系数(14-18时)</t>
+        </is>
+      </c>
+      <c r="B18" s="187" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C18" s="187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="189" t="inlineStr">
+        <is>
+          <t>参照8/6下午高峰期56.7万/h</t>
+        </is>
+      </c>
+      <c r="E18" s="188" t="n"/>
+      <c r="F18" s="188" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="187" t="inlineStr">
+        <is>
+          <t>晚间系数(18-23时)</t>
+        </is>
+      </c>
+      <c r="B19" s="187" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C19" s="187" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D19" s="189" t="inlineStr">
+        <is>
+          <t>8/6晚间42万/h，8/7预期宣发效应更强</t>
+        </is>
+      </c>
+      <c r="E19" s="188" t="n"/>
+      <c r="F19" s="188" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="187" t="inlineStr">
+        <is>
+          <t>映前4天日期系数(8/7)</t>
+        </is>
+      </c>
+      <c r="B20" s="187" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C20" s="187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="189" t="inlineStr">
+        <is>
+          <t>作为基准日=1.0</t>
+        </is>
+      </c>
+      <c r="E20" s="188" t="n"/>
+      <c r="F20" s="188" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="187" t="inlineStr">
+        <is>
+          <t>映前3天日期系数(8/8)</t>
+        </is>
+      </c>
+      <c r="B21" s="187" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C21" s="187" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D21" s="189" t="inlineStr">
+        <is>
+          <t>点映前半天</t>
+        </is>
+      </c>
+      <c r="E21" s="188" t="n"/>
+      <c r="F21" s="188" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="187" t="inlineStr">
+        <is>
+          <t>点映系数(8/8 14:00+)</t>
+        </is>
+      </c>
+      <c r="B22" s="187" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C22" s="187" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D22" s="189" t="inlineStr">
+        <is>
+          <t>保持不变</t>
+        </is>
+      </c>
+      <c r="E22" s="188" t="n"/>
+      <c r="F22" s="188" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" s="69">
+      <c r="A24" s="181" t="inlineStr">
+        <is>
+          <t>三、V4逐小时预测（8/7 11:00 - 8/8 14:00）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="186" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B25" s="186" t="inlineStr">
+        <is>
+          <t>星期</t>
+        </is>
+      </c>
+      <c r="C25" s="186" t="inlineStr">
+        <is>
+          <t>预测增速(万/h)</t>
+        </is>
+      </c>
+      <c r="D25" s="186" t="inlineStr">
+        <is>
+          <t>预测累计(万)</t>
+        </is>
+      </c>
+      <c r="E25" s="186" t="inlineStr">
+        <is>
+          <t>时段说明</t>
+        </is>
+      </c>
+      <c r="F25" s="186" t="inlineStr">
+        <is>
+          <t>置信度</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="177" t="inlineStr">
+        <is>
+          <t>08-07 11:00</t>
+        </is>
+      </c>
+      <c r="B26" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C26" s="177" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D26" s="177" t="n">
+        <v>706.9</v>
+      </c>
+      <c r="E26" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·上午增长</t>
+        </is>
+      </c>
+      <c r="F26" s="177" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="177" t="inlineStr">
+        <is>
+          <t>08-07 12:00</t>
+        </is>
+      </c>
+      <c r="B27" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C27" s="177" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D27" s="177" t="n">
+        <v>736.1</v>
+      </c>
+      <c r="E27" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·午间小高峰</t>
+        </is>
+      </c>
+      <c r="F27" s="177" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="177" t="inlineStr">
+        <is>
+          <t>08-07 13:00</t>
+        </is>
+      </c>
+      <c r="B28" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C28" s="177" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="D28" s="177" t="n">
+        <v>774.4</v>
+      </c>
+      <c r="E28" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·午间小高峰</t>
+        </is>
+      </c>
+      <c r="F28" s="177" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="177" t="inlineStr">
+        <is>
+          <t>08-07 14:00</t>
+        </is>
+      </c>
+      <c r="B29" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C29" s="177" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="D29" s="177" t="n">
+        <v>812.6</v>
+      </c>
+      <c r="E29" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·下午高峰</t>
+        </is>
+      </c>
+      <c r="F29" s="177" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="177" t="inlineStr">
+        <is>
+          <t>08-07 15:00</t>
+        </is>
+      </c>
+      <c r="B30" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C30" s="177" t="n">
+        <v>45</v>
+      </c>
+      <c r="D30" s="177" t="n">
+        <v>857.6</v>
+      </c>
+      <c r="E30" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·下午高峰</t>
+        </is>
+      </c>
+      <c r="F30" s="177" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="177" t="inlineStr">
+        <is>
+          <t>08-07 16:00</t>
+        </is>
+      </c>
+      <c r="B31" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C31" s="177" t="n">
+        <v>45</v>
+      </c>
+      <c r="D31" s="177" t="n">
+        <v>902.6</v>
+      </c>
+      <c r="E31" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·下午高峰</t>
+        </is>
+      </c>
+      <c r="F31" s="177" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="177" t="inlineStr">
+        <is>
+          <t>08-07 17:00</t>
+        </is>
+      </c>
+      <c r="B32" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C32" s="177" t="n">
+        <v>45</v>
+      </c>
+      <c r="D32" s="177" t="n">
+        <v>947.6</v>
+      </c>
+      <c r="E32" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·下午高峰</t>
+        </is>
+      </c>
+      <c r="F32" s="177" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="177" t="inlineStr">
+        <is>
+          <t>08-07 18:00</t>
+        </is>
+      </c>
+      <c r="B33" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C33" s="177" t="n">
+        <v>45</v>
+      </c>
+      <c r="D33" s="177" t="n">
+        <v>992.6</v>
+      </c>
+      <c r="E33" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·晚间增长</t>
+        </is>
+      </c>
+      <c r="F33" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="177" t="inlineStr">
+        <is>
+          <t>08-07 19:00</t>
+        </is>
+      </c>
+      <c r="B34" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C34" s="177" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="D34" s="177" t="n">
+        <v>1042.1</v>
+      </c>
+      <c r="E34" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·晚间增长</t>
+        </is>
+      </c>
+      <c r="F34" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="177" t="inlineStr">
+        <is>
+          <t>08-07 20:00</t>
+        </is>
+      </c>
+      <c r="B35" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C35" s="177" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="D35" s="177" t="n">
+        <v>1091.6</v>
+      </c>
+      <c r="E35" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·晚间增长</t>
+        </is>
+      </c>
+      <c r="F35" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="177" t="inlineStr">
+        <is>
+          <t>08-07 21:00</t>
+        </is>
+      </c>
+      <c r="B36" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C36" s="177" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="D36" s="177" t="n">
+        <v>1141.1</v>
+      </c>
+      <c r="E36" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·晚间增长</t>
+        </is>
+      </c>
+      <c r="F36" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="177" t="inlineStr">
+        <is>
+          <t>08-07 22:00</t>
+        </is>
+      </c>
+      <c r="B37" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C37" s="177" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="D37" s="177" t="n">
+        <v>1190.6</v>
+      </c>
+      <c r="E37" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·晚间增长</t>
+        </is>
+      </c>
+      <c r="F37" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="177" t="inlineStr">
+        <is>
+          <t>08-07 23:00</t>
+        </is>
+      </c>
+      <c r="B38" s="177" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C38" s="177" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="D38" s="177" t="n">
+        <v>1240.1</v>
+      </c>
+      <c r="E38" s="177" t="inlineStr">
+        <is>
+          <t>映前4天·深夜回落</t>
+        </is>
+      </c>
+      <c r="F38" s="177" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="177" t="inlineStr">
+        <is>
+          <t>08-08 00:00</t>
+        </is>
+      </c>
+      <c r="B39" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C39" s="177" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D39" s="177" t="n">
+        <v>1264.9</v>
+      </c>
+      <c r="E39" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·深夜回落</t>
+        </is>
+      </c>
+      <c r="F39" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="177" t="inlineStr">
+        <is>
+          <t>08-08 01:00</t>
+        </is>
+      </c>
+      <c r="B40" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C40" s="177" t="n">
+        <v>7</v>
+      </c>
+      <c r="D40" s="177" t="n">
+        <v>1271.9</v>
+      </c>
+      <c r="E40" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·凌晨低谷</t>
+        </is>
+      </c>
+      <c r="F40" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="177" t="inlineStr">
+        <is>
+          <t>08-08 02:00</t>
+        </is>
+      </c>
+      <c r="B41" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C41" s="177" t="n">
+        <v>7</v>
+      </c>
+      <c r="D41" s="177" t="n">
+        <v>1278.9</v>
+      </c>
+      <c r="E41" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·凌晨低谷</t>
+        </is>
+      </c>
+      <c r="F41" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="177" t="inlineStr">
+        <is>
+          <t>08-08 03:00</t>
+        </is>
+      </c>
+      <c r="B42" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C42" s="177" t="n">
+        <v>7</v>
+      </c>
+      <c r="D42" s="177" t="n">
+        <v>1285.9</v>
+      </c>
+      <c r="E42" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·凌晨低谷</t>
+        </is>
+      </c>
+      <c r="F42" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="177" t="inlineStr">
+        <is>
+          <t>08-08 04:00</t>
+        </is>
+      </c>
+      <c r="B43" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C43" s="177" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" s="177" t="n">
+        <v>1292.9</v>
+      </c>
+      <c r="E43" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·凌晨低谷</t>
+        </is>
+      </c>
+      <c r="F43" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="177" t="inlineStr">
+        <is>
+          <t>08-08 05:00</t>
+        </is>
+      </c>
+      <c r="B44" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C44" s="177" t="n">
+        <v>7</v>
+      </c>
+      <c r="D44" s="177" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E44" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·凌晨低谷</t>
+        </is>
+      </c>
+      <c r="F44" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="177" t="inlineStr">
+        <is>
+          <t>08-08 06:00</t>
+        </is>
+      </c>
+      <c r="B45" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C45" s="177" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" s="177" t="n">
+        <v>1307</v>
+      </c>
+      <c r="E45" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·早晨恢复</t>
+        </is>
+      </c>
+      <c r="F45" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="177" t="inlineStr">
+        <is>
+          <t>08-08 07:00</t>
+        </is>
+      </c>
+      <c r="B46" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C46" s="177" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D46" s="177" t="n">
+        <v>1309.9</v>
+      </c>
+      <c r="E46" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·早晨恢复</t>
+        </is>
+      </c>
+      <c r="F46" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="177" t="inlineStr">
+        <is>
+          <t>08-08 08:00</t>
+        </is>
+      </c>
+      <c r="B47" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C47" s="177" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D47" s="177" t="n">
+        <v>1312.8</v>
+      </c>
+      <c r="E47" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·早晨恢复</t>
+        </is>
+      </c>
+      <c r="F47" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="177" t="inlineStr">
+        <is>
+          <t>08-08 09:00</t>
+        </is>
+      </c>
+      <c r="B48" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C48" s="177" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D48" s="177" t="n">
+        <v>1315.7</v>
+      </c>
+      <c r="E48" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·早晨恢复</t>
+        </is>
+      </c>
+      <c r="F48" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="177" t="inlineStr">
+        <is>
+          <t>08-08 10:00</t>
+        </is>
+      </c>
+      <c r="B49" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C49" s="177" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D49" s="177" t="n">
+        <v>1318.7</v>
+      </c>
+      <c r="E49" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·上午增长</t>
+        </is>
+      </c>
+      <c r="F49" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="177" t="inlineStr">
+        <is>
+          <t>08-08 11:00</t>
+        </is>
+      </c>
+      <c r="B50" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C50" s="177" t="n">
+        <v>38</v>
+      </c>
+      <c r="D50" s="177" t="n">
+        <v>1356.7</v>
+      </c>
+      <c r="E50" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·上午增长</t>
+        </is>
+      </c>
+      <c r="F50" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="177" t="inlineStr">
+        <is>
+          <t>08-08 12:00</t>
+        </is>
+      </c>
+      <c r="B51" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C51" s="177" t="n">
+        <v>38</v>
+      </c>
+      <c r="D51" s="177" t="n">
+        <v>1394.7</v>
+      </c>
+      <c r="E51" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·午间小高峰</t>
+        </is>
+      </c>
+      <c r="F51" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="177" t="inlineStr">
+        <is>
+          <t>08-08 13:00</t>
+        </is>
+      </c>
+      <c r="B52" s="177" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C52" s="177" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="D52" s="177" t="n">
+        <v>1444.4</v>
+      </c>
+      <c r="E52" s="177" t="inlineStr">
+        <is>
+          <t>映前3天·午间小高峰</t>
+        </is>
+      </c>
+      <c r="F52" s="177" t="inlineStr">
+        <is>
+          <t>中低</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1" s="69">
+      <c r="A54" s="181" t="inlineStr">
+        <is>
+          <t>四、V3 vs V4 关键节点对比</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="186" t="inlineStr">
+        <is>
+          <t>关键节点</t>
+        </is>
+      </c>
+      <c r="B55" s="186" t="inlineStr">
+        <is>
+          <t>V3预测(万)</t>
+        </is>
+      </c>
+      <c r="C55" s="186" t="inlineStr">
+        <is>
+          <t>V4预测(万)</t>
+        </is>
+      </c>
+      <c r="D55" s="186" t="inlineStr">
+        <is>
+          <t>偏差</t>
+        </is>
+      </c>
+      <c r="E55" s="186" t="inlineStr">
+        <is>
+          <t>目标(万)</t>
+        </is>
+      </c>
+      <c r="F55" s="186" t="inlineStr">
+        <is>
+          <t>达标?</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="177" t="inlineStr">
+        <is>
+          <t>8/7 12:00 午间</t>
+        </is>
+      </c>
+      <c r="B56" s="177" t="n">
+        <v>736.2</v>
+      </c>
+      <c r="C56" s="177" t="n">
+        <v>736.1</v>
+      </c>
+      <c r="D56" s="177" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E56" s="177" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="177" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="177" t="inlineStr">
+        <is>
+          <t>8/7 18:00 晚间</t>
+        </is>
+      </c>
+      <c r="B57" s="177" t="n">
+        <v>940.4</v>
+      </c>
+      <c r="C57" s="177" t="n">
+        <v>992.6</v>
+      </c>
+      <c r="D57" s="177" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="E57" s="177" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="177" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="177" t="inlineStr">
+        <is>
+          <t>8/7 23:00 收尾</t>
+        </is>
+      </c>
+      <c r="B58" s="177" t="n">
+        <v>1181.9</v>
+      </c>
+      <c r="C58" s="177" t="n">
+        <v>1240.1</v>
+      </c>
+      <c r="D58" s="177" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="E58" s="177" t="inlineStr">
+        <is>
+          <t>2229.34</t>
+        </is>
+      </c>
+      <c r="F58" s="198" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="177" t="inlineStr">
+        <is>
+          <t>8/8 08:00 早晨</t>
+        </is>
+      </c>
+      <c r="B59" s="177" t="n">
+        <v>1299.9</v>
+      </c>
+      <c r="C59" s="177" t="n">
+        <v>1312.8</v>
+      </c>
+      <c r="D59" s="177" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="E59" s="177" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="177" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="177" t="inlineStr">
+        <is>
+          <t>8/8 14:00 点映</t>
+        </is>
+      </c>
+      <c r="B60" s="177" t="n">
+        <v>1446</v>
+      </c>
+      <c r="C60" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="177" t="n">
+        <v>-1446</v>
+      </c>
+      <c r="E60" s="177" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="177" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1" s="69">
+      <c r="A62" s="181" t="inlineStr">
+        <is>
+          <t>五、V4模型修正说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1" s="69">
+      <c r="A63" s="192" t="inlineStr">
+        <is>
+          <t>• 基准增速微调：V3的43.3万/h → V4的45.0万/h（综合8/6白天49万/h + 8/7上午36.4万/h）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1" s="69">
+      <c r="A64" s="192" t="inlineStr">
+        <is>
+          <t>• 深夜系数大幅下调：V3的0.55 → V4的0.12（8/7实测00-06仅6.1万/h，远低于预期）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1" s="69">
+      <c r="A65" s="192" t="inlineStr">
+        <is>
+          <t>• 早晨系数大幅下调：V3的0.25 → V4的0.05（8/7实测06-10仅1.3万/h，几乎停滞）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1" s="69">
+      <c r="A66" s="192" t="inlineStr">
+        <is>
+          <t>• 上午系数上调：V3的0.45 → V4的0.65（10:00-10:50已达36.4万/h，加速明显）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1" s="69">
+      <c r="A67" s="192" t="inlineStr">
+        <is>
+          <t>• 下午系数上调：V3的0.75 → V4的1.0（参照8/6下午高峰56.7万/h）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1" s="69">
+      <c r="A68" s="192" t="inlineStr">
+        <is>
+          <t>• 晚间系数上调：V3的0.97 → V4的1.1（8/7宣发效应预期更强）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1" s="69">
+      <c r="A69" s="192" t="inlineStr">
+        <is>
+          <t>• 关键发现：8/7凌晨至早晨增速极低（1-6万/h），但10点后开始快速回升</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1" s="69">
+      <c r="A70" s="192" t="inlineStr">
+        <is>
+          <t>• V4预测8/7 23:00累计: 1240.1万，目标2229.34万</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1" s="69">
+      <c r="A71" s="192" t="inlineStr">
+        <is>
+          <t>• 差距: 目标比V4预测高约989万</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1" s="69">
+      <c r="A72" s="192" t="inlineStr">
+        <is>
+          <t>• 数据来源：猫眼专业版 | 基于33组实测数据(8/6 21:52-8/7 10:50)拟合</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A65:F65"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="69" min="1" max="1"/>
+    <col width="10" customWidth="1" style="69" min="2" max="2"/>
+    <col width="16" customWidth="1" style="69" min="3" max="3"/>
+    <col width="14" customWidth="1" style="69" min="4" max="4"/>
+    <col width="16" customWidth="1" style="69" min="5" max="5"/>
+    <col width="14" customWidth="1" style="69" min="6" max="6"/>
+    <col width="16" customWidth="1" style="69" min="7" max="7"/>
+    <col width="10" customWidth="1" style="69" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="69">
+      <c r="A1" s="178" t="inlineStr">
+        <is>
+          <t>《欢迎来龙餐馆》8/7目标1630.24万达成路径分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="199" t="inlineStr">
+        <is>
+          <t>当前: 677.6万(10:50) | 已增: 78.5万(4.8%) | 剩余: 1551.7万 / 12.2h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" s="69">
+      <c r="A4" s="181" t="inlineStr">
+        <is>
+          <t>一、当前进度总览</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="187" t="inlineStr">
+        <is>
+          <t>8/6收尾基准</t>
+        </is>
+      </c>
+      <c r="B5" s="177" t="inlineStr">
+        <is>
+          <t>599.1万</t>
+        </is>
+      </c>
+      <c r="C5" s="189" t="inlineStr">
+        <is>
+          <t>8/7 00:00实测</t>
+        </is>
+      </c>
+      <c r="D5" s="188" t="n"/>
+      <c r="E5" s="188" t="n"/>
+      <c r="F5" s="188" t="n"/>
+      <c r="G5" s="188" t="n"/>
+      <c r="H5" s="188" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="187" t="inlineStr">
+        <is>
+          <t>当前累计</t>
+        </is>
+      </c>
+      <c r="B6" s="177" t="inlineStr">
+        <is>
+          <t>677.6万</t>
+        </is>
+      </c>
+      <c r="C6" s="189" t="inlineStr">
+        <is>
+          <t>8/7 2026-08-07 10:50</t>
+        </is>
+      </c>
+      <c r="D6" s="188" t="n"/>
+      <c r="E6" s="188" t="n"/>
+      <c r="F6" s="188" t="n"/>
+      <c r="G6" s="188" t="n"/>
+      <c r="H6" s="188" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="187" t="inlineStr">
+        <is>
+          <t>8/7已增长</t>
+        </is>
+      </c>
+      <c r="B7" s="177" t="inlineStr">
+        <is>
+          <t>78.5万</t>
+        </is>
+      </c>
+      <c r="C7" s="189" t="inlineStr">
+        <is>
+          <t>完成度4.8%</t>
+        </is>
+      </c>
+      <c r="D7" s="188" t="n"/>
+      <c r="E7" s="188" t="n"/>
+      <c r="F7" s="188" t="n"/>
+      <c r="G7" s="188" t="n"/>
+      <c r="H7" s="188" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="187" t="inlineStr">
+        <is>
+          <t>目标新增</t>
+        </is>
+      </c>
+      <c r="B8" s="177" t="inlineStr">
+        <is>
+          <t>1630.24万</t>
+        </is>
+      </c>
+      <c r="C8" s="189" t="inlineStr">
+        <is>
+          <t>对标抓娃娃映前4天</t>
+        </is>
+      </c>
+      <c r="D8" s="188" t="n"/>
+      <c r="E8" s="188" t="n"/>
+      <c r="F8" s="188" t="n"/>
+      <c r="G8" s="188" t="n"/>
+      <c r="H8" s="188" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="187" t="inlineStr">
+        <is>
+          <t>目标累计</t>
+        </is>
+      </c>
+      <c r="B9" s="177" t="inlineStr">
+        <is>
+          <t>2229.34万</t>
+        </is>
+      </c>
+      <c r="C9" s="189">
+        <f>599.1+1630.24</f>
+        <v/>
+      </c>
+      <c r="D9" s="188" t="n"/>
+      <c r="E9" s="188" t="n"/>
+      <c r="F9" s="188" t="n"/>
+      <c r="G9" s="188" t="n"/>
+      <c r="H9" s="188" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="187" t="inlineStr">
+        <is>
+          <t>剩余需增长</t>
+        </is>
+      </c>
+      <c r="B10" s="177" t="inlineStr">
+        <is>
+          <t>1551.7万</t>
+        </is>
+      </c>
+      <c r="C10" s="189" t="inlineStr">
+        <is>
+          <t>距目标</t>
+        </is>
+      </c>
+      <c r="D10" s="188" t="n"/>
+      <c r="E10" s="188" t="n"/>
+      <c r="F10" s="188" t="n"/>
+      <c r="G10" s="188" t="n"/>
+      <c r="H10" s="188" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="187" t="inlineStr">
+        <is>
+          <t>剩余时间</t>
+        </is>
+      </c>
+      <c r="B11" s="177" t="inlineStr">
+        <is>
+          <t>12.2小时</t>
+        </is>
+      </c>
+      <c r="C11" s="189" t="inlineStr">
+        <is>
+          <t>至8/7 23:00</t>
+        </is>
+      </c>
+      <c r="D11" s="188" t="n"/>
+      <c r="E11" s="188" t="n"/>
+      <c r="F11" s="188" t="n"/>
+      <c r="G11" s="188" t="n"/>
+      <c r="H11" s="188" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="195" t="inlineStr">
+        <is>
+          <t>所需平均增速</t>
+        </is>
+      </c>
+      <c r="B12" s="198" t="inlineStr">
+        <is>
+          <t>127.2万/h</t>
+        </is>
+      </c>
+      <c r="C12" s="189" t="inlineStr">
+        <is>
+          <t>V4预测约45万/h</t>
+        </is>
+      </c>
+      <c r="D12" s="188" t="n"/>
+      <c r="E12" s="188" t="n"/>
+      <c r="F12" s="188" t="n"/>
+      <c r="G12" s="188" t="n"/>
+      <c r="H12" s="188" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" s="69">
+      <c r="A14" s="181" t="inlineStr">
+        <is>
+          <t>二、达成目标逐小时所需数据（从10:50开始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="186" t="inlineStr">
+        <is>
+          <t>目标时间</t>
+        </is>
+      </c>
+      <c r="B15" s="186" t="inlineStr">
+        <is>
+          <t>时长(h)</t>
+        </is>
+      </c>
+      <c r="C15" s="186" t="inlineStr">
+        <is>
+          <t>所需增速(万/h)</t>
+        </is>
+      </c>
+      <c r="D15" s="186" t="inlineStr">
+        <is>
+          <t>时段新增(万)</t>
+        </is>
+      </c>
+      <c r="E15" s="186" t="inlineStr">
+        <is>
+          <t>目标累计(万)</t>
+        </is>
+      </c>
+      <c r="F15" s="186" t="inlineStr">
+        <is>
+          <t>V4预测(万)</t>
+        </is>
+      </c>
+      <c r="G15" s="186" t="inlineStr">
+        <is>
+          <t>差距(万)</t>
+        </is>
+      </c>
+      <c r="H15" s="186" t="inlineStr">
+        <is>
+          <t>难度</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="177" t="inlineStr">
+        <is>
+          <t>10:50-12:00</t>
+        </is>
+      </c>
+      <c r="B16" s="177" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="C16" s="177" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="D16" s="177" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="E16" s="177" t="n">
+        <v>739.8</v>
+      </c>
+      <c r="F16" s="177" t="n">
+        <v>736.1</v>
+      </c>
+      <c r="G16" s="200" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H16" s="182" t="inlineStr">
+        <is>
+          <t>可行</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="177" t="inlineStr">
+        <is>
+          <t>12:00-14:00</t>
+        </is>
+      </c>
+      <c r="B17" s="177" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="177" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="D17" s="177" t="n">
+        <v>170.2</v>
+      </c>
+      <c r="E17" s="177" t="n">
+        <v>910</v>
+      </c>
+      <c r="F17" s="177" t="n">
+        <v>812.6</v>
+      </c>
+      <c r="G17" s="200" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="H17" s="194" t="inlineStr">
+        <is>
+          <t>有挑战</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="177" t="inlineStr">
+        <is>
+          <t>14:00-16:00</t>
+        </is>
+      </c>
+      <c r="B18" s="177" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="177" t="n">
+        <v>127.7</v>
+      </c>
+      <c r="D18" s="177" t="n">
+        <v>255.3</v>
+      </c>
+      <c r="E18" s="177" t="n">
+        <v>1165.3</v>
+      </c>
+      <c r="F18" s="177" t="n">
+        <v>902.6</v>
+      </c>
+      <c r="G18" s="200" t="n">
+        <v>262.7</v>
+      </c>
+      <c r="H18" s="195" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="177" t="inlineStr">
+        <is>
+          <t>16:00-18:00</t>
+        </is>
+      </c>
+      <c r="B19" s="177" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="177" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="D19" s="177" t="n">
+        <v>276.6</v>
+      </c>
+      <c r="E19" s="177" t="n">
+        <v>1441.9</v>
+      </c>
+      <c r="F19" s="177" t="n">
+        <v>992.6</v>
+      </c>
+      <c r="G19" s="200" t="n">
+        <v>449.3</v>
+      </c>
+      <c r="H19" s="195" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="177" t="inlineStr">
+        <is>
+          <t>18:00-20:00</t>
+        </is>
+      </c>
+      <c r="B20" s="177" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="177" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="D20" s="177" t="n">
+        <v>319.2</v>
+      </c>
+      <c r="E20" s="177" t="n">
+        <v>1761.1</v>
+      </c>
+      <c r="F20" s="177" t="n">
+        <v>1091.6</v>
+      </c>
+      <c r="G20" s="200" t="n">
+        <v>669.5</v>
+      </c>
+      <c r="H20" s="195" t="inlineStr">
+        <is>
+          <t>极难</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="177" t="inlineStr">
+        <is>
+          <t>20:00-22:00</t>
+        </is>
+      </c>
+      <c r="B21" s="177" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="177" t="n">
+        <v>170.2</v>
+      </c>
+      <c r="D21" s="177" t="n">
+        <v>340.4</v>
+      </c>
+      <c r="E21" s="177" t="n">
+        <v>2101.5</v>
+      </c>
+      <c r="F21" s="177" t="n">
+        <v>1190.6</v>
+      </c>
+      <c r="G21" s="200" t="n">
+        <v>910.9</v>
+      </c>
+      <c r="H21" s="195" t="inlineStr">
+        <is>
+          <t>极难</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="177" t="inlineStr">
+        <is>
+          <t>22:00-23:00</t>
+        </is>
+      </c>
+      <c r="B22" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="177" t="n">
+        <v>127.7</v>
+      </c>
+      <c r="D22" s="177" t="n">
+        <v>127.7</v>
+      </c>
+      <c r="E22" s="177" t="n">
+        <v>2229.2</v>
+      </c>
+      <c r="F22" s="177" t="n">
+        <v>1240.1</v>
+      </c>
+      <c r="G22" s="200" t="n">
+        <v>989.1</v>
+      </c>
+      <c r="H22" s="195" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" s="69">
+      <c r="A24" s="181" t="inlineStr">
+        <is>
+          <t>三、关键节点检查线（预警机制）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="186" t="inlineStr">
+        <is>
+          <t>检查时间</t>
+        </is>
+      </c>
+      <c r="B25" s="186" t="inlineStr">
+        <is>
+          <t>目标累计(万)</t>
+        </is>
+      </c>
+      <c r="C25" s="186" t="inlineStr">
+        <is>
+          <t>所需增速(万/h)</t>
+        </is>
+      </c>
+      <c r="D25" s="186" t="inlineStr">
+        <is>
+          <t>V4预测(万)</t>
+        </is>
+      </c>
+      <c r="E25" s="186" t="inlineStr">
+        <is>
+          <t>预测差距</t>
+        </is>
+      </c>
+      <c r="F25" s="186" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="G25" s="186" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="H25" s="151" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="177" t="inlineStr">
+        <is>
+          <t>8/7 12:00</t>
+        </is>
+      </c>
+      <c r="B26" s="177" t="n">
+        <v>739.8</v>
+      </c>
+      <c r="C26" s="177" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="D26" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="200" t="n">
+        <v>739.8</v>
+      </c>
+      <c r="F26" s="195" t="inlineStr">
+        <is>
+          <t>严重落后</t>
+        </is>
+      </c>
+      <c r="G26" s="177" t="inlineStr">
+        <is>
+          <t>上午尾段检查</t>
+        </is>
+      </c>
+      <c r="H26" s="188" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="177" t="inlineStr">
+        <is>
+          <t>8/7 14:00</t>
+        </is>
+      </c>
+      <c r="B27" s="177" t="n">
+        <v>910.1</v>
+      </c>
+      <c r="C27" s="177" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="D27" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="200" t="n">
+        <v>910.1</v>
+      </c>
+      <c r="F27" s="195" t="inlineStr">
+        <is>
+          <t>严重落后</t>
+        </is>
+      </c>
+      <c r="G27" s="177" t="inlineStr">
+        <is>
+          <t>午间检查</t>
+        </is>
+      </c>
+      <c r="H27" s="188" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="177" t="inlineStr">
+        <is>
+          <t>8/7 18:00</t>
+        </is>
+      </c>
+      <c r="B28" s="177" t="n">
+        <v>1442</v>
+      </c>
+      <c r="C28" s="177" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="D28" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="200" t="n">
+        <v>1442</v>
+      </c>
+      <c r="F28" s="195" t="inlineStr">
+        <is>
+          <t>严重落后</t>
+        </is>
+      </c>
+      <c r="G28" s="177" t="inlineStr">
+        <is>
+          <t>下午检查</t>
+        </is>
+      </c>
+      <c r="H28" s="188" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="177" t="inlineStr">
+        <is>
+          <t>8/7 20:00</t>
+        </is>
+      </c>
+      <c r="B29" s="177" t="n">
+        <v>1761.2</v>
+      </c>
+      <c r="C29" s="177" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="D29" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="200" t="n">
+        <v>1761.2</v>
+      </c>
+      <c r="F29" s="195" t="inlineStr">
+        <is>
+          <t>严重落后</t>
+        </is>
+      </c>
+      <c r="G29" s="177" t="inlineStr">
+        <is>
+          <t>晚高峰前检查</t>
+        </is>
+      </c>
+      <c r="H29" s="188" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="177" t="inlineStr">
+        <is>
+          <t>8/7 23:00</t>
+        </is>
+      </c>
+      <c r="B30" s="177" t="n">
+        <v>2229.3</v>
+      </c>
+      <c r="C30" s="177" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="D30" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="200" t="n">
+        <v>2229.3</v>
+      </c>
+      <c r="F30" s="195" t="inlineStr">
+        <is>
+          <t>严重落后</t>
+        </is>
+      </c>
+      <c r="G30" s="177" t="inlineStr">
+        <is>
+          <t>最终收尾</t>
+        </is>
+      </c>
+      <c r="H30" s="188" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1" s="69">
+      <c r="A32" s="181" t="inlineStr">
+        <is>
+          <t>四、结论与建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1" s="69">
+      <c r="A33" s="192" t="inlineStr">
+        <is>
+          <t>• 当前已增78.5万(4.8%)，剩余1551.7万需在12.2小时内完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1" s="69">
+      <c r="A34" s="192" t="inlineStr">
+        <is>
+          <t>• 达成目标需平均127.2万/h，是V4预测(45万/h)的2.8倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1" s="69">
+      <c r="A35" s="192" t="inlineStr">
+        <is>
+          <t>• V4预测8/7 23:00累计约1240.1万，比目标2229.34万低约989万</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" s="69">
+      <c r="A36" s="192" t="inlineStr">
+        <is>
+          <t>• 关键时段: 18:00-22:00需贡献约660万，占总剩余的43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1" s="69">
+      <c r="A37" s="196" t="inlineStr">
+        <is>
+          <t>• 预警线1: 12:00需达740万，V4预测约736万</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1" s="69">
+      <c r="A38" s="196" t="inlineStr">
+        <is>
+          <t>• 预警线2: 14:00需达910万，V4预测约813万</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1" s="69">
+      <c r="A39" s="196" t="inlineStr">
+        <is>
+          <t>• 预警线3: 18:00需达1442万，V4预测约993万</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1" s="69">
+      <c r="A40" s="197" t="inlineStr">
+        <is>
+          <t>• 总判断: 按当前趋势达成目标难度极大，需8/7下午至晚间出现爆发式增长(&gt;100万/h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1" s="69">
+      <c r="A41" s="192" t="inlineStr">
+        <is>
+          <t>• 参考抓娃娃: 映前4天日增1630万(68万/h)，但映前5天基数579万低于龙餐馆599万</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1" s="69">
+      <c r="A42" s="192" t="inlineStr">
+        <is>
+          <t>• 若8/7 23:00未达标，8/8点映开始后仍有追赶机会(抓娃娃映前3天爆发14877万)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="A34:H34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4306,7 +7134,7 @@
           <t>预售首日</t>
         </is>
       </c>
-      <c r="G5" s="188" t="n"/>
+      <c r="G5" s="151" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="177" t="inlineStr">
@@ -4335,7 +7163,7 @@
           <t>稳步增长</t>
         </is>
       </c>
-      <c r="G6" s="188" t="n"/>
+      <c r="G6" s="151" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="180" t="inlineStr">
@@ -4364,7 +7192,7 @@
           <t>点映开始!! 爆发</t>
         </is>
       </c>
-      <c r="G7" s="188" t="n"/>
+      <c r="G7" s="151" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="180" t="inlineStr">
@@ -4393,7 +7221,7 @@
           <t>点映高峰</t>
         </is>
       </c>
-      <c r="G8" s="188" t="n"/>
+      <c r="G8" s="151" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="177" t="inlineStr">
@@ -4422,7 +7250,7 @@
           <t>首映前夕</t>
         </is>
       </c>
-      <c r="G9" s="188" t="n"/>
+      <c r="G9" s="151" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="193" t="inlineStr">
@@ -4475,10 +7303,10 @@
           <t>8/6 23:01实测值</t>
         </is>
       </c>
-      <c r="D15" s="188" t="n"/>
-      <c r="E15" s="188" t="n"/>
-      <c r="F15" s="188" t="n"/>
-      <c r="G15" s="188" t="n"/>
+      <c r="D15" s="150" t="n"/>
+      <c r="E15" s="150" t="n"/>
+      <c r="F15" s="150" t="n"/>
+      <c r="G15" s="151" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="187" t="inlineStr">
@@ -4496,10 +7324,10 @@
           <t>最新获取数据</t>
         </is>
       </c>
-      <c r="D16" s="188" t="n"/>
-      <c r="E16" s="188" t="n"/>
-      <c r="F16" s="188" t="n"/>
-      <c r="G16" s="188" t="n"/>
+      <c r="D16" s="150" t="n"/>
+      <c r="E16" s="150" t="n"/>
+      <c r="F16" s="150" t="n"/>
+      <c r="G16" s="151" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="187" t="inlineStr">
@@ -4517,10 +7345,10 @@
           <t>约1.5小时增长，增速12.7万/h</t>
         </is>
       </c>
-      <c r="D17" s="188" t="n"/>
-      <c r="E17" s="188" t="n"/>
-      <c r="F17" s="188" t="n"/>
-      <c r="G17" s="188" t="n"/>
+      <c r="D17" s="150" t="n"/>
+      <c r="E17" s="150" t="n"/>
+      <c r="F17" s="150" t="n"/>
+      <c r="G17" s="151" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="194" t="inlineStr">
@@ -4538,10 +7366,10 @@
           <t>对标抓娃娃映前4天</t>
         </is>
       </c>
-      <c r="D18" s="188" t="n"/>
-      <c r="E18" s="188" t="n"/>
-      <c r="F18" s="188" t="n"/>
-      <c r="G18" s="188" t="n"/>
+      <c r="D18" s="150" t="n"/>
+      <c r="E18" s="150" t="n"/>
+      <c r="F18" s="150" t="n"/>
+      <c r="G18" s="151" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="187" t="inlineStr">
@@ -4558,10 +7386,10 @@
         <f> 599.1 + 1630.24</f>
         <v/>
       </c>
-      <c r="D19" s="188" t="n"/>
-      <c r="E19" s="188" t="n"/>
-      <c r="F19" s="188" t="n"/>
-      <c r="G19" s="188" t="n"/>
+      <c r="D19" s="150" t="n"/>
+      <c r="E19" s="150" t="n"/>
+      <c r="F19" s="150" t="n"/>
+      <c r="G19" s="151" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="187" t="inlineStr">
@@ -4579,10 +7407,10 @@
           <t>目标1630.24 - 已完成19.0</t>
         </is>
       </c>
-      <c r="D20" s="188" t="n"/>
-      <c r="E20" s="188" t="n"/>
-      <c r="F20" s="188" t="n"/>
-      <c r="G20" s="188" t="n"/>
+      <c r="D20" s="150" t="n"/>
+      <c r="E20" s="150" t="n"/>
+      <c r="F20" s="150" t="n"/>
+      <c r="G20" s="151" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="187" t="inlineStr">
@@ -4600,10 +7428,10 @@
           <t>至8/7 23:00</t>
         </is>
       </c>
-      <c r="D21" s="188" t="n"/>
-      <c r="E21" s="188" t="n"/>
-      <c r="F21" s="188" t="n"/>
-      <c r="G21" s="188" t="n"/>
+      <c r="D21" s="150" t="n"/>
+      <c r="E21" s="150" t="n"/>
+      <c r="F21" s="150" t="n"/>
+      <c r="G21" s="151" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="194" t="inlineStr">
@@ -4621,10 +7449,10 @@
           <t>V3预测仅43.3万/h，需达成的1.7倍</t>
         </is>
       </c>
-      <c r="D22" s="188" t="n"/>
-      <c r="E22" s="188" t="n"/>
-      <c r="F22" s="188" t="n"/>
-      <c r="G22" s="188" t="n"/>
+      <c r="D22" s="150" t="n"/>
+      <c r="E22" s="150" t="n"/>
+      <c r="F22" s="150" t="n"/>
+      <c r="G22" s="151" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="187" t="inlineStr">
@@ -4642,10 +7470,10 @@
           <t>比目标低1013.8万</t>
         </is>
       </c>
-      <c r="D23" s="188" t="n"/>
-      <c r="E23" s="188" t="n"/>
-      <c r="F23" s="188" t="n"/>
-      <c r="G23" s="188" t="n"/>
+      <c r="D23" s="150" t="n"/>
+      <c r="E23" s="150" t="n"/>
+      <c r="F23" s="150" t="n"/>
+      <c r="G23" s="151" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="187" t="inlineStr">
@@ -4663,10 +7491,10 @@
           <t>比目标低1013.8万</t>
         </is>
       </c>
-      <c r="D24" s="188" t="n"/>
-      <c r="E24" s="188" t="n"/>
-      <c r="F24" s="188" t="n"/>
-      <c r="G24" s="188" t="n"/>
+      <c r="D24" s="150" t="n"/>
+      <c r="E24" s="150" t="n"/>
+      <c r="F24" s="150" t="n"/>
+      <c r="G24" s="151" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1" s="69">
       <c r="A26" s="181" t="inlineStr">
@@ -4983,2180 +7811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F98"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" style="69" min="1" max="1"/>
-    <col width="10" customWidth="1" style="69" min="2" max="2"/>
-    <col width="16" customWidth="1" style="69" min="3" max="3"/>
-    <col width="16" customWidth="1" style="69" min="4" max="4"/>
-    <col width="22" customWidth="1" style="69" min="5" max="5"/>
-    <col width="10" customWidth="1" style="69" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" s="69">
-      <c r="A1" s="178" t="inlineStr">
-        <is>
-          <t>《欢迎来龙餐馆》预售票房增长预测（V3 修正版）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="185" t="inlineStr">
-        <is>
-          <t>基准: 23:01实测 = 565.5万 | 基于14组实测数据修正 | 数据来源: 猫眼专业版 | 更新: 2026-08-06 23:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" s="69">
-      <c r="A4" s="181" t="inlineStr">
-        <is>
-          <t>一、实测增速回算（14组数据，14:45-23:01）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="186" t="inlineStr">
-        <is>
-          <t>时间段</t>
-        </is>
-      </c>
-      <c r="B5" s="186" t="inlineStr">
-        <is>
-          <t>时长(min)</t>
-        </is>
-      </c>
-      <c r="C5" s="186" t="inlineStr">
-        <is>
-          <t>增长(万)</t>
-        </is>
-      </c>
-      <c r="D5" s="186" t="inlineStr">
-        <is>
-          <t>小时增速(万/h)</t>
-        </is>
-      </c>
-      <c r="E5" s="186" t="inlineStr">
-        <is>
-          <t>时段归类</t>
-        </is>
-      </c>
-      <c r="F5" s="186" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="177" t="inlineStr">
-        <is>
-          <t>14:45-14:55</t>
-        </is>
-      </c>
-      <c r="B6" s="177" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" s="177" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="D6" s="177" t="n">
-        <v>69</v>
-      </c>
-      <c r="E6" s="177" t="inlineStr">
-        <is>
-          <t>开售首波</t>
-        </is>
-      </c>
-      <c r="F6" s="177" t="inlineStr">
-        <is>
-          <t>爆发期，预售刚开放</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="177" t="inlineStr">
-        <is>
-          <t>14:55-15:01</t>
-        </is>
-      </c>
-      <c r="B7" s="177" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" s="177" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D7" s="177" t="n">
-        <v>84</v>
-      </c>
-      <c r="E7" s="177" t="inlineStr">
-        <is>
-          <t>下午高峰</t>
-        </is>
-      </c>
-      <c r="F7" s="177" t="inlineStr">
-        <is>
-          <t>开售高峰延续</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="180" t="inlineStr">
-        <is>
-          <t>15:01-15:03</t>
-        </is>
-      </c>
-      <c r="B8" s="180" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="180" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D8" s="180" t="n">
-        <v>105</v>
-      </c>
-      <c r="E8" s="180" t="inlineStr">
-        <is>
-          <t>短暂冲高</t>
-        </is>
-      </c>
-      <c r="F8" s="180" t="inlineStr">
-        <is>
-          <t>极短时脉冲</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="177" t="inlineStr">
-        <is>
-          <t>15:03-16:53</t>
-        </is>
-      </c>
-      <c r="B9" s="177" t="n">
-        <v>110</v>
-      </c>
-      <c r="C9" s="177" t="n">
-        <v>103.9</v>
-      </c>
-      <c r="D9" s="177" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="E9" s="177" t="inlineStr">
-        <is>
-          <t>下午平稳</t>
-        </is>
-      </c>
-      <c r="F9" s="177" t="inlineStr">
-        <is>
-          <t>通勤时段稳定增长</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="177" t="inlineStr">
-        <is>
-          <t>16:53-17:37</t>
-        </is>
-      </c>
-      <c r="B10" s="177" t="n">
-        <v>44</v>
-      </c>
-      <c r="C10" s="177" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="D10" s="177" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="E10" s="177" t="inlineStr">
-        <is>
-          <t>傍晚过渡</t>
-        </is>
-      </c>
-      <c r="F10" s="177" t="inlineStr">
-        <is>
-          <t>晚饭前回落</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="177" t="inlineStr">
-        <is>
-          <t>17:37-18:03</t>
-        </is>
-      </c>
-      <c r="B11" s="177" t="n">
-        <v>26</v>
-      </c>
-      <c r="C11" s="177" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="D11" s="177" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="E11" s="177" t="inlineStr">
-        <is>
-          <t>晚高峰前</t>
-        </is>
-      </c>
-      <c r="F11" s="177" t="inlineStr">
-        <is>
-          <t>逐步回升</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="177" t="inlineStr">
-        <is>
-          <t>18:03-20:02</t>
-        </is>
-      </c>
-      <c r="B12" s="177" t="n">
-        <v>119</v>
-      </c>
-      <c r="C12" s="177" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="D12" s="177" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="E12" s="177" t="inlineStr">
-        <is>
-          <t>晚间平稳</t>
-        </is>
-      </c>
-      <c r="F12" s="177" t="inlineStr">
-        <is>
-          <t>持续稳定增长</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="177" t="inlineStr">
-        <is>
-          <t>20:02-21:52</t>
-        </is>
-      </c>
-      <c r="B13" s="177" t="n">
-        <v>110</v>
-      </c>
-      <c r="C13" s="177" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="D13" s="177" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="E13" s="177" t="inlineStr">
-        <is>
-          <t>晚间回落</t>
-        </is>
-      </c>
-      <c r="F13" s="177" t="inlineStr">
-        <is>
-          <t>增速逐步下降</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="177" t="inlineStr">
-        <is>
-          <t>21:52-22:02</t>
-        </is>
-      </c>
-      <c r="B14" s="177" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="177" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="D14" s="177" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E14" s="177" t="inlineStr">
-        <is>
-          <t>深夜前低谷</t>
-        </is>
-      </c>
-      <c r="F14" s="177" t="inlineStr">
-        <is>
-          <t>晚间最低速</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="177" t="inlineStr">
-        <is>
-          <t>22:02-22:30</t>
-        </is>
-      </c>
-      <c r="B15" s="177" t="n">
-        <v>28</v>
-      </c>
-      <c r="C15" s="177" t="n">
-        <v>23</v>
-      </c>
-      <c r="D15" s="177" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="E15" s="177" t="inlineStr">
-        <is>
-          <t>夜间回升</t>
-        </is>
-      </c>
-      <c r="F15" s="177" t="inlineStr">
-        <is>
-          <t>22点后小幅反弹</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="180" t="inlineStr">
-        <is>
-          <t>22:30-22:50</t>
-        </is>
-      </c>
-      <c r="B16" s="180" t="n">
-        <v>20</v>
-      </c>
-      <c r="C16" s="180" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="D16" s="180" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="E16" s="180" t="inlineStr">
-        <is>
-          <t>夜间脉冲</t>
-        </is>
-      </c>
-      <c r="F16" s="180" t="inlineStr">
-        <is>
-          <t>疑似集中下单(异常高)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="177" t="inlineStr">
-        <is>
-          <t>22:50-23:01</t>
-        </is>
-      </c>
-      <c r="B17" s="177" t="n">
-        <v>11</v>
-      </c>
-      <c r="C17" s="177" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="D17" s="177" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="E17" s="177" t="inlineStr">
-        <is>
-          <t>深夜收尾</t>
-        </is>
-      </c>
-      <c r="F17" s="177" t="inlineStr">
-        <is>
-          <t>脉冲后回落</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="187" t="inlineStr">
-        <is>
-          <t>排除首波+脉冲后均值</t>
-        </is>
-      </c>
-      <c r="B18" s="187" t="inlineStr">
-        <is>
-          <t>8组稳态均值</t>
-        </is>
-      </c>
-      <c r="C18" s="151" t="n"/>
-      <c r="D18" s="187" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="E18" s="187" t="inlineStr">
-        <is>
-          <t>晚间均值42.0万/h | 白天均值45.5万/h</t>
-        </is>
-      </c>
-      <c r="F18" s="151" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="69">
-      <c r="A20" s="181" t="inlineStr">
-        <is>
-          <t>二、V3模型参数（基于14组实测数据修正）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="186" t="inlineStr">
-        <is>
-          <t>参数</t>
-        </is>
-      </c>
-      <c r="B21" s="186" t="inlineStr">
-        <is>
-          <t>V2旧值</t>
-        </is>
-      </c>
-      <c r="C21" s="186" t="inlineStr">
-        <is>
-          <t>V3修正值</t>
-        </is>
-      </c>
-      <c r="D21" s="186" t="inlineStr">
-        <is>
-          <t>修正依据</t>
-        </is>
-      </c>
-      <c r="E21" s="150" t="n"/>
-      <c r="F21" s="151" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="187" t="inlineStr">
-        <is>
-          <t>基准增速(万/h)</t>
-        </is>
-      </c>
-      <c r="B22" s="187" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="C22" s="187" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="D22" s="189" t="inlineStr">
-        <is>
-          <t>8组稳态实测均值(排除首波3组+脉冲1组)，较V2大幅下调</t>
-        </is>
-      </c>
-      <c r="E22" s="150" t="n"/>
-      <c r="F22" s="151" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="187" t="inlineStr">
-        <is>
-          <t>晚间系数(18-23时)</t>
-        </is>
-      </c>
-      <c r="B23" s="187" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="187" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="D23" s="189" t="inlineStr">
-        <is>
-          <t>晚间均值42.0/基准43.3，晚间略低于白天</t>
-        </is>
-      </c>
-      <c r="E23" s="150" t="n"/>
-      <c r="F23" s="151" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="187" t="inlineStr">
-        <is>
-          <t>深夜系数(23-01时)</t>
-        </is>
-      </c>
-      <c r="B24" s="187" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C24" s="187" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D24" s="189" t="inlineStr">
-        <is>
-          <t>23点后增速明显回落，参照21:52-22:02的29.4万/h</t>
-        </is>
-      </c>
-      <c r="E24" s="150" t="n"/>
-      <c r="F24" s="151" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="187" t="inlineStr">
-        <is>
-          <t>凌晨系数(01-06时)</t>
-        </is>
-      </c>
-      <c r="B25" s="187" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C25" s="187" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D25" s="189" t="inlineStr">
-        <is>
-          <t>深夜购票几乎停滞</t>
-        </is>
-      </c>
-      <c r="E25" s="150" t="n"/>
-      <c r="F25" s="151" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="187" t="inlineStr">
-        <is>
-          <t>早晨系数(06-10时)</t>
-        </is>
-      </c>
-      <c r="B26" s="187" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C26" s="187" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D26" s="189" t="inlineStr">
-        <is>
-          <t>少量恢复</t>
-        </is>
-      </c>
-      <c r="E26" s="150" t="n"/>
-      <c r="F26" s="151" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="187" t="inlineStr">
-        <is>
-          <t>上午系数(10-12时)</t>
-        </is>
-      </c>
-      <c r="B27" s="187" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C27" s="187" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="D27" s="189" t="inlineStr">
-        <is>
-          <t>平稳低速</t>
-        </is>
-      </c>
-      <c r="E27" s="150" t="n"/>
-      <c r="F27" s="151" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="187" t="inlineStr">
-        <is>
-          <t>午间系数(12-14时)</t>
-        </is>
-      </c>
-      <c r="B28" s="187" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C28" s="187" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D28" s="189" t="inlineStr">
-        <is>
-          <t>午间小幅回升</t>
-        </is>
-      </c>
-      <c r="E28" s="150" t="n"/>
-      <c r="F28" s="151" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="187" t="inlineStr">
-        <is>
-          <t>下午系数(14-18时)</t>
-        </is>
-      </c>
-      <c r="B29" s="187" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C29" s="187" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D29" s="189" t="inlineStr">
-        <is>
-          <t>下午增速回升，保持不变</t>
-        </is>
-      </c>
-      <c r="E29" s="150" t="n"/>
-      <c r="F29" s="151" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="187" t="inlineStr">
-        <is>
-          <t>映前5天日期系数(8/6)</t>
-        </is>
-      </c>
-      <c r="B30" s="187" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C30" s="187" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="189" t="inlineStr">
-        <is>
-          <t>作为基准日=1.0，其他日期相对调整</t>
-        </is>
-      </c>
-      <c r="E30" s="150" t="n"/>
-      <c r="F30" s="151" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="187" t="inlineStr">
-        <is>
-          <t>映前4天日期系数(8/7)</t>
-        </is>
-      </c>
-      <c r="B31" s="187" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C31" s="187" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="D31" s="189" t="inlineStr">
-        <is>
-          <t>宣发发酵，但想看基数低(2.5万)，适度上调</t>
-        </is>
-      </c>
-      <c r="E31" s="150" t="n"/>
-      <c r="F31" s="151" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="187" t="inlineStr">
-        <is>
-          <t>映前3天日期系数(8/8)</t>
-        </is>
-      </c>
-      <c r="B32" s="187" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C32" s="187" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="D32" s="189" t="inlineStr">
-        <is>
-          <t>点映前半天，预期温和增长</t>
-        </is>
-      </c>
-      <c r="E32" s="150" t="n"/>
-      <c r="F32" s="151" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="187" t="inlineStr">
-        <is>
-          <t>点映系数(8/8 14:00+)</t>
-        </is>
-      </c>
-      <c r="B33" s="187" t="n">
-        <v>3</v>
-      </c>
-      <c r="C33" s="187" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D33" s="189" t="inlineStr">
-        <is>
-          <t>点映票房计入，但想看基数偏低</t>
-        </is>
-      </c>
-      <c r="E33" s="150" t="n"/>
-      <c r="F33" s="151" t="n"/>
-    </row>
-    <row r="35" ht="24" customHeight="1" s="69">
-      <c r="A35" s="181" t="inlineStr">
-        <is>
-          <t>三、逐小时预测（8月6日23:00 - 8月8日14:00点映开始）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="186" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B36" s="186" t="inlineStr">
-        <is>
-          <t>星期</t>
-        </is>
-      </c>
-      <c r="C36" s="186" t="inlineStr">
-        <is>
-          <t>预测增速(万/h)</t>
-        </is>
-      </c>
-      <c r="D36" s="186" t="inlineStr">
-        <is>
-          <t>预测累计(万)</t>
-        </is>
-      </c>
-      <c r="E36" s="186" t="inlineStr">
-        <is>
-          <t>时段说明</t>
-        </is>
-      </c>
-      <c r="F36" s="186" t="inlineStr">
-        <is>
-          <t>置信度</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="190" t="inlineStr">
-        <is>
-          <t>08-06 23:00</t>
-        </is>
-      </c>
-      <c r="B37" s="190" t="inlineStr">
-        <is>
-          <t>周四</t>
-        </is>
-      </c>
-      <c r="C37" s="190" t="inlineStr">
-        <is>
-          <t>—（实际值）</t>
-        </is>
-      </c>
-      <c r="D37" s="190" t="n">
-        <v>565.5</v>
-      </c>
-      <c r="E37" s="190" t="inlineStr">
-        <is>
-          <t>映前5天·实测基准</t>
-        </is>
-      </c>
-      <c r="F37" s="190" t="inlineStr">
-        <is>
-          <t>实际</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="177" t="inlineStr">
-        <is>
-          <t>08-07 00:00</t>
-        </is>
-      </c>
-      <c r="B38" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C38" s="177" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="D38" s="177" t="n">
-        <v>589.3</v>
-      </c>
-      <c r="E38" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·深夜回落</t>
-        </is>
-      </c>
-      <c r="F38" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="177" t="inlineStr">
-        <is>
-          <t>08-07 01:00</t>
-        </is>
-      </c>
-      <c r="B39" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C39" s="177" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="D39" s="177" t="n">
-        <v>616.7</v>
-      </c>
-      <c r="E39" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F39" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="177" t="inlineStr">
-        <is>
-          <t>08-07 02:00</t>
-        </is>
-      </c>
-      <c r="B40" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C40" s="177" t="n">
-        <v>5</v>
-      </c>
-      <c r="D40" s="177" t="n">
-        <v>621.7</v>
-      </c>
-      <c r="E40" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F40" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="177" t="inlineStr">
-        <is>
-          <t>08-07 03:00</t>
-        </is>
-      </c>
-      <c r="B41" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C41" s="177" t="n">
-        <v>5</v>
-      </c>
-      <c r="D41" s="177" t="n">
-        <v>626.7</v>
-      </c>
-      <c r="E41" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F41" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="177" t="inlineStr">
-        <is>
-          <t>08-07 04:00</t>
-        </is>
-      </c>
-      <c r="B42" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C42" s="177" t="n">
-        <v>5</v>
-      </c>
-      <c r="D42" s="177" t="n">
-        <v>631.6</v>
-      </c>
-      <c r="E42" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F42" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="177" t="inlineStr">
-        <is>
-          <t>08-07 05:00</t>
-        </is>
-      </c>
-      <c r="B43" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C43" s="177" t="n">
-        <v>5</v>
-      </c>
-      <c r="D43" s="177" t="n">
-        <v>636.6</v>
-      </c>
-      <c r="E43" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F43" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="177" t="inlineStr">
-        <is>
-          <t>08-07 06:00</t>
-        </is>
-      </c>
-      <c r="B44" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C44" s="177" t="n">
-        <v>5</v>
-      </c>
-      <c r="D44" s="177" t="n">
-        <v>641.6</v>
-      </c>
-      <c r="E44" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·早晨恢复</t>
-        </is>
-      </c>
-      <c r="F44" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="177" t="inlineStr">
-        <is>
-          <t>08-07 07:00</t>
-        </is>
-      </c>
-      <c r="B45" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C45" s="177" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="D45" s="177" t="n">
-        <v>654</v>
-      </c>
-      <c r="E45" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·早晨恢复</t>
-        </is>
-      </c>
-      <c r="F45" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="177" t="inlineStr">
-        <is>
-          <t>08-07 08:00</t>
-        </is>
-      </c>
-      <c r="B46" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C46" s="177" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="D46" s="177" t="n">
-        <v>666.5</v>
-      </c>
-      <c r="E46" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·早晨恢复</t>
-        </is>
-      </c>
-      <c r="F46" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="177" t="inlineStr">
-        <is>
-          <t>08-07 09:00</t>
-        </is>
-      </c>
-      <c r="B47" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C47" s="177" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="D47" s="177" t="n">
-        <v>678.9</v>
-      </c>
-      <c r="E47" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·早晨恢复</t>
-        </is>
-      </c>
-      <c r="F47" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="177" t="inlineStr">
-        <is>
-          <t>08-07 10:00</t>
-        </is>
-      </c>
-      <c r="B48" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C48" s="177" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="D48" s="177" t="n">
-        <v>691.4</v>
-      </c>
-      <c r="E48" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·上午平稳</t>
-        </is>
-      </c>
-      <c r="F48" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="177" t="inlineStr">
-        <is>
-          <t>08-07 11:00</t>
-        </is>
-      </c>
-      <c r="B49" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C49" s="177" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="D49" s="177" t="n">
-        <v>713.8</v>
-      </c>
-      <c r="E49" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·上午平稳</t>
-        </is>
-      </c>
-      <c r="F49" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="177" t="inlineStr">
-        <is>
-          <t>08-07 12:00</t>
-        </is>
-      </c>
-      <c r="B50" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C50" s="177" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="D50" s="177" t="n">
-        <v>736.2</v>
-      </c>
-      <c r="E50" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·午间小高峰</t>
-        </is>
-      </c>
-      <c r="F50" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="177" t="inlineStr">
-        <is>
-          <t>08-07 13:00</t>
-        </is>
-      </c>
-      <c r="B51" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C51" s="177" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="D51" s="177" t="n">
-        <v>763.6</v>
-      </c>
-      <c r="E51" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·午间小高峰</t>
-        </is>
-      </c>
-      <c r="F51" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="177" t="inlineStr">
-        <is>
-          <t>08-07 14:00</t>
-        </is>
-      </c>
-      <c r="B52" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C52" s="177" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="D52" s="177" t="n">
-        <v>791</v>
-      </c>
-      <c r="E52" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·下午增长</t>
-        </is>
-      </c>
-      <c r="F52" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="177" t="inlineStr">
-        <is>
-          <t>08-07 15:00</t>
-        </is>
-      </c>
-      <c r="B53" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C53" s="177" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="D53" s="177" t="n">
-        <v>828.3</v>
-      </c>
-      <c r="E53" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·下午增长</t>
-        </is>
-      </c>
-      <c r="F53" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="177" t="inlineStr">
-        <is>
-          <t>08-07 16:00</t>
-        </is>
-      </c>
-      <c r="B54" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C54" s="177" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="D54" s="177" t="n">
-        <v>865.7</v>
-      </c>
-      <c r="E54" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·下午增长</t>
-        </is>
-      </c>
-      <c r="F54" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="177" t="inlineStr">
-        <is>
-          <t>08-07 17:00</t>
-        </is>
-      </c>
-      <c r="B55" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C55" s="177" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="D55" s="177" t="n">
-        <v>903</v>
-      </c>
-      <c r="E55" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·下午增长</t>
-        </is>
-      </c>
-      <c r="F55" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="177" t="inlineStr">
-        <is>
-          <t>08-07 18:00</t>
-        </is>
-      </c>
-      <c r="B56" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C56" s="177" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="D56" s="177" t="n">
-        <v>940.4</v>
-      </c>
-      <c r="E56" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·晚间增长</t>
-        </is>
-      </c>
-      <c r="F56" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="177" t="inlineStr">
-        <is>
-          <t>08-07 19:00</t>
-        </is>
-      </c>
-      <c r="B57" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C57" s="177" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="D57" s="177" t="n">
-        <v>988.7</v>
-      </c>
-      <c r="E57" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·晚间增长</t>
-        </is>
-      </c>
-      <c r="F57" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="177" t="inlineStr">
-        <is>
-          <t>08-07 20:00</t>
-        </is>
-      </c>
-      <c r="B58" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C58" s="177" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="D58" s="177" t="n">
-        <v>1037</v>
-      </c>
-      <c r="E58" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·晚间增长</t>
-        </is>
-      </c>
-      <c r="F58" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="177" t="inlineStr">
-        <is>
-          <t>08-07 21:00</t>
-        </is>
-      </c>
-      <c r="B59" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C59" s="177" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="D59" s="177" t="n">
-        <v>1085.3</v>
-      </c>
-      <c r="E59" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·晚间增长</t>
-        </is>
-      </c>
-      <c r="F59" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="177" t="inlineStr">
-        <is>
-          <t>08-07 22:00</t>
-        </is>
-      </c>
-      <c r="B60" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C60" s="177" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="D60" s="177" t="n">
-        <v>1133.6</v>
-      </c>
-      <c r="E60" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·晚间增长</t>
-        </is>
-      </c>
-      <c r="F60" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="177" t="inlineStr">
-        <is>
-          <t>08-07 23:00</t>
-        </is>
-      </c>
-      <c r="B61" s="177" t="inlineStr">
-        <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="C61" s="177" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="D61" s="177" t="n">
-        <v>1181.9</v>
-      </c>
-      <c r="E61" s="177" t="inlineStr">
-        <is>
-          <t>映前4天·深夜回落</t>
-        </is>
-      </c>
-      <c r="F61" s="177" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="177" t="inlineStr">
-        <is>
-          <t>08-08 00:00</t>
-        </is>
-      </c>
-      <c r="B62" s="177" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C62" s="177" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="D62" s="177" t="n">
-        <v>1209.3</v>
-      </c>
-      <c r="E62" s="177" t="inlineStr">
-        <is>
-          <t>映前3天·深夜回落</t>
-        </is>
-      </c>
-      <c r="F62" s="177" t="inlineStr">
-        <is>
-          <t>中低</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="177" t="inlineStr">
-        <is>
-          <t>08-08 01:00</t>
-        </is>
-      </c>
-      <c r="B63" s="177" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C63" s="177" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="D63" s="177" t="n">
-        <v>1241.4</v>
-      </c>
-      <c r="E63" s="177" t="inlineStr">
-        <is>
-          <t>映前3天·凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F63" s="177" t="inlineStr">
-        <is>
-          <t>中低</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="177" t="inlineStr">
-        <is>
-          <t>08-08 02:00</t>
-        </is>
-      </c>
-      <c r="B64" s="177" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C64" s="177" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D64" s="177" t="n">
-        <v>1247.3</v>
-      </c>
-      <c r="E64" s="177" t="inlineStr">
-        <is>
-          <t>映前3天·凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F64" s="177" t="inlineStr">
-        <is>
-          <t>中低</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="177" t="inlineStr">
-        <is>
-          <t>08-08 03:00</t>
-        </is>
-      </c>
-      <c r="B65" s="177" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C65" s="177" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D65" s="177" t="n">
-        <v>1253.1</v>
-      </c>
-      <c r="E65" s="177" t="inlineStr">
-        <is>
-          <t>映前3天·凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F65" s="177" t="inlineStr">
-        <is>
-          <t>中低</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="177" t="inlineStr">
-        <is>
-          <t>08-08 04:00</t>
-        </is>
-      </c>
-      <c r="B66" s="177" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C66" s="177" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D66" s="177" t="n">
-        <v>1258.9</v>
-      </c>
-      <c r="E66" s="177" t="inlineStr">
-        <is>
-          <t>映前3天·凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F66" s="177" t="inlineStr">
-        <is>
-          <t>中低</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="177" t="inlineStr">
-        <is>
-          <t>08-08 05:00</t>
-        </is>
-      </c>
-      <c r="B67" s="177" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C67" s="177" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D67" s="177" t="n">
-        <v>1264.8</v>
-      </c>
-      <c r="E67" s="177" t="inlineStr">
-        <is>
-          <t>映前3天·凌晨低谷</t>
-        </is>
-      </c>
-      <c r="F67" s="177" t="inlineStr">
-        <is>
-          <t>中低</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="177" t="inlineStr">
-        <is>
-          <t>08-08 06:00</t>
-        </is>
-      </c>
-      <c r="B68" s="177" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C68" s="177" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D68" s="177" t="n">
-        <v>1270.6</v>
-      </c>
-      <c r="E68" s="177" t="inlineStr">
-        <is>
-          <t>映前3天·早晨恢复</t>
-        </is>
-      </c>
-      <c r="F68" s="177" t="inlineStr">
-        <is>
-          <t>中低</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="177" t="inlineStr">
-        <is>
-          <t>08-08 07:00</t>
-        </is>
-      </c>
-      <c r="B69" s="177" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C69" s="177" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="D69" s="177" t="n">
-        <v>1285.3</v>
-      </c>
-      <c r="E69" s="177" t="inlineStr">
-        <is>
-          <t>映前3天·早晨恢复</t>
-        </is>
-      </c>
-      <c r="F69" s="177" t="inlineStr">
-        <is>
-          <t>中低</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="177" t="inlineStr">
-        <is>
-          <t>08-08 08:00</t>
-        </is>
-      </c>
-      <c r="B70" s="177" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C70" s="177" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="D70" s="177" t="n">
-        <v>1299.9</v>
-      </c>
-      <c r="E70" s="177" t="inlineStr">
-        <is>
-          <t>映前3天·早晨恢复</t>
-        </is>
-      </c>
-      <c r="F70" s="177" t="inlineStr">
-        <is>
-          <t>中低</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="177" t="inlineStr">
-        <is>
-          <t>08-08 09:00</t>
-        </is>
-      </c>
-      <c r="B71" s="177" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C71" s="177" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="D71" s="177" t="n">
-        <v>1314.5</v>
-      </c>
-      <c r="E71" s="177" t="inlineStr">
-        <is>
-          <t>映前3天·早晨恢复</t>
-        </is>
-      </c>
-      <c r="F71" s="177" t="inlineStr">
-        <is>
-          <t>中低</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="177" t="inlineStr">
-        <is>
-          <t>08-08 10:00</t>
-        </is>
-      </c>
-      <c r="B72" s="177" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C72" s="177" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="D72" s="177" t="n">
-        <v>1329.1</v>
-      </c>
-      <c r="E72" s="177" t="inlineStr">
-        <is>
-          <t>映前3天·上午平稳</t>
-        </is>
-      </c>
-      <c r="F72" s="177" t="inlineStr">
-        <is>
-          <t>中低</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="177" t="inlineStr">
-        <is>
-          <t>08-08 11:00</t>
-        </is>
-      </c>
-      <c r="B73" s="177" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C73" s="177" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="D73" s="177" t="n">
-        <v>1355.4</v>
-      </c>
-      <c r="E73" s="177" t="inlineStr">
-        <is>
-          <t>映前3天·上午平稳</t>
-        </is>
-      </c>
-      <c r="F73" s="177" t="inlineStr">
-        <is>
-          <t>中低</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="177" t="inlineStr">
-        <is>
-          <t>08-08 12:00</t>
-        </is>
-      </c>
-      <c r="B74" s="177" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C74" s="177" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="D74" s="177" t="n">
-        <v>1381.7</v>
-      </c>
-      <c r="E74" s="177" t="inlineStr">
-        <is>
-          <t>映前3天·午间小高峰</t>
-        </is>
-      </c>
-      <c r="F74" s="177" t="inlineStr">
-        <is>
-          <t>中低</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="177" t="inlineStr">
-        <is>
-          <t>08-08 13:00</t>
-        </is>
-      </c>
-      <c r="B75" s="177" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C75" s="177" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="D75" s="177" t="n">
-        <v>1413.9</v>
-      </c>
-      <c r="E75" s="177" t="inlineStr">
-        <is>
-          <t>映前3天·午间小高峰</t>
-        </is>
-      </c>
-      <c r="F75" s="177" t="inlineStr">
-        <is>
-          <t>中低</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="180" t="inlineStr">
-        <is>
-          <t>08-08 14:00</t>
-        </is>
-      </c>
-      <c r="B76" s="180" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="C76" s="180" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="D76" s="180" t="n">
-        <v>1446</v>
-      </c>
-      <c r="E76" s="180" t="inlineStr">
-        <is>
-          <t>点映开始·点映开始!!</t>
-        </is>
-      </c>
-      <c r="F76" s="180" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="24" customHeight="1" s="69">
-      <c r="A78" s="181" t="inlineStr">
-        <is>
-          <t>四、关键节点预测对比（V2 vs V3）</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="186" t="inlineStr">
-        <is>
-          <t>关键节点</t>
-        </is>
-      </c>
-      <c r="B79" s="186" t="inlineStr">
-        <is>
-          <t>V2预测(万)</t>
-        </is>
-      </c>
-      <c r="C79" s="186" t="inlineStr">
-        <is>
-          <t>V3预测(万)</t>
-        </is>
-      </c>
-      <c r="D79" s="186" t="inlineStr">
-        <is>
-          <t>偏差(万)</t>
-        </is>
-      </c>
-      <c r="E79" s="186" t="inlineStr">
-        <is>
-          <t>偏差率</t>
-        </is>
-      </c>
-      <c r="F79" s="186" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="177" t="inlineStr">
-        <is>
-          <t>8/6 23:00 深夜收尾</t>
-        </is>
-      </c>
-      <c r="B80" s="177" t="n">
-        <v>573.9</v>
-      </c>
-      <c r="C80" s="183" t="n">
-        <v>565.5</v>
-      </c>
-      <c r="D80" s="191" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="E80" s="177" t="inlineStr">
-        <is>
-          <t>-1.5%</t>
-        </is>
-      </c>
-      <c r="F80" s="177" t="inlineStr">
-        <is>
-          <t>实际值565.5万，V3以此为准</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="177" t="inlineStr">
-        <is>
-          <t>8/7 08:00 映前4天早晨</t>
-        </is>
-      </c>
-      <c r="B81" s="177" t="n">
-        <v>727.5</v>
-      </c>
-      <c r="C81" s="183" t="n">
-        <v>666.5</v>
-      </c>
-      <c r="D81" s="191" t="n">
-        <v>-61</v>
-      </c>
-      <c r="E81" s="177" t="inlineStr">
-        <is>
-          <t>-8.4%</t>
-        </is>
-      </c>
-      <c r="F81" s="177" t="inlineStr">
-        <is>
-          <t>V3基准下调，差距开始拉大</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="177" t="inlineStr">
-        <is>
-          <t>8/7 12:00 午间</t>
-        </is>
-      </c>
-      <c r="B82" s="177" t="n">
-        <v>863.7</v>
-      </c>
-      <c r="C82" s="183" t="n">
-        <v>736.2</v>
-      </c>
-      <c r="D82" s="191" t="n">
-        <v>-127.5</v>
-      </c>
-      <c r="E82" s="177" t="inlineStr">
-        <is>
-          <t>-14.8%</t>
-        </is>
-      </c>
-      <c r="F82" s="177" t="inlineStr">
-        <is>
-          <t>V3显著低于V2</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="177" t="inlineStr">
-        <is>
-          <t>8/7 18:00 晚间高峰</t>
-        </is>
-      </c>
-      <c r="B83" s="177" t="n">
-        <v>1171</v>
-      </c>
-      <c r="C83" s="183" t="n">
-        <v>940.4</v>
-      </c>
-      <c r="D83" s="191" t="n">
-        <v>-230.6</v>
-      </c>
-      <c r="E83" s="177" t="inlineStr">
-        <is>
-          <t>-19.7%</t>
-        </is>
-      </c>
-      <c r="F83" s="177" t="inlineStr">
-        <is>
-          <t>V3差距继续扩大</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="177" t="inlineStr">
-        <is>
-          <t>8/7 23:00 映前4天收尾</t>
-        </is>
-      </c>
-      <c r="B84" s="177" t="n">
-        <v>1478.3</v>
-      </c>
-      <c r="C84" s="183" t="n">
-        <v>1181.9</v>
-      </c>
-      <c r="D84" s="191" t="n">
-        <v>-296.4</v>
-      </c>
-      <c r="E84" s="177" t="inlineStr">
-        <is>
-          <t>-20.1%</t>
-        </is>
-      </c>
-      <c r="F84" s="177" t="inlineStr">
-        <is>
-          <t>V3约低230万</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="177" t="inlineStr">
-        <is>
-          <t>8/8 08:00 点映日早晨</t>
-        </is>
-      </c>
-      <c r="B85" s="177" t="n">
-        <v>1670.4</v>
-      </c>
-      <c r="C85" s="183" t="n">
-        <v>1299.9</v>
-      </c>
-      <c r="D85" s="191" t="n">
-        <v>-370.5</v>
-      </c>
-      <c r="E85" s="177" t="inlineStr">
-        <is>
-          <t>-22.2%</t>
-        </is>
-      </c>
-      <c r="F85" s="177" t="inlineStr">
-        <is>
-          <t>V3约低280万</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="177" t="inlineStr">
-        <is>
-          <t>8/8 14:00 点映开始!!</t>
-        </is>
-      </c>
-      <c r="B86" s="177" t="n">
-        <v>2071.9</v>
-      </c>
-      <c r="C86" s="183" t="n">
-        <v>1446</v>
-      </c>
-      <c r="D86" s="191" t="n">
-        <v>-625.9</v>
-      </c>
-      <c r="E86" s="177" t="inlineStr">
-        <is>
-          <t>-30.2%</t>
-        </is>
-      </c>
-      <c r="F86" s="177" t="inlineStr">
-        <is>
-          <t>V3约低515万，最大变量</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="24" customHeight="1" s="69">
-      <c r="A88" s="181" t="inlineStr">
-        <is>
-          <t>五、V3模型修正说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1" s="69">
-      <c r="A89" s="192" t="inlineStr">
-        <is>
-          <t>• 基准增速大幅修正：V2的58.2万/h → V3的43.3万/h（8组稳态实测均值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1" s="69">
-      <c r="A90" s="192" t="inlineStr">
-        <is>
-          <t>• V2高估原因：V2仅基于白天5组数据(14:45-18:03)，白天增速偏高；晚间18:03-23:01实测均值仅42.0万/h</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1" s="69">
-      <c r="A91" s="192" t="inlineStr">
-        <is>
-          <t>• 晚间系数修正：V2的1.0 → V3的0.97（晚间实际略低于白天）</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1" s="69">
-      <c r="A92" s="192" t="inlineStr">
-        <is>
-          <t>• 深夜系数修正：V2的0.7 → V3的0.55（21:52-22:02实测仅29.4万/h，远低于预期）</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1" s="69">
-      <c r="A93" s="192" t="inlineStr">
-        <is>
-          <t>• 日期系数修正：映前4天1.2→1.15、映前3天1.5→1.35、点映3.0→2.5（想看基数低，增长空间有限）</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1" s="69">
-      <c r="A94" s="192" t="inlineStr">
-        <is>
-          <t>• 实测vs预测验证：V2预测23:00=573.9万，实际565.5万，误差仅1.5%（V2单点尚可，但累积偏差放大）</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1" s="69">
-      <c r="A95" s="192" t="inlineStr">
-        <is>
-          <t>• V3与V2关键节点偏差：8/8 14:00点映开始 V3比V2低约515万（-24.9%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1" s="69">
-      <c r="A96" s="192" t="inlineStr">
-        <is>
-          <t>• 异常数据说明：22:30-22:50出现88.8万/h脉冲增速，疑似集中下单，已排除出基准计算</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1" s="69">
-      <c r="A97" s="192" t="inlineStr">
-        <is>
-          <t>• 最大变量：8/8 14:00点映口碑，若口碑爆发增速可能远超预测；若平庸则更低</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1" s="69">
-      <c r="A98" s="192" t="inlineStr">
-        <is>
-          <t>• 数据来源：猫眼专业版 | 预测基于14组实测数据(14:45-23:01)拟合，仅供参考</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="A90:F90"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="A89:F89"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A95:F95"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A97:F97"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A96:F96"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="A93:F93"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A98:F98"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="A88:F88"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="E18:F18"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7452,574 +8107,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="16" customWidth="1" style="68" min="1" max="1"/>
-    <col width="12" customWidth="1" style="68" min="2" max="2"/>
-    <col width="24" customWidth="1" style="68" min="3" max="3"/>
-    <col width="16" customWidth="1" style="68" min="4" max="4"/>
-    <col width="40" customWidth="1" style="68" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="31.5" customHeight="1" s="69">
-      <c r="A1" s="70" t="inlineStr">
-        <is>
-          <t>预售与票房关键节点数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="25.5" customHeight="1" s="69">
-      <c r="A2" s="72" t="inlineStr">
-        <is>
-          <t>电影</t>
-        </is>
-      </c>
-      <c r="B2" s="72" t="inlineStr">
-        <is>
-          <t>数据类型</t>
-        </is>
-      </c>
-      <c r="C2" s="72" t="inlineStr">
-        <is>
-          <t>时间节点</t>
-        </is>
-      </c>
-      <c r="D2" s="72" t="inlineStr">
-        <is>
-          <t>金额(元)</t>
-        </is>
-      </c>
-      <c r="E2" s="72" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="21.75" customHeight="1" s="69">
-      <c r="A3" s="142" t="inlineStr">
-        <is>
-          <t>抓娃娃</t>
-        </is>
-      </c>
-      <c r="B3" s="143" t="inlineStr">
-        <is>
-          <t>预售</t>
-        </is>
-      </c>
-      <c r="C3" s="121" t="inlineStr">
-        <is>
-          <t>映前10天(07-06)</t>
-        </is>
-      </c>
-      <c r="D3" s="77" t="n">
-        <v>630000</v>
-      </c>
-      <c r="E3" s="144" t="inlineStr">
-        <is>
-          <t>当日新增63.0万</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="21.75" customHeight="1" s="69">
-      <c r="A4" s="145" t="inlineStr">
-        <is>
-          <t>抓娃娃</t>
-        </is>
-      </c>
-      <c r="B4" s="143" t="inlineStr">
-        <is>
-          <t>预售</t>
-        </is>
-      </c>
-      <c r="C4" s="119" t="inlineStr">
-        <is>
-          <t>映前4天(07-12)</t>
-        </is>
-      </c>
-      <c r="D4" s="83" t="n">
-        <v>1720000</v>
-      </c>
-      <c r="E4" s="146" t="inlineStr">
-        <is>
-          <t>当日新增17.2万</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="21.75" customHeight="1" s="69">
-      <c r="A5" s="142" t="inlineStr">
-        <is>
-          <t>抓娃娃</t>
-        </is>
-      </c>
-      <c r="B5" s="143" t="inlineStr">
-        <is>
-          <t>预售</t>
-        </is>
-      </c>
-      <c r="C5" s="121" t="inlineStr">
-        <is>
-          <t>映前3天(07-13)</t>
-        </is>
-      </c>
-      <c r="D5" s="77" t="n">
-        <v>3450000</v>
-      </c>
-      <c r="E5" s="144" t="inlineStr">
-        <is>
-          <t>当日新增34.5万，点映首日</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="21.75" customHeight="1" s="69">
-      <c r="A6" s="145" t="inlineStr">
-        <is>
-          <t>抓娃娃</t>
-        </is>
-      </c>
-      <c r="B6" s="143" t="inlineStr">
-        <is>
-          <t>预售</t>
-        </is>
-      </c>
-      <c r="C6" s="119" t="inlineStr">
-        <is>
-          <t>映前2天(07-14)</t>
-        </is>
-      </c>
-      <c r="D6" s="83" t="n">
-        <v>15640000</v>
-      </c>
-      <c r="E6" s="146" t="inlineStr">
-        <is>
-          <t>当日新增156.4万</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="21.75" customHeight="1" s="69">
-      <c r="A7" s="142" t="inlineStr">
-        <is>
-          <t>抓娃娃</t>
-        </is>
-      </c>
-      <c r="B7" s="143" t="inlineStr">
-        <is>
-          <t>预售</t>
-        </is>
-      </c>
-      <c r="C7" s="121" t="inlineStr">
-        <is>
-          <t>映前1天(07-15)</t>
-        </is>
-      </c>
-      <c r="D7" s="78" t="n">
-        <v>138260000</v>
-      </c>
-      <c r="E7" s="144" t="inlineStr">
-        <is>
-          <t>当日新增1382.6万，预售集中爆发</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="21.75" customHeight="1" s="69">
-      <c r="A8" s="145" t="inlineStr">
-        <is>
-          <t>抓娃娃</t>
-        </is>
-      </c>
-      <c r="B8" s="147" t="inlineStr">
-        <is>
-          <t>票房</t>
-        </is>
-      </c>
-      <c r="C8" s="80" t="inlineStr">
-        <is>
-          <t>2024-07-13(点映首日)</t>
-        </is>
-      </c>
-      <c r="D8" s="83" t="n">
-        <v>156000000</v>
-      </c>
-      <c r="E8" s="146" t="inlineStr">
-        <is>
-          <t>点映首日单日票房约1.56亿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="21.75" customHeight="1" s="69">
-      <c r="A9" s="142" t="inlineStr">
-        <is>
-          <t>抓娃娃</t>
-        </is>
-      </c>
-      <c r="B9" s="147" t="inlineStr">
-        <is>
-          <t>票房</t>
-        </is>
-      </c>
-      <c r="C9" s="74" t="inlineStr">
-        <is>
-          <t>2024-07-16(上映首日)</t>
-        </is>
-      </c>
-      <c r="D9" s="77" t="n">
-        <v>650000000</v>
-      </c>
-      <c r="E9" s="144" t="inlineStr">
-        <is>
-          <t>正式上映首日票房6.5亿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="21.75" customHeight="1" s="69">
-      <c r="A10" s="145" t="inlineStr">
-        <is>
-          <t>抓娃娃</t>
-        </is>
-      </c>
-      <c r="B10" s="147" t="inlineStr">
-        <is>
-          <t>票房</t>
-        </is>
-      </c>
-      <c r="C10" s="80" t="inlineStr">
-        <is>
-          <t>2024-07-20(上映第4天)</t>
-        </is>
-      </c>
-      <c r="D10" s="83" t="n">
-        <v>1100000000</v>
-      </c>
-      <c r="E10" s="146" t="inlineStr">
-        <is>
-          <t>票房突破11亿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="21.75" customHeight="1" s="69">
-      <c r="A11" s="142" t="inlineStr">
-        <is>
-          <t>抓娃娃</t>
-        </is>
-      </c>
-      <c r="B11" s="147" t="inlineStr">
-        <is>
-          <t>票房</t>
-        </is>
-      </c>
-      <c r="C11" s="121" t="inlineStr">
-        <is>
-          <t>累计总票房</t>
-        </is>
-      </c>
-      <c r="D11" s="78" t="n">
-        <v>3300000000</v>
-      </c>
-      <c r="E11" s="144" t="inlineStr">
-        <is>
-          <t>累计票房超33亿，暑期档冠军</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="21.75" customHeight="1" s="69">
-      <c r="A12" s="145" t="inlineStr">
-        <is>
-          <t>独行月球</t>
-        </is>
-      </c>
-      <c r="B12" s="143" t="inlineStr">
-        <is>
-          <t>预售</t>
-        </is>
-      </c>
-      <c r="C12" s="119" t="inlineStr">
-        <is>
-          <t>映前10天(07-19)</t>
-        </is>
-      </c>
-      <c r="D12" s="83" t="n">
-        <v>890000</v>
-      </c>
-      <c r="E12" s="146" t="inlineStr">
-        <is>
-          <t>当日新增8.9万</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="21.75" customHeight="1" s="69">
-      <c r="A13" s="142" t="inlineStr">
-        <is>
-          <t>独行月球</t>
-        </is>
-      </c>
-      <c r="B13" s="143" t="inlineStr">
-        <is>
-          <t>预售</t>
-        </is>
-      </c>
-      <c r="C13" s="121" t="inlineStr">
-        <is>
-          <t>映前7天(07-22)</t>
-        </is>
-      </c>
-      <c r="D13" s="77" t="n">
-        <v>2582000</v>
-      </c>
-      <c r="E13" s="144" t="inlineStr">
-        <is>
-          <t>当日新增258.2万</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="21.75" customHeight="1" s="69">
-      <c r="A14" s="145" t="inlineStr">
-        <is>
-          <t>独行月球</t>
-        </is>
-      </c>
-      <c r="B14" s="143" t="inlineStr">
-        <is>
-          <t>预售</t>
-        </is>
-      </c>
-      <c r="C14" s="119" t="inlineStr">
-        <is>
-          <t>映前4天(07-25)</t>
-        </is>
-      </c>
-      <c r="D14" s="83" t="n">
-        <v>27200000</v>
-      </c>
-      <c r="E14" s="146" t="inlineStr">
-        <is>
-          <t>当日新增272.0万</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21.75" customHeight="1" s="69">
-      <c r="A15" s="142" t="inlineStr">
-        <is>
-          <t>独行月球</t>
-        </is>
-      </c>
-      <c r="B15" s="143" t="inlineStr">
-        <is>
-          <t>预售</t>
-        </is>
-      </c>
-      <c r="C15" s="121" t="inlineStr">
-        <is>
-          <t>映前3天(07-26)</t>
-        </is>
-      </c>
-      <c r="D15" s="77" t="n">
-        <v>40040000</v>
-      </c>
-      <c r="E15" s="144" t="inlineStr">
-        <is>
-          <t>当日新增400.4万</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="21.75" customHeight="1" s="69">
-      <c r="A16" s="145" t="inlineStr">
-        <is>
-          <t>独行月球</t>
-        </is>
-      </c>
-      <c r="B16" s="143" t="inlineStr">
-        <is>
-          <t>预售</t>
-        </is>
-      </c>
-      <c r="C16" s="119" t="inlineStr">
-        <is>
-          <t>映前2天(07-27)</t>
-        </is>
-      </c>
-      <c r="D16" s="83" t="n">
-        <v>89600000</v>
-      </c>
-      <c r="E16" s="146" t="inlineStr">
-        <is>
-          <t>当日新增896.0万</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="21.75" customHeight="1" s="69">
-      <c r="A17" s="142" t="inlineStr">
-        <is>
-          <t>独行月球</t>
-        </is>
-      </c>
-      <c r="B17" s="143" t="inlineStr">
-        <is>
-          <t>预售</t>
-        </is>
-      </c>
-      <c r="C17" s="121" t="inlineStr">
-        <is>
-          <t>映前1天(07-28)</t>
-        </is>
-      </c>
-      <c r="D17" s="78" t="n">
-        <v>273500000</v>
-      </c>
-      <c r="E17" s="144" t="inlineStr">
-        <is>
-          <t>当日新增2735.0万，预售集中爆发</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="21.75" customHeight="1" s="69">
-      <c r="A18" s="145" t="inlineStr">
-        <is>
-          <t>独行月球</t>
-        </is>
-      </c>
-      <c r="B18" s="147" t="inlineStr">
-        <is>
-          <t>票房</t>
-        </is>
-      </c>
-      <c r="C18" s="80" t="inlineStr">
-        <is>
-          <t>2022-07-29(上映首日)</t>
-        </is>
-      </c>
-      <c r="D18" s="83" t="n">
-        <v>200000000</v>
-      </c>
-      <c r="E18" s="146" t="inlineStr">
-        <is>
-          <t>首日票房(含预售)破2亿</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="21.75" customHeight="1" s="69">
-      <c r="A19" s="142" t="inlineStr">
-        <is>
-          <t>独行月球</t>
-        </is>
-      </c>
-      <c r="B19" s="147" t="inlineStr">
-        <is>
-          <t>票房</t>
-        </is>
-      </c>
-      <c r="C19" s="74" t="inlineStr">
-        <is>
-          <t>2022-07-31(上映第3天)</t>
-        </is>
-      </c>
-      <c r="D19" s="77" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="E19" s="148" t="inlineStr">
-        <is>
-          <t>3天票房破10亿</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="21.75" customHeight="1" s="69">
-      <c r="A20" s="145" t="inlineStr">
-        <is>
-          <t>独行月球</t>
-        </is>
-      </c>
-      <c r="B20" s="147" t="inlineStr">
-        <is>
-          <t>票房</t>
-        </is>
-      </c>
-      <c r="C20" s="119" t="inlineStr">
-        <is>
-          <t>累计总票房</t>
-        </is>
-      </c>
-      <c r="D20" s="78" t="n">
-        <v>3103000000</v>
-      </c>
-      <c r="E20" s="146" t="inlineStr">
-        <is>
-          <t>最终累计票房31.03亿，2022年度亚军</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="21.75" customHeight="1" s="69">
-      <c r="A21" s="142" t="inlineStr">
-        <is>
-          <t>欢迎来龙餐馆</t>
-        </is>
-      </c>
-      <c r="B21" s="143" t="inlineStr">
-        <is>
-          <t>预售</t>
-        </is>
-      </c>
-      <c r="C21" s="74" t="inlineStr">
-        <is>
-          <t>2026-08-06 14:45(映前5天)</t>
-        </is>
-      </c>
-      <c r="D21" s="149" t="n">
-        <v>18030000</v>
-      </c>
-      <c r="E21" s="144" t="inlineStr">
-        <is>
-          <t>点映及预售总票房180.3万；预售总票房3.5万；首日预售3.0万；首日排片占比77.1%；首日黄金场占比78.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="21.75" customHeight="1" s="69">
-      <c r="A22" s="145" t="inlineStr">
-        <is>
-          <t>欢迎来龙餐馆</t>
-        </is>
-      </c>
-      <c r="B22" s="147" t="inlineStr">
-        <is>
-          <t>票房</t>
-        </is>
-      </c>
-      <c r="C22" s="119" t="inlineStr">
-        <is>
-          <t>未上映</t>
-        </is>
-      </c>
-      <c r="D22" s="137" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" s="99" t="inlineStr">
-        <is>
-          <t>8月11日全国公映，8月8-10日超前点映</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1" s="69">
-      <c r="A23" s="123" t="inlineStr">
-        <is>
-          <t>数据来源：猫眼专业版；金额为关键节点公开数据。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
 </file>